--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.2%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.8%</t>
+          <t>430.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-650.3%</t>
+          <t>-643.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.8%</t>
+          <t>-160.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-350.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-163.9%</t>
+          <t>-181.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-6.967160419040002</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.329941562892845</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7766563720186828</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.651168331611383</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.153880127349304</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.2512273750347207</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7766563720186828</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.64714202707698</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.536881516091936</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>0.09792471821608428</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7766563720186828</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.647039925755396</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.541367961293324</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>0.09870165610695869</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7811428172200714</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.646919574605993</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-7.900898283797326</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.03976016959659168</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7811428172200714</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.652269877904044</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-7.951247347251548</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.05198377502110274</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-0.8314918806742935</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.629976459788688</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.048866624672945</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.08798973536789267</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-0.9291111580956901</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.574446643957619</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.102938124181303</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.1067247788496641</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-0.9831826576040495</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.544897300574175</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.307196299511167</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.1829148518629671</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.110821602218038</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.473827130924424</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.340849138019641</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.1918934327819204</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.211234970135076</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.418061664658638</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.267379306352192</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1471337986215198</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.137765138467627</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.477515265152528</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.442503723738735</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.2026283448286206</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.312889555854171</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.386995835468119</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.676955817753225</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.3036283473360122</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.312889555854171</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.379776670566523</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.781330548779671</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.3520504305205669</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.417264286880617</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.310479641176679</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-8.943844014478255</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.4159400269614446</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.514897717299303</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.253015372764023</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.069880807846545</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.4636610156796457</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489646094489561</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.270860075078983</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.012809035950614</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4368419712348723</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489646094489561</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.274850410765384</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.154480877674734</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.4949859348232621</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489646094489561</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.273375183866643</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.1048900332499</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.4600961868884563</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.440055250064727</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.318183100686415</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-8.955971698778043</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4135799867463965</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.408805659329554</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.323881721480836</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.730126546058631</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.3136628526224232</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.36687898374239</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.358616799869343</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.60554788972104</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.2626922455313276</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.36687898374239</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.359755944425402</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.658443177765326</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.2812165865869343</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.361923637653944</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.365362926240577</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.586310002477445</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2466296122331455</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.361923637653944</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.371096630479213</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.514943609867798</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2278203175831517</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.290557245044296</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.404179203651137</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.421484575882573</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.2003201853019694</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.290557245044296</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.39429572233823</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.410831394329142</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.1978934731799709</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.290557245044296</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.392461161838856</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.312924355652651</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.1590309726828352</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.22257149518374</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.432952296781729</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.288970814676693</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1487810501469586</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.198617954207782</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.447992927512797</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.024910876353896</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.05641739097959197</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9345580158849862</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.593168574344722</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.597401606198926</v>
+        <v>-7.317831252849058</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1117992834220951</v>
+        <v>0.2236274247620424</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9345580158849862</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.590381540684422</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.557217307832736</v>
+        <v>-7.277646954482868</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1282166266564126</v>
+        <v>0.24004476799636</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.8943737175187955</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.614835743591978</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.393817436893373</v>
+        <v>-7.114247083543505</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1929433962529146</v>
+        <v>0.3047715375928619</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.730973846579433</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.712242487376352</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.160336214663775</v>
+        <v>-6.880765861313907</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2942603139826065</v>
+        <v>0.4060884553225539</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.4974926243498344</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.860255649551963</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.01066982365626</v>
+        <v>-6.731099470306392</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3512346600726532</v>
+        <v>0.4630628014126006</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.4045891331072985</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.913105533984526</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.878394350025373</v>
+        <v>-6.598823996675505</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3995123362720352</v>
+        <v>0.5113404776119821</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.2723136594764118</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.987838304910085</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.722656017465631</v>
+        <v>-6.443085664115763</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4646227299835686</v>
+        <v>0.5764508713235159</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.1165753269166703</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.084096365133567</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.637691350736311</v>
+        <v>-6.358120997386443</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5115149378989554</v>
+        <v>0.6233430792389023</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.0316106601873507</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.147981506394817</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.743281340509416</v>
+        <v>-6.463710987159548</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3413030123904948</v>
+        <v>0.4531311537304421</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.1372006499604551</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.956651582931736</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.675046755883988</v>
+        <v>-6.39547640253412</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.417141188117752</v>
+        <v>0.5289693294576994</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.1187853270879191</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>3.016245118532344</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.527106714476389</v>
+        <v>-6.247536361126521</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3564382819926242</v>
+        <v>0.4682664233325715</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.0984644111793615</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.90855874538931</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.4741371922224</v>
+        <v>-6.194566838872532</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3689121046407413</v>
+        <v>0.4807402459806887</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.931626472488226</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.30834899626211</v>
+        <v>-6.028778642912242</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4282667709297647</v>
+        <v>0.5400949122697121</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.924665860393133</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.274985789783341</v>
+        <v>-5.995415436433473</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.456074407902415</v>
+        <v>0.5679025492423624</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.939128214774276</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.166726652660819</v>
+        <v>-5.887156299310951</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4939101832106187</v>
+        <v>0.6057383245505661</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.933660335233471</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.043435517843688</v>
+        <v>-5.76386516449382</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5407247311480483</v>
+        <v>0.6525528724879956</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.07779624589175788</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>3.005133110134326</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.990738650712397</v>
+        <v>-5.711168297362529</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5695044562378899</v>
+        <v>0.6813325975778373</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1304931130230491</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>3.044452208650426</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.746973208728953</v>
+        <v>-5.467402855379085</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6627913413783184</v>
+        <v>0.7746194827182658</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1304931130230491</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>3.040232916997477</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.657197536352481</v>
+        <v>-5.377627183002613</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7008259242489232</v>
+        <v>0.8126540655888705</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920925579373591</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.079316897866078</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.407347142403406</v>
+        <v>-5.127776789053538</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7935081568122553</v>
+        <v>0.9053362981522026</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920925579373591</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.07205897284978</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.231455049935974</v>
+        <v>-4.951884696586106</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8674641173198769</v>
+        <v>0.9792922586598241</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920925579373591</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.075658096370429</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.060008586913511</v>
+        <v>-4.780438233563642</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9493702085834159</v>
+        <v>1.061198349923363</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.3635390209598222</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.191853480238461</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.97998629980439</v>
+        <v>-4.700415946454521</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9803996010433611</v>
+        <v>1.092227742383308</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.4435613080689432</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.23888733012023</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.916350557570455</v>
+        <v>-4.636780204220587</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.010548698991252</v>
+        <v>1.1223768403312</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.5071970503028778</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.281763576514908</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.82265323935406</v>
+        <v>-4.543082886004192</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.029221885061606</v>
+        <v>1.141050026401553</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.5071970503028778</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.262957835298704</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.833155862419349</v>
+        <v>-4.553585509069481</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.026763912460368</v>
+        <v>1.138592053800315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4966944272375888</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.258399338084408</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.760913294248154</v>
+        <v>-4.481342940898286</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.059590253563666</v>
+        <v>1.171418394903613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4966944272375888</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.262328651919228</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.743199607370289</v>
+        <v>-4.463629254020421</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.067354312232152</v>
+        <v>1.179182453572099</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4998757561345056</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.264916033174718</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.634394721890562</v>
+        <v>-4.354824368540694</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.107874337644036</v>
+        <v>1.219702478983983</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4998757561345056</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.261914104394712</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.414373923853551</v>
+        <v>-4.134803570503683</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.197461693869455</v>
+        <v>1.309289835209402</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6410956012024859</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.348225048446114</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.281506234790274</v>
+        <v>-4.001935881440405</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.266502952296589</v>
+        <v>1.378331093636536</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6410956012024859</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.364119231247937</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.161333151425775</v>
+        <v>-3.881762798075906</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.31571803008269</v>
+        <v>1.427546171422638</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.7612686845669848</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.437368925706939</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.026079790095798</v>
+        <v>-3.746509436745928</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.379907477176121</v>
+        <v>1.491735618516069</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.8965220458969619</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.528609045066365</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.08595461745349</v>
+        <v>-3.806384264103621</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.34199503763447</v>
+        <v>1.453823178974418</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.8366472185392698</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.478721640053176</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.966134386542653</v>
+        <v>-3.686564033192783</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.405212299233013</v>
+        <v>1.517040440572961</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.8366472185392698</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.494010809287384</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.968604093004459</v>
+        <v>-3.689033739654589</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.311868615970733</v>
+        <v>1.42369675731068</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.8341775120774637</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.400173184732742</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.036974279328469</v>
+        <v>-3.757403925978599</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.20378240292643</v>
+        <v>1.315610544266378</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.325000465639772</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.050762332175515</v>
+        <v>-3.771191978825646</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.188703890419503</v>
+        <v>1.30053203175945</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.315437174271664</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.106282408068105</v>
+        <v>-3.826712054718235</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.303526696754669</v>
+        <v>1.415354838094617</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.452468010963866</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.930808148275636</v>
+        <v>-3.651237794925766</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.378283632663445</v>
+        <v>1.490111774003392</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.457035242955654</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.922883773690721</v>
+        <v>-3.643313420340852</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.357195411258618</v>
+        <v>1.469023552598565</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.432777271716861</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.88922022821844</v>
+        <v>-3.60964987486857</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.29919914284898</v>
+        <v>1.411027284188928</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8771167565859606</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.362268482219687</v>
+        <v>3.38151371240168</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.829367609014716</v>
+        <v>-3.549797255664847</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.333312576962602</v>
+        <v>1.445140718302549</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8771167565859606</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.372440868651819</v>
+        <v>3.391686098833812</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.743124145988339</v>
+        <v>-3.463553792638469</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.362756232747013</v>
+        <v>1.474584374086961</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8771167565859606</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.367387139225679</v>
+        <v>3.386632369407672</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.788430965387318</v>
+        <v>-3.508860612037449</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.336409280431947</v>
+        <v>1.448237421771894</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8363065935767298</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.334676816864667</v>
+        <v>3.353922047046659</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.81746407008962</v>
+        <v>-3.537893716739751</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.325347911584128</v>
+        <v>1.437176052924075</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8363065935767298</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.335228689897768</v>
+        <v>3.354473920079761</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.724653588638761</v>
+        <v>-3.445083235288891</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.291744796055837</v>
+        <v>1.403572937395785</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8970416913909339</v>
+        <v>0.9291170750275891</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.320187670659649</v>
+        <v>3.339432900841642</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.769043057968188</v>
+        <v>-3.489472704618319</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.275862484248667</v>
+        <v>1.387690625588614</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8526522220615063</v>
+        <v>0.8847276056981614</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.295427464986593</v>
+        <v>3.314672695168587</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.885584663073531</v>
+        <v>-3.606014309723662</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.224321550718253</v>
+        <v>1.3361496920582</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.7681860005928187</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220578210435111</v>
+        <v>3.239823440617104</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.925508757656103</v>
+        <v>-3.645938404306234</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.213843208715891</v>
+        <v>1.325671350055839</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.7681860005928187</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.226069506265778</v>
+        <v>3.245314736447771</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.953289155557456</v>
+        <v>-3.673718802207587</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.214228251323889</v>
+        <v>1.326056392663836</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7083302190548104</v>
+        <v>0.7404056026914656</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220898469293505</v>
+        <v>3.240143699475498</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.071669828287594</v>
+        <v>-3.792099474937725</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.005231702232487</v>
+        <v>1.117059843572434</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6731877505404894</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018923478003573</v>
+        <v>3.038168708185566</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.180283906730925</v>
+        <v>-3.900713553381056</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.08193573157436</v>
+        <v>1.193763872914308</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6731877505404894</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.139073138722778</v>
+        <v>3.158318368904772</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.144874868482782</v>
+        <v>-3.865304515132913</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.11061237297594</v>
+        <v>1.222440514315888</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6731877505404894</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153586164825101</v>
+        <v>3.172831395007095</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.106491205924631</v>
+        <v>-3.826920852574762</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.12338527934157</v>
+        <v>1.235213420681517</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7115714130986406</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.174035803702361</v>
+        <v>3.193281033884354</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.929374875889465</v>
+        <v>-3.649804522539596</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.190960840200938</v>
+        <v>1.302788981540885</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7115714130986406</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170764832547663</v>
+        <v>3.190010062729656</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.974467120723011</v>
+        <v>-3.694896767373141</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.173607334029433</v>
+        <v>1.28543547536938</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6175999862925956</v>
+        <v>0.6496753699292508</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134310598407942</v>
+        <v>3.153555828589935</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.795091699484243</v>
+        <v>-3.515521346134374</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.239144477831354</v>
+        <v>1.350972619171302</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7743767444633143</v>
+        <v>0.8064521280999695</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.222163628616787</v>
+        <v>3.24140885879878</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.840105913004849</v>
+        <v>-3.56053555965498</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.201946247754701</v>
+        <v>1.313774389094649</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7440278491487097</v>
+        <v>0.7761032327853649</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.184761746759615</v>
+        <v>3.204006976941607</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.107110423277285</v>
+        <v>-3.827540069927415</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.100836005984673</v>
+        <v>1.21266414732462</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5496648111057612</v>
+        <v>0.5817401947424163</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073835486272791</v>
+        <v>3.093080716454784</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.208308204714458</v>
+        <v>-3.928737851364588</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.059560815306305</v>
+        <v>1.171388956646253</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.481255997560442</v>
+        <v>0.5133313811970972</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031994120042101</v>
+        <v>3.051239350224094</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.201797238100145</v>
+        <v>-3.922226884750275</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.059765163506347</v>
+        <v>1.171593304846295</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.481255997560442</v>
+        <v>0.5133313811970972</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029594081596418</v>
+        <v>3.048839311778411</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.182759110392848</v>
+        <v>-3.903188757042978</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.063905133797511</v>
+        <v>1.175733275137459</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.4551477698659027</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.991208634005946</v>
+        <v>3.010453864187939</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.235274912667668</v>
+        <v>-3.955704559317798</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.162193214521773</v>
+        <v>1.274021355861721</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.4551477698659027</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.110503035640136</v>
+        <v>3.129748265822129</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.249141674001586</v>
+        <v>-3.969571320651716</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.157479838974339</v>
+        <v>1.269307980314287</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.4172898531320797</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088621614585976</v>
+        <v>3.107866844767969</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.204337502461656</v>
+        <v>-3.924767149111786</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.181410037987237</v>
+        <v>1.293238179327185</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.4172898531320797</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094630144982902</v>
+        <v>3.113875375164895</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.056594532226653</v>
+        <v>-3.777024178876784</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.138457447358438</v>
+        <v>1.250285588698386</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.5850972103669629</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.093264780601031</v>
+        <v>3.112510010783025</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.140415753501352</v>
+        <v>-3.860845400151482</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.107722580380039</v>
+        <v>1.219550721719987</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.5850972103669629</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.115303632314506</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.134263047448568</v>
+        <v>-3.854692694098697</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.110846011192812</v>
+        <v>1.22267415253276</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5591745327830919</v>
+        <v>0.5912499164197472</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.119657604337835</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.151072345599069</v>
+        <v>-3.871501992249199</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.103202768672721</v>
+        <v>1.215030910012669</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5423652346325902</v>
+        <v>0.5744406182692456</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.108652502187644</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.088774346822947</v>
+        <v>-3.809203993473077</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.194457521979991</v>
+        <v>1.306285663319939</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5876594989070323</v>
+        <v>0.6197348825436877</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.20216461454913</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.886984149157789</v>
+        <v>-3.607413795807919</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.077465602760181</v>
+        <v>1.189293744100129</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7856776910761867</v>
+        <v>0.8177530747128421</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.12326753156475</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.937870861843984</v>
+        <v>-3.658300508494114</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.127401150007878</v>
+        <v>1.239229291347826</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7347909783899922</v>
+        <v>0.7668663620266476</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.163025736275208</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.851260119194177</v>
+        <v>-3.571689765844306</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.176673183183845</v>
+        <v>1.288501324523793</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8134167095951504</v>
+        <v>0.8454920932318059</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.224828911114347</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.911469417199461</v>
+        <v>-3.631899063849591</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.151125444806403</v>
+        <v>1.262953586146351</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.7852827952265213</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.187239313135848</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.835047370767534</v>
+        <v>-3.555477017417664</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.180185881419102</v>
+        <v>1.29201402275905</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.7852827952265213</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.185730931175776</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.790674239128966</v>
+        <v>-3.511103885779095</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.197798001509966</v>
+        <v>1.309626142849914</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.8296559268650899</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.212217677594353</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.813154589987851</v>
+        <v>-3.53358423663798</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.183199655305002</v>
+        <v>1.29502779664495</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.8296559268650899</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.206611471732944</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.765498859426795</v>
+        <v>-3.485928506076924</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.208643704557229</v>
+        <v>1.320471845897177</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8452362737894902</v>
+        <v>0.8773116574261456</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.241586667097382</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.66498070092804</v>
+        <v>-3.38541034757817</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.253743341331456</v>
+        <v>1.365571482671404</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9457544322882447</v>
+        <v>0.9778298159249001</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.30678993557136</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.649075371495687</v>
+        <v>-3.369505018145817</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.246860145580269</v>
+        <v>1.358688286920217</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8666417715790058</v>
+        <v>0.8987171552156612</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.246077011621689</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.604236969887289</v>
+        <v>-3.324666616537419</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.268893208834257</v>
+        <v>1.380721350174205</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8711852045238753</v>
+        <v>0.9032605881605307</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.252900773999239</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.623735426129298</v>
+        <v>-3.344165072779427</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.265254765968532</v>
+        <v>1.37708290730848</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.823100563243971</v>
+        <v>0.8551759468806264</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.228210928862374</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.579532589043397</v>
+        <v>-3.299962235693527</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.288815503330729</v>
+        <v>1.400643644670677</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8673034003298714</v>
+        <v>0.8993787839665268</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.260612233641751</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.587092254880444</v>
+        <v>-3.307521901530574</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.284201637465158</v>
+        <v>1.396029778805106</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.9541821879763461</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.291904276516891</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.428800837341172</v>
+        <v>-3.149230483991301</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.398765969663907</v>
+        <v>1.510594111003854</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.9541821879763461</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.343152041699931</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.221158833706696</v>
+        <v>-2.941588480356825</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.48026347571195</v>
+        <v>1.592091617051898</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.129748807974167</v>
+        <v>1.161824191610822</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.466177948474869</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.170126740984168</v>
+        <v>-2.890556387634297</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.495624541039231</v>
+        <v>1.607452682379179</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.180780900696695</v>
+        <v>1.21285628433335</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.491745432346656</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.104902559856962</v>
+        <v>-2.825332206507091</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.538901617582819</v>
+        <v>1.650729758922767</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.246005081823901</v>
+        <v>1.278080465460556</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.548067345115684</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.067475539785828</v>
+        <v>-2.787905186435958</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.549833397910553</v>
+        <v>1.661661539250501</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.251256619853082</v>
+        <v>1.283332003489738</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.547179240232474</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.087587195820536</v>
+        <v>-2.808016842470666</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.543045527827909</v>
+        <v>1.654873669167857</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.262283964850502</v>
+        <v>1.294359348487157</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.555052439562166</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.033842381393332</v>
+        <v>-2.754272028043461</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.725101224620002</v>
+        <v>1.83692936595995</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.272347274290964</v>
+        <v>1.304422657927619</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.721648196247653</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.959060120368319</v>
+        <v>-2.679489767018449</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.875127038247824</v>
+        <v>1.986955179587772</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.347129535315976</v>
+        <v>1.379204918952631</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.886630462080478</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.932976036104511</v>
+        <v>-2.653405682754641</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.877268647967206</v>
+        <v>1.989096789307155</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.347129535315976</v>
+        <v>1.379204918952631</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.878338438094337</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.84509812299539</v>
+        <v>-2.56552776964552</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.910613008794634</v>
+        <v>2.022441150134582</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.463055177739327</v>
+        <v>1.495130561375983</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.946087019132127</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.836205661602107</v>
+        <v>-2.556635308252237</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.931724399078739</v>
+        <v>2.043552540418687</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.463055177739327</v>
+        <v>1.495130561375983</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.963641424858919</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.004681778571985</v>
+        <v>-2.725111425222114</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.856188999695372</v>
+        <v>1.96801714103532</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.435107342022747</v>
+        <v>1.467182725659402</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.938727770833554</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.558425585942545</v>
+        <v>-2.278855232592675</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.015961173935009</v>
+        <v>2.127789315274958</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.340388672353114</v>
+        <v>1.372464055989769</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.863166266219637</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.535704482259392</v>
+        <v>-2.256134128909522</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.015713637905175</v>
+        <v>2.127541779245123</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.340388672353114</v>
+        <v>1.372464055989769</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.853830288716541</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.664906295553435</v>
+        <v>-2.385335942203564</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.122939038438727</v>
+        <v>2.234767179778675</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.211186859059072</v>
+        <v>1.243262242695727</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.935215326591285</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.81968730233169</v>
+        <v>-2.54011694898182</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.098104458221071</v>
+        <v>2.20993259956102</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177819185004596</v>
+        <v>1.209894568641251</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.952272544652246</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.812632612116517</v>
+        <v>-2.533062258766646</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.097601690296686</v>
+        <v>2.209429831636634</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184873875219769</v>
+        <v>1.216949258856425</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.953180714770895</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.785681387790029</v>
+        <v>-2.506111034440158</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.118388333672023</v>
+        <v>2.230216475011971</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199754221247489</v>
+        <v>1.231829604884144</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.972115076032268</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921634395846345</v>
+        <v>-2.642064042496475</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.248110262594456</v>
+        <v>2.359938403934404</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199754221247489</v>
+        <v>1.231829604884144</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.156218208177227</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.944042513651217</v>
+        <v>-2.664472160301347</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.2312637103755</v>
+        <v>2.343091851715449</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199754221247489</v>
+        <v>1.231829604884144</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.148334903080221</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.972266749228818</v>
+        <v>-2.692696395878947</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.222028015694097</v>
+        <v>2.333856157034046</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217730973698797</v>
+        <v>1.249806357335452</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.161174954100644</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981707675117347</v>
+        <v>-2.702137321767477</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.274505363060533</v>
+        <v>2.386333504400481</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340158091242189</v>
+        <v>1.372233474878844</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.290884942348526</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.033981282452989</v>
+        <v>-2.754410929103118</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.256487014671577</v>
+        <v>2.368315156011525</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.287884483906547</v>
+        <v>1.319959867543202</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.262411872492442</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.110311260053895</v>
+        <v>-2.830740906704024</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.22406683652499</v>
+        <v>2.335894977864938</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.287884483906547</v>
+        <v>1.319959867543202</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.260523685386217</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.312564980378248</v>
+        <v>-3.032994627028378</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.137985577998111</v>
+        <v>2.249813719338059</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.085630763582194</v>
+        <v>1.117706147218849</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.133991682794467</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.474133405905503</v>
+        <v>-3.194563052555633</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.071792217997361</v>
+        <v>2.183620359337309</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.9909232234209697</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>4.056355938725892</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.606434698003056</v>
+        <v>-3.326864344653186</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.031945108024258</v>
+        <v>2.143773249364207</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.9909232234209697</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>4.069429345591811</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.792303008842286</v>
+        <v>-3.512732655492416</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.949602980471506</v>
+        <v>2.061431121811454</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8002822464643667</v>
+        <v>0.832357630101022</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.966295186382782</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.820203795951759</v>
+        <v>-3.540633442601889</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.93696670675472</v>
+        <v>2.048794848094667</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7656853223214319</v>
+        <v>0.7977607059580872</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.944061073024023</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.942729898654653</v>
+        <v>-3.663159545304783</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.884720709650761</v>
+        <v>1.996548850990709</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6431592196185381</v>
+        <v>0.6752346032551934</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.867309855379486</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.173244394840242</v>
+        <v>-3.893674041490371</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.859220870767029</v>
+        <v>1.971049012106977</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4126447234329493</v>
+        <v>0.4447201070696046</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.795707117258636</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.429965212835066</v>
+        <v>-4.150394859485196</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.896844262570946</v>
+        <v>2.008672403910894</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.870970091774194</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.583951630611207</v>
+        <v>-4.304381277261337</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.90422996460613</v>
+        <v>2.016058105946078</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.939950360919834</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.533429726783541</v>
+        <v>-4.253859373433671</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.910489928257317</v>
+        <v>2.022318069597265</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.926001563039955</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.785904880791265</v>
+        <v>-4.506334527441395</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.821370355709641</v>
+        <v>1.933198497049589</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.937872052095369</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.078800637270677</v>
+        <v>-4.799230283920807</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.70542258763682</v>
+        <v>1.817250728976768</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.939082586614313</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.265464765405485</v>
+        <v>-4.985894412055615</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.634878678610218</v>
+        <v>1.746706819950166</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2774911784645746</v>
+        <v>0.3095665621012299</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.907915716164905</v>
+        <v>3.927160946346897</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.411485452319448</v>
+        <v>-5.131915098969578</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.571548256580823</v>
+        <v>1.683376397920771</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2684080866707176</v>
+        <v>0.3004834703073729</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.89754371382478</v>
+        <v>3.916788944006774</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.528453144958339</v>
+        <v>-5.248882791608469</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.686965236224311</v>
+        <v>1.798793377564258</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2684080866707176</v>
+        <v>0.3004834703073729</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.059747770523824</v>
+        <v>4.078993000705817</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.613171087179292</v>
+        <v>-5.333600733829422</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.647924697299743</v>
+        <v>1.759752838639691</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1832920577426713</v>
+        <v>0.2153674413793266</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.00352479113081</v>
+        <v>4.022770021312803</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.695105905448175</v>
+        <v>-5.415535552098305</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.625380187560681</v>
+        <v>1.737208328900629</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1733573121555911</v>
+        <v>0.2054326957922464</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.007793361347053</v>
+        <v>4.027038591529046</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.797082027696582</v>
+        <v>-5.517511674346713</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.593515377117221</v>
+        <v>1.705343518457169</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07138118990718351</v>
+        <v>0.1034565735438388</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.955533326453911</v>
+        <v>3.974778556635904</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.687075744219361</v>
+        <v>-5.407505390869491</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.629670777752285</v>
+        <v>1.741498919092233</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09458576182445871</v>
+        <v>0.126661145461114</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.961608956848452</v>
+        <v>3.980854187030445</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.544016168478436</v>
+        <v>-5.264445815128566</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.691144618770629</v>
+        <v>1.802972760110577</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.102599188414438</v>
+        <v>0.1346745720510933</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.970667023524414</v>
+        <v>3.989912253706407</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.242569443006598</v>
+        <v>-4.962999089656728</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.8189841918419</v>
+        <v>1.930812333181848</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4361212975229306</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.158795941690052</v>
+        <v>4.178041171872045</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.267159687241782</v>
+        <v>-4.987589333891912</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.810119271900537</v>
+        <v>1.921947413240485</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4361212975229306</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.159767119442763</v>
+        <v>4.179012349624756</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.216121311235262</v>
+        <v>-4.936550957885392</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.8313775266829</v>
+        <v>1.943205668022848</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4361212975229306</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.160610023822517</v>
+        <v>4.179855254004511</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.174982016368631</v>
+        <v>-4.895411663018761</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.866871343503698</v>
+        <v>1.978699484843646</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4451852087529061</v>
+        <v>0.4772605923895614</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.204331699616642</v>
+        <v>4.223576929798635</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.078347104349991</v>
+        <v>-4.798776751000121</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.721709304435089</v>
+        <v>1.833537445775037</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5418201207715461</v>
+        <v>0.5738955044082013</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.078496642951761</v>
+        <v>4.097741873133753</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.208927838880833</v>
+        <v>-4.929357485530963</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.672979054696715</v>
+        <v>1.784807196036663</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4433147698773587</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.003650246307219</v>
+        <v>4.022895476489212</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.044431504689872</v>
+        <v>-4.764861151340002</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.723204407449183</v>
+        <v>1.835032548789131</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4433147698773587</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.988077065383301</v>
+        <v>4.007322295565294</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.071801437374304</v>
+        <v>-4.792231084024434</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.71144414481184</v>
+        <v>1.823272286151788</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4433147698773587</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.987264775819731</v>
+        <v>4.006510006001724</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.082186632264193</v>
+        <v>-4.802616278914323</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.717158845980956</v>
+        <v>1.828986987320904</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4008541913508142</v>
+        <v>0.4329295749874694</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.99090243801087</v>
+        <v>4.010147668192863</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.100774790986418</v>
+        <v>-4.821204437636548</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.780560588268492</v>
+        <v>1.892388729608439</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3822660326285889</v>
+        <v>0.4143414162652441</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.05058654855396</v>
+        <v>4.069831778735953</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.101073337682454</v>
+        <v>-4.821502984332584</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.777310180408376</v>
+        <v>1.889138321748324</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3822660326285889</v>
+        <v>0.4143414162652441</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.047455559372258</v>
+        <v>4.066700789554251</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.000250203992026</v>
+        <v>-4.720679850642156</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.822170328823938</v>
+        <v>1.933998470163886</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3947302481129427</v>
+        <v>0.4268056317495979</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.059464983602262</v>
+        <v>4.078710213784255</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.809468843239619</v>
+        <v>-4.529898489889749</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.898612126603444</v>
+        <v>2.010440267943392</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.58551160886535</v>
+        <v>0.6175869925020052</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.174063053532249</v>
+        <v>4.193308283714242</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.790951989197799</v>
+        <v>-4.511381635847929</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.885855713957769</v>
+        <v>1.997683855297717</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5984417382905582</v>
+        <v>0.6305171219272134</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.161657976924971</v>
+        <v>4.180903207106964</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.765758804696481</v>
+        <v>-4.486188451346611</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.930899924370355</v>
+        <v>2.042728065710302</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6236349227918766</v>
+        <v>0.6557103064285318</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.21174082423782</v>
+        <v>4.230986054419813</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.753704677783518</v>
+        <v>-4.474134324433648</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.929408143036977</v>
+        <v>2.041236284376925</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6356890497048394</v>
+        <v>0.6677644333414946</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.212659868287036</v>
+        <v>4.231905098469029</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.760327924473876</v>
+        <v>-4.480757571124006</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.92863947454497</v>
+        <v>2.040467615884918</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6290658030144811</v>
+        <v>0.6611411866511363</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.210566550456956</v>
+        <v>4.22981178063895</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.657447334945283</v>
+        <v>-4.377876981595413</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.98264273623429</v>
+        <v>2.094470877574238</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.285145930051995</v>
+        <v>4.304391160233988</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.68088937412537</v>
+        <v>-4.4013190207755</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.993468590735849</v>
+        <v>2.105296732075797</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.305348600225589</v>
+        <v>4.324593830407582</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.698961882416982</v>
+        <v>-4.419391529067112</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.986239587419204</v>
+        <v>2.098067728759152</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.305348600225589</v>
+        <v>4.324593830407582</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.930135676293614</v>
+        <v>-4.650565322943744</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.854021983462018</v>
+        <v>1.965850124801966</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.265600513819056</v>
+        <v>4.284845744001049</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.898849655753159</v>
+        <v>-4.619279302403289</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.87355901067514</v>
+        <v>1.985387152015088</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7632324130835294</v>
+        <v>0.7953077967201846</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.291394745140269</v>
+        <v>4.310639975322262</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.745824263639874</v>
+        <v>-4.466253910290004</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.033940167093358</v>
+        <v>2.145768308433306</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9162578051968135</v>
+        <v>0.9483331888334687</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.482380979981143</v>
+        <v>4.501626210163137</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.774131577513145</v>
+        <v>-4.494561224163275</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.210083466452343</v>
+        <v>2.32191160779229</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9162578051968135</v>
+        <v>0.9483331888334687</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.669847204889436</v>
+        <v>4.689092435071429</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.940724802626667</v>
+        <v>-4.661154449276797</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.112849127761016</v>
+        <v>2.224677269100964</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.7817399637199463</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.539294221175405</v>
+        <v>4.558539451357397</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.767660423244367</v>
+        <v>-4.488090069894497</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.185751282175653</v>
+        <v>2.297579423515602</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.7817399637199463</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.542970623837123</v>
+        <v>4.562215854019115</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.73841444278867</v>
+        <v>-4.4588440894388</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.195067729481427</v>
+        <v>2.306895870821375</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.7817399637199463</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.540588678960618</v>
+        <v>4.559833909142611</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.845339990666521</v>
+        <v>-4.565769637316651</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.149590749487922</v>
+        <v>2.26141889082787</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6427390322054397</v>
+        <v>0.6748144158420949</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.473726589391542</v>
+        <v>4.492971819573535</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.505899308054221</v>
+        <v>3.886228925002293</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.887012744005666</v>
+        <v>-4.817974269198269</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.134350450295498</v>
+        <v>2.161965840218457</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6010662788662946</v>
+        <v>0.4226097839604766</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.45015173953129</v>
+        <v>4.343077842587798</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-45.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.2%</t>
+          <t>427.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.4%</t>
+          <t>-660.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,42 +1155,42 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.0%</t>
+          <t>-167.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-350.2%</t>
+          <t>-329.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-181.7%</t>
+          <t>-174.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.967160419040002</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.329941562892845</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7766563720186828</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.651168331611383</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.153880127349304</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2512273750347207</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7766563720186828</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.64714202707698</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.536881516091936</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09792471821608428</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7766563720186828</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.647039925755396</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.541367961293324</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09870165610695869</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7811428172200714</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.646919574605993</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.900898283797326</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.03976016959659168</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7811428172200714</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.652269877904044</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.951247347251548</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05198377502110274</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8314918806742935</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.629976459788688</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.048866624672945</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.08798973536789267</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9291111580956901</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.574446643957619</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.102938124181303</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1067247788496641</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9831826576040495</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.544897300574175</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.307196299511167</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1829148518629671</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.110821602218038</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.473827130924424</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.340849138019641</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1918934327819204</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.211234970135076</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.418061664658638</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.267379306352192</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1471337986215198</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.137765138467627</v>
+        <v>-1.169840522104282</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.477515265152528</v>
+        <v>2.458270034970535</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.442503723738735</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2026283448286206</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.312889555854171</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.386995835468119</v>
+        <v>2.367750605286126</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.676955817753225</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3036283473360122</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.312889555854171</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.379776670566523</v>
+        <v>2.36053144038453</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.781330548779671</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3520504305205669</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.417264286880617</v>
+        <v>-1.449339670517272</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.310479641176679</v>
+        <v>2.291234410994686</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.943844014478255</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4159400269614446</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.514897717299303</v>
+        <v>-1.546973100935959</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.253015372764023</v>
+        <v>2.23377014258203</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.069880807846545</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4636610156796457</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.489646094489561</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.270860075078983</v>
+        <v>2.25161484489699</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.012809035950614</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4368419712348723</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.489646094489561</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.274850410765384</v>
+        <v>2.255605180583391</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.154480877674734</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4949859348232621</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.489646094489561</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.273375183866643</v>
+        <v>2.254129953684649</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.1048900332499</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4600961868884563</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.440055250064727</v>
+        <v>-1.472130633701382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.318183100686415</v>
+        <v>2.298937870504422</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.955971698778043</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4135799867463965</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.408805659329554</v>
+        <v>-1.440881042966209</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.323881721480836</v>
+        <v>2.304636491298843</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.730126546058631</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3136628526224232</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.36687898374239</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.358616799869343</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.60554788972104</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2626922455313276</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.36687898374239</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.359755944425402</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.658443177765326</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2812165865869343</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.361923637653944</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.365362926240577</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.586310002477445</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2466296122331455</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.361923637653944</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.371096630479213</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.514943609867798</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2278203175831517</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.290557245044296</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.404179203651137</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.421484575882573</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2003201853019694</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.290557245044296</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.39429572233823</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.410831394329142</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1978934731799709</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.290557245044296</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.392461161838856</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.312924355652651</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1590309726828352</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.22257149518374</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.432952296781729</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.288970814676693</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1487810501469586</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.198617954207782</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.447992927512797</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.024910876353896</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05641739097959197</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9345580158849862</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.593168574344722</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839719</v>
+        <v>3.83325274783972</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.317831252849058</v>
+        <v>-7.597401606198926</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2236274247620424</v>
+        <v>0.1117992834220951</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9345580158849862</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.590381540684422</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388723</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.277646954482868</v>
+        <v>-7.557217307832736</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.24004476799636</v>
+        <v>0.1282166266564126</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.8943737175187955</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.614835743591978</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.856161751626469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.114247083543505</v>
+        <v>-7.393817436893373</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3047715375928619</v>
+        <v>0.1929433962529146</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.730973846579433</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.712242487376352</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.880765861313907</v>
+        <v>-7.160336214663775</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4060884553225539</v>
+        <v>0.2942603139826065</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.4974926243498344</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.860255649551963</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.731099470306392</v>
+        <v>-7.01066982365626</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4630628014126006</v>
+        <v>0.3512346600726532</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4045891331072985</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.913105533984526</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.598823996675505</v>
+        <v>-6.878394350025373</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5113404776119821</v>
+        <v>0.3995123362720352</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.2723136594764118</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.987838304910085</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.443085664115763</v>
+        <v>-6.722656017465631</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5764508713235159</v>
+        <v>0.4646227299835686</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1165753269166703</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.084096365133567</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.358120997386443</v>
+        <v>-6.637691350736311</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6233430792389023</v>
+        <v>0.5115149378989554</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.0316106601873507</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.147981506394817</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.463710987159548</v>
+        <v>-6.743281340509416</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4531311537304421</v>
+        <v>0.3413030123904948</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1372006499604551</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.956651582931736</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987897</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.39547640253412</v>
+        <v>-6.675046755883988</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5289693294576994</v>
+        <v>0.417141188117752</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1187853270879191</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.016245118532344</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.247536361126521</v>
+        <v>-6.527106714476389</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4682664233325715</v>
+        <v>0.3564382819926242</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.0984644111793615</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.90855874538931</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.194566838872532</v>
+        <v>-6.4741371922224</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4807402459806887</v>
+        <v>0.3689121046407413</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.931626472488226</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.028778642912242</v>
+        <v>-6.30834899626211</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5400949122697121</v>
+        <v>0.4282667709297647</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.924665860393133</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.995415436433473</v>
+        <v>-6.274985789783341</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5679025492423624</v>
+        <v>0.456074407902415</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.939128214774276</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.887156299310951</v>
+        <v>-6.166726652660819</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6057383245505661</v>
+        <v>0.4939101832106187</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.933660335233471</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.76386516449382</v>
+        <v>-6.043435517843688</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6525528724879956</v>
+        <v>0.5407247311480483</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.07779624589175788</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.005133110134326</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.711168297362529</v>
+        <v>-5.990738650712397</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6813325975778373</v>
+        <v>0.5695044562378899</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1304931130230491</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.044452208650426</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.467402855379085</v>
+        <v>-5.746973208728953</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7746194827182658</v>
+        <v>0.6627913413783184</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1304931130230491</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.040232916997477</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.377627183002613</v>
+        <v>-5.657197536352481</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8126540655888705</v>
+        <v>0.7008259242489232</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1920925579373591</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.079316897866078</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.127776789053538</v>
+        <v>-5.407347142403406</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9053362981522026</v>
+        <v>0.7935081568122553</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1920925579373591</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.07205897284978</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.951884696586106</v>
+        <v>-5.231455049935974</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9792922586598241</v>
+        <v>0.8674641173198769</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1920925579373591</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.075658096370429</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.780438233563642</v>
+        <v>-5.060008586913511</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.061198349923363</v>
+        <v>0.9493702085834159</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3635390209598222</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.191853480238461</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.700415946454521</v>
+        <v>-4.97998629980439</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.092227742383308</v>
+        <v>0.9803996010433611</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4435613080689432</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.23888733012023</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.636780204220587</v>
+        <v>-4.916350557570455</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.1223768403312</v>
+        <v>1.010548698991252</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.5071970503028778</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.281763576514908</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.543082886004192</v>
+        <v>-4.82265323935406</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.141050026401553</v>
+        <v>1.029221885061606</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.5071970503028778</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.262957835298704</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.553585509069481</v>
+        <v>-4.833155862419349</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.138592053800315</v>
+        <v>1.026763912460368</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4966944272375888</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.258399338084408</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.481342940898286</v>
+        <v>-4.760913294248154</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.171418394903613</v>
+        <v>1.059590253563666</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4966944272375888</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.262328651919228</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.463629254020421</v>
+        <v>-4.743199607370289</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.179182453572099</v>
+        <v>1.067354312232152</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4998757561345056</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.264916033174718</v>
+        <v>3.245670802992725</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.354824368540694</v>
+        <v>-4.634394721890562</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.219702478983983</v>
+        <v>1.107874337644036</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4998757561345056</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.261914104394712</v>
+        <v>3.242668874212719</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675932</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.134803570503683</v>
+        <v>-4.414373923853551</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.309289835209402</v>
+        <v>1.197461693869455</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6410956012024859</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.348225048446114</v>
+        <v>3.328979818264121</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539944</v>
+        <v>3.843274527539946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.001935881440405</v>
+        <v>-4.281506234790274</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.378331093636536</v>
+        <v>1.266502952296589</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6410956012024859</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.364119231247937</v>
+        <v>3.344874001065945</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.881762798075906</v>
+        <v>-4.161333151425775</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.427546171422638</v>
+        <v>1.31571803008269</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7612686845669848</v>
+        <v>0.7291933009303296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.437368925706939</v>
+        <v>3.418123695524946</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.746509436745928</v>
+        <v>-4.026079790095798</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.491735618516069</v>
+        <v>1.379907477176121</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8965220458969619</v>
+        <v>0.8644466622603068</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.528609045066365</v>
+        <v>3.509363814884372</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.806384264103621</v>
+        <v>-4.08595461745349</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.453823178974418</v>
+        <v>1.34199503763447</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8366472185392698</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.478721640053176</v>
+        <v>3.459476409871182</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.686564033192783</v>
+        <v>-3.966134386542653</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.517040440572961</v>
+        <v>1.405212299233013</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8366472185392698</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.494010809287384</v>
+        <v>3.474765579105391</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.689033739654589</v>
+        <v>-3.968604093004459</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.42369675731068</v>
+        <v>1.311868615970733</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8341775120774637</v>
+        <v>0.8021021284408085</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.400173184732742</v>
+        <v>3.380927954550749</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.757403925978599</v>
+        <v>-4.036974279328469</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.315610544266378</v>
+        <v>1.20378240292643</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.325000465639772</v>
+        <v>3.305755235457779</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.771191978825646</v>
+        <v>-4.050762332175515</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.30053203175945</v>
+        <v>1.188703890419503</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.315437174271664</v>
+        <v>3.29619194408967</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.826712054718235</v>
+        <v>-4.106282408068105</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.415354838094617</v>
+        <v>1.303526696754669</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.452468010963866</v>
+        <v>3.433222780781873</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.651237794925766</v>
+        <v>-3.930808148275636</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.490111774003392</v>
+        <v>1.378283632663445</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.457035242955654</v>
+        <v>3.43779001277366</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.643313420340852</v>
+        <v>-3.922883773690721</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.469023552598565</v>
+        <v>1.357195411258618</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.432777271716861</v>
+        <v>3.413532041534868</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.60964987486857</v>
+        <v>-3.88922022821844</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.411027284188928</v>
+        <v>1.29919914284898</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8771167565859606</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.38151371240168</v>
+        <v>3.362268482219687</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.549797255664847</v>
+        <v>-3.829367609014716</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.445140718302549</v>
+        <v>1.333312576962602</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8771167565859606</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.391686098833812</v>
+        <v>3.372440868651819</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.463553792638469</v>
+        <v>-3.743124145988339</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.474584374086961</v>
+        <v>1.362756232747013</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8771167565859606</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.386632369407672</v>
+        <v>3.367387139225679</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.508860612037449</v>
+        <v>-3.788430965387318</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.448237421771894</v>
+        <v>1.336409280431947</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8363065935767298</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.353922047046659</v>
+        <v>3.334676816864667</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.537893716739751</v>
+        <v>-3.81746407008962</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.437176052924075</v>
+        <v>1.325347911584128</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8363065935767298</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.354473920079761</v>
+        <v>3.335228689897768</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.445083235288891</v>
+        <v>-3.724653588638761</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.403572937395785</v>
+        <v>1.291744796055837</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9291170750275891</v>
+        <v>0.8970416913909339</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.339432900841642</v>
+        <v>3.320187670659649</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.489472704618319</v>
+        <v>-3.769043057968188</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.387690625588614</v>
+        <v>1.275862484248667</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8847276056981614</v>
+        <v>0.8526522220615063</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.314672695168587</v>
+        <v>3.295427464986593</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.606014309723662</v>
+        <v>-3.885584663073531</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.3361496920582</v>
+        <v>1.224321550718253</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7681860005928187</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.239823440617104</v>
+        <v>3.220578210435111</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.645938404306234</v>
+        <v>-3.925508757656103</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.325671350055839</v>
+        <v>1.213843208715891</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7681860005928187</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.245314736447771</v>
+        <v>3.226069506265778</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.673718802207587</v>
+        <v>-3.953289155557456</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.326056392663836</v>
+        <v>1.214228251323889</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7404056026914656</v>
+        <v>0.7083302190548104</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.240143699475498</v>
+        <v>3.220898469293505</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.792099474937725</v>
+        <v>-4.071669828287594</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.117059843572434</v>
+        <v>1.005231702232487</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6731877505404894</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.038168708185566</v>
+        <v>3.018923478003573</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.900713553381056</v>
+        <v>-4.180283906730925</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.193763872914308</v>
+        <v>1.08193573157436</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6731877505404894</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.158318368904772</v>
+        <v>3.139073138722778</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.865304515132913</v>
+        <v>-4.144874868482782</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.222440514315888</v>
+        <v>1.11061237297594</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6731877505404894</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.172831395007095</v>
+        <v>3.153586164825101</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.826920852574762</v>
+        <v>-4.106491205924631</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.235213420681517</v>
+        <v>1.12338527934157</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7115714130986406</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.193281033884354</v>
+        <v>3.174035803702361</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.649804522539596</v>
+        <v>-3.929374875889465</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.302788981540885</v>
+        <v>1.190960840200938</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7115714130986406</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.190010062729656</v>
+        <v>3.170764832547663</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.694896767373141</v>
+        <v>-3.974467120723011</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.28543547536938</v>
+        <v>1.173607334029433</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6496753699292508</v>
+        <v>0.6175999862925956</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.153555828589935</v>
+        <v>3.134310598407942</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.515521346134374</v>
+        <v>-3.795091699484243</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.350972619171302</v>
+        <v>1.239144477831354</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8064521280999695</v>
+        <v>0.7743767444633143</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.24140885879878</v>
+        <v>3.222163628616787</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.56053555965498</v>
+        <v>-3.840105913004849</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.313774389094649</v>
+        <v>1.201946247754701</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7761032327853649</v>
+        <v>0.7440278491487097</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.204006976941607</v>
+        <v>3.184761746759615</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.827540069927415</v>
+        <v>-4.107110423277285</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.21266414732462</v>
+        <v>1.100836005984673</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5817401947424163</v>
+        <v>0.5496648111057612</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.093080716454784</v>
+        <v>3.073835486272791</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.928737851364588</v>
+        <v>-4.208308204714458</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.171388956646253</v>
+        <v>1.059560815306305</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5133313811970972</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.051239350224094</v>
+        <v>3.031994120042101</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.922226884750275</v>
+        <v>-4.201797238100145</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.171593304846295</v>
+        <v>1.059765163506347</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5133313811970972</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.048839311778411</v>
+        <v>3.029594081596418</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.903188757042978</v>
+        <v>-4.182759110392848</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.175733275137459</v>
+        <v>1.063905133797511</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4551477698659027</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.010453864187939</v>
+        <v>2.991208634005946</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.955704559317798</v>
+        <v>-4.235274912667668</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.274021355861721</v>
+        <v>1.162193214521773</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4551477698659027</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.129748265822129</v>
+        <v>3.110503035640136</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.969571320651716</v>
+        <v>-4.249141674001586</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.269307980314287</v>
+        <v>1.157479838974339</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4172898531320797</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.107866844767969</v>
+        <v>3.088621614585976</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.924767149111786</v>
+        <v>-4.204337502461656</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.293238179327185</v>
+        <v>1.181410037987237</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4172898531320797</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.113875375164895</v>
+        <v>3.094630144982902</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.777024178876784</v>
+        <v>-4.056594532226653</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.250285588698386</v>
+        <v>1.138457447358438</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5850972103669629</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.112510010783025</v>
+        <v>3.093264780601031</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.860845400151482</v>
+        <v>-4.140415753501352</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.219550721719987</v>
+        <v>1.107722580380039</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5850972103669629</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.115303632314506</v>
+        <v>3.096058402132512</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.854692694098697</v>
+        <v>-4.134263047448568</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.22267415253276</v>
+        <v>1.110846011192812</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5912499164197472</v>
+        <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.119657604337835</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.871501992249199</v>
+        <v>-4.151072345599069</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.215030910012669</v>
+        <v>1.103202768672721</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5744406182692456</v>
+        <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.108652502187644</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.809203993473077</v>
+        <v>-4.088774346822947</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.306285663319939</v>
+        <v>1.194457521979991</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6197348825436877</v>
+        <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.20216461454913</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.607413795807919</v>
+        <v>-3.886984149157789</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.189293744100129</v>
+        <v>1.077465602760181</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8177530747128421</v>
+        <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.12326753156475</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.658300508494114</v>
+        <v>-3.937870861843984</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.239229291347826</v>
+        <v>1.127401150007878</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7668663620266476</v>
+        <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.163025736275208</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.571689765844306</v>
+        <v>-3.851260119194177</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.288501324523793</v>
+        <v>1.176673183183845</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8454920932318059</v>
+        <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.224828911114347</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.631899063849591</v>
+        <v>-3.911469417199461</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.262953586146351</v>
+        <v>1.151125444806403</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7852827952265213</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.187239313135848</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.555477017417664</v>
+        <v>-3.835047370767534</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.29201402275905</v>
+        <v>1.180185881419102</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7852827952265213</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.185730931175776</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.511103885779095</v>
+        <v>-3.790674239128966</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.309626142849914</v>
+        <v>1.197798001509966</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8296559268650899</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.212217677594353</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.53358423663798</v>
+        <v>-3.813154589987851</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.29502779664495</v>
+        <v>1.183199655305002</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8296559268650899</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.206611471732944</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.485928506076924</v>
+        <v>-3.765498859426795</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.320471845897177</v>
+        <v>1.208643704557229</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8773116574261456</v>
+        <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.241586667097382</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.38541034757817</v>
+        <v>-3.66498070092804</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.365571482671404</v>
+        <v>1.253743341331456</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9778298159249001</v>
+        <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.30678993557136</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.369505018145817</v>
+        <v>-3.649075371495687</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.358688286920217</v>
+        <v>1.246860145580269</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8987171552156612</v>
+        <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.246077011621689</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.324666616537419</v>
+        <v>-3.604236969887289</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.380721350174205</v>
+        <v>1.268893208834257</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9032605881605307</v>
+        <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.252900773999239</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.344165072779427</v>
+        <v>-3.623735426129298</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.37708290730848</v>
+        <v>1.265254765968532</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8551759468806264</v>
+        <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.228210928862374</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.299962235693527</v>
+        <v>-3.579532589043397</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.400643644670677</v>
+        <v>1.288815503330729</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8993787839665268</v>
+        <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.260612233641751</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.307521901530574</v>
+        <v>-3.587092254880444</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.396029778805106</v>
+        <v>1.284201637465158</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9541821879763461</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.291904276516891</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.149230483991301</v>
+        <v>-3.428800837341172</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.510594111003854</v>
+        <v>1.398765969663907</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9541821879763461</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.343152041699931</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.941588480356825</v>
+        <v>-3.221158833706696</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.592091617051898</v>
+        <v>1.48026347571195</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.161824191610822</v>
+        <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.466177948474869</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.890556387634297</v>
+        <v>-3.170126740984168</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.607452682379179</v>
+        <v>1.495624541039231</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.21285628433335</v>
+        <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.491745432346656</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.825332206507091</v>
+        <v>-3.104902559856962</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.650729758922767</v>
+        <v>1.538901617582819</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.278080465460556</v>
+        <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.548067345115684</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.787905186435958</v>
+        <v>-3.067475539785828</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.661661539250501</v>
+        <v>1.549833397910553</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.283332003489738</v>
+        <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.547179240232474</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.808016842470666</v>
+        <v>-3.087587195820536</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.654873669167857</v>
+        <v>1.543045527827909</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.294359348487157</v>
+        <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.555052439562166</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.754272028043461</v>
+        <v>-3.033842381393332</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.83692936595995</v>
+        <v>1.725101224620002</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.304422657927619</v>
+        <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.721648196247653</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.679489767018449</v>
+        <v>-2.959060120368319</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.986955179587772</v>
+        <v>1.875127038247824</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.379204918952631</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.886630462080478</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.653405682754641</v>
+        <v>-2.932976036104511</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.989096789307155</v>
+        <v>1.877268647967206</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.379204918952631</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.878338438094337</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.56552776964552</v>
+        <v>-2.84509812299539</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.022441150134582</v>
+        <v>1.910613008794634</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.495130561375983</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.946087019132127</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959861</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.556635308252237</v>
+        <v>-2.836205661602107</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.043552540418687</v>
+        <v>1.931724399078739</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.495130561375983</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.963641424858919</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.725111425222114</v>
+        <v>-3.004681778571985</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.96801714103532</v>
+        <v>1.856188999695372</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.467182725659402</v>
+        <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.938727770833554</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782712</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.278855232592675</v>
+        <v>-2.558425585942545</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.127789315274958</v>
+        <v>2.015961173935009</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.372464055989769</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.863166266219637</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.78467134563264</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.256134128909522</v>
+        <v>-2.535704482259392</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.127541779245123</v>
+        <v>2.015713637905175</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.372464055989769</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.853830288716541</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.385335942203564</v>
+        <v>-2.664906295553435</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.234767179778675</v>
+        <v>2.122939038438727</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.243262242695727</v>
+        <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.935215326591285</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644416</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.54011694898182</v>
+        <v>-2.81968730233169</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.20993259956102</v>
+        <v>2.098104458221071</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.209894568641251</v>
+        <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.952272544652246</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.533062258766646</v>
+        <v>-2.812632612116517</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.209429831636634</v>
+        <v>2.097601690296686</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.216949258856425</v>
+        <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.953180714770895</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331119</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.506111034440158</v>
+        <v>-2.785681387790029</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.230216475011971</v>
+        <v>2.118388333672023</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.231829604884144</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.972115076032268</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.642064042496475</v>
+        <v>-2.921634395846345</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.359938403934404</v>
+        <v>2.248110262594456</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.231829604884144</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.156218208177227</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.664472160301347</v>
+        <v>-2.944042513651217</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.343091851715449</v>
+        <v>2.2312637103755</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.231829604884144</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.148334903080221</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155036</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.692696395878947</v>
+        <v>-2.972266749228818</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.333856157034046</v>
+        <v>2.222028015694097</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.249806357335452</v>
+        <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.161174954100644</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.702137321767477</v>
+        <v>-2.981707675117347</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.386333504400481</v>
+        <v>2.274505363060533</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.372233474878844</v>
+        <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.290884942348526</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.754410929103118</v>
+        <v>-3.033981282452989</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.368315156011525</v>
+        <v>2.256487014671577</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.319959867543202</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.262411872492442</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.830740906704024</v>
+        <v>-3.110311260053895</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.335894977864938</v>
+        <v>2.22406683652499</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.319959867543202</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.260523685386217</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.032994627028378</v>
+        <v>-3.312564980378248</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.249813719338059</v>
+        <v>2.137985577998111</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.117706147218849</v>
+        <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.133991682794467</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.71289761234307</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.194563052555633</v>
+        <v>-3.474133405905503</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.183620359337309</v>
+        <v>2.071792217997361</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9909232234209697</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.056355938725892</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389353</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.326864344653186</v>
+        <v>-3.606434698003056</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.143773249364207</v>
+        <v>2.031945108024258</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9909232234209697</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.069429345591811</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378397</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.512732655492416</v>
+        <v>-3.792303008842286</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.061431121811454</v>
+        <v>1.949602980471506</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.832357630101022</v>
+        <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.966295186382782</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006979</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.540633442601889</v>
+        <v>-3.820203795951759</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.048794848094667</v>
+        <v>1.93696670675472</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7977607059580872</v>
+        <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.944061073024023</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787391</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.663159545304783</v>
+        <v>-3.942729898654653</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.996548850990709</v>
+        <v>1.884720709650761</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6752346032551934</v>
+        <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.867309855379486</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585942</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.893674041490371</v>
+        <v>-4.173244394840242</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.971049012106977</v>
+        <v>1.859220870767029</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4447201070696046</v>
+        <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.795707117258636</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814669</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.150394859485196</v>
+        <v>-4.429965212835066</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.008672403910894</v>
+        <v>1.896844262570946</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.870970091774194</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.304381277261337</v>
+        <v>-4.583951630611207</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.016058105946078</v>
+        <v>1.90422996460613</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.939950360919834</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423391</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.253859373433671</v>
+        <v>-4.533429726783541</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.022318069597265</v>
+        <v>1.910489928257317</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.926001563039955</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609757</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.506334527441395</v>
+        <v>-4.785904880791265</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.933198497049589</v>
+        <v>1.821370355709641</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.937872052095369</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.799230283920807</v>
+        <v>-5.078800637270677</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.817250728976768</v>
+        <v>1.70542258763682</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.939082586614313</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.985894412055615</v>
+        <v>-5.265464765405485</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.746706819950166</v>
+        <v>1.634878678610218</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3095665621012299</v>
+        <v>0.2774911784645746</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.927160946346897</v>
+        <v>3.907915716164905</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.131915098969578</v>
+        <v>-5.411485452319448</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.683376397920771</v>
+        <v>1.571548256580823</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3004834703073729</v>
+        <v>0.2684080866707176</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.916788944006774</v>
+        <v>3.89754371382478</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.248882791608469</v>
+        <v>-5.528453144958339</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.798793377564258</v>
+        <v>1.686965236224311</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3004834703073729</v>
+        <v>0.2684080866707176</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.078993000705817</v>
+        <v>4.059747770523824</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.333600733829422</v>
+        <v>-5.613171087179292</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759752838639691</v>
+        <v>1.647924697299743</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2153674413793266</v>
+        <v>0.1832920577426713</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.022770021312803</v>
+        <v>4.00352479113081</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.415535552098305</v>
+        <v>-5.695105905448175</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.737208328900629</v>
+        <v>1.625380187560681</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2054326957922464</v>
+        <v>0.1733573121555911</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.027038591529046</v>
+        <v>4.007793361347053</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.517511674346713</v>
+        <v>-5.797082027696582</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.705343518457169</v>
+        <v>1.593515377117221</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1034565735438388</v>
+        <v>0.07138118990718351</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.974778556635904</v>
+        <v>3.955533326453911</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.407505390869491</v>
+        <v>-5.687075744219361</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741498919092233</v>
+        <v>1.629670777752285</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.126661145461114</v>
+        <v>0.09458576182445871</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.980854187030445</v>
+        <v>3.961608956848452</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818525</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.264445815128566</v>
+        <v>-5.544016168478436</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802972760110577</v>
+        <v>1.691144618770629</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1346745720510933</v>
+        <v>0.102599188414438</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.989912253706407</v>
+        <v>3.970667023524414</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.962999089656728</v>
+        <v>-5.242569443006598</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.930812333181848</v>
+        <v>1.8189841918419</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4361212975229306</v>
+        <v>0.4040459138862753</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.178041171872045</v>
+        <v>4.158795941690052</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679627</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.987589333891912</v>
+        <v>-5.267159687241782</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.921947413240485</v>
+        <v>1.810119271900537</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4361212975229306</v>
+        <v>0.4040459138862753</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.179012349624756</v>
+        <v>4.159767119442763</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474162</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.936550957885392</v>
+        <v>-5.216121311235262</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.943205668022848</v>
+        <v>1.8313775266829</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4361212975229306</v>
+        <v>0.4040459138862753</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.179855254004511</v>
+        <v>4.160610023822517</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.895411663018761</v>
+        <v>-5.174982016368631</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978699484843646</v>
+        <v>1.866871343503698</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4772605923895614</v>
+        <v>0.4451852087529061</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.223576929798635</v>
+        <v>4.204331699616642</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700481</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.798776751000121</v>
+        <v>-5.078347104349991</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833537445775037</v>
+        <v>1.721709304435089</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5738955044082013</v>
+        <v>0.5418201207715461</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.097741873133753</v>
+        <v>4.078496642951761</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.929357485530963</v>
+        <v>-5.208927838880833</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784807196036663</v>
+        <v>1.672979054696715</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4433147698773587</v>
+        <v>0.4112393862407036</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.022895476489212</v>
+        <v>4.003650246307219</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.764861151340002</v>
+        <v>-5.044431504689872</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.835032548789131</v>
+        <v>1.723204407449183</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4433147698773587</v>
+        <v>0.4112393862407036</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.007322295565294</v>
+        <v>3.988077065383301</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077631</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.792231084024434</v>
+        <v>-5.071801437374304</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.823272286151788</v>
+        <v>1.71144414481184</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4433147698773587</v>
+        <v>0.4112393862407036</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.006510006001724</v>
+        <v>3.987264775819731</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.802616278914323</v>
+        <v>-5.082186632264193</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.828986987320904</v>
+        <v>1.717158845980956</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4329295749874694</v>
+        <v>0.4008541913508142</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.010147668192863</v>
+        <v>3.99090243801087</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735284</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.821204437636548</v>
+        <v>-5.100774790986418</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.892388729608439</v>
+        <v>1.780560588268492</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4143414162652441</v>
+        <v>0.3822660326285889</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.069831778735953</v>
+        <v>4.05058654855396</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.821502984332584</v>
+        <v>-5.101073337682454</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.889138321748324</v>
+        <v>1.777310180408376</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4143414162652441</v>
+        <v>0.3822660326285889</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.066700789554251</v>
+        <v>4.047455559372258</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108859</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.720679850642156</v>
+        <v>-5.000250203992026</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.933998470163886</v>
+        <v>1.822170328823938</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4268056317495979</v>
+        <v>0.3947302481129427</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.078710213784255</v>
+        <v>4.059464983602262</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.529898489889749</v>
+        <v>-4.809468843239619</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.010440267943392</v>
+        <v>1.898612126603444</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6175869925020052</v>
+        <v>0.58551160886535</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.193308283714242</v>
+        <v>4.174063053532249</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.511381635847929</v>
+        <v>-4.790951989197799</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.997683855297717</v>
+        <v>1.885855713957769</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6305171219272134</v>
+        <v>0.5984417382905582</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.180903207106964</v>
+        <v>4.161657976924971</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912988</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.486188451346611</v>
+        <v>-4.765758804696481</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.042728065710302</v>
+        <v>1.930899924370355</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6557103064285318</v>
+        <v>0.6236349227918766</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.230986054419813</v>
+        <v>4.21174082423782</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539897</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.474134324433648</v>
+        <v>-4.753704677783518</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.041236284376925</v>
+        <v>1.929408143036977</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6677644333414946</v>
+        <v>0.6356890497048394</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.231905098469029</v>
+        <v>4.212659868287036</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.480757571124006</v>
+        <v>-4.760327924473876</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.040467615884918</v>
+        <v>1.92863947454497</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6611411866511363</v>
+        <v>0.6290658030144811</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.22981178063895</v>
+        <v>4.210566550456956</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.377876981595413</v>
+        <v>-4.657447334945283</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.094470877574238</v>
+        <v>1.98264273623429</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.304391160233988</v>
+        <v>4.285145930051995</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760318</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.4013190207755</v>
+        <v>-4.68088937412537</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.105296732075797</v>
+        <v>1.993468590735849</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.324593830407582</v>
+        <v>4.305348600225589</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781709</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.419391529067112</v>
+        <v>-4.698961882416982</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.098067728759152</v>
+        <v>1.986239587419204</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.324593830407582</v>
+        <v>4.305348600225589</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082838</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.650565322943744</v>
+        <v>-4.930135676293614</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.965850124801966</v>
+        <v>1.854021983462018</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.284845744001049</v>
+        <v>4.265600513819056</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.619279302403289</v>
+        <v>-4.898849655753159</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.985387152015088</v>
+        <v>1.87355901067514</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7953077967201846</v>
+        <v>0.7632324130835294</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.310639975322262</v>
+        <v>4.291394745140269</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.466253910290004</v>
+        <v>-4.745824263639874</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.145768308433306</v>
+        <v>2.033940167093358</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9483331888334687</v>
+        <v>0.9162578051968135</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.501626210163137</v>
+        <v>4.482380979981143</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.494561224163275</v>
+        <v>-4.774131577513145</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.32191160779229</v>
+        <v>2.210083466452343</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9483331888334687</v>
+        <v>0.9162578051968135</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.689092435071429</v>
+        <v>4.669847204889436</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.661154449276797</v>
+        <v>-4.940724802626667</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.224677269100964</v>
+        <v>2.112849127761016</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7817399637199463</v>
+        <v>0.7496645800832911</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.558539451357397</v>
+        <v>4.539294221175405</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568386</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.488090069894497</v>
+        <v>-4.767660423244367</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.297579423515602</v>
+        <v>2.185751282175653</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7817399637199463</v>
+        <v>0.7496645800832911</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.562215854019115</v>
+        <v>4.542970623837123</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682208</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.4588440894388</v>
+        <v>-4.73841444278867</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.306895870821375</v>
+        <v>2.195067729481427</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7817399637199463</v>
+        <v>0.7496645800832911</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.559833909142611</v>
+        <v>4.540588678960618</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539111</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.565769637316651</v>
+        <v>-4.845339990666521</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.26141889082787</v>
+        <v>2.149590749487922</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6748144158420949</v>
+        <v>0.6427390322054397</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.492971819573535</v>
+        <v>4.473726589391542</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.886228925002293</v>
+        <v>3.505899308054224</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.817974269198269</v>
+        <v>-4.992226622453786</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.161965840218457</v>
+        <v>2.09226489891625</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4226097839604766</v>
+        <v>0.4958524004181749</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.343077842587798</v>
+        <v>4.387023412462417</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.3%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.5%</t>
+          <t>430.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.8%</t>
+          <t>-632.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-155.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-349.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.4%</t>
+          <t>-171.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-6.967160419040002</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.329941562892845</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7766563720186828</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.651168331611383</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.153880127349304</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.2512273750347207</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7766563720186828</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.64714202707698</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.536881516091936</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>0.09792471821608428</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7766563720186828</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.647039925755396</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.541367961293324</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>0.09870165610695869</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7811428172200714</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.646919574605993</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-7.900898283797326</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.03976016959659168</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7811428172200714</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.652269877904044</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-7.951247347251548</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.05198377502110274</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-0.8314918806742935</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.629976459788688</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.048866624672945</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.08798973536789267</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-0.9291111580956901</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.574446643957619</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.102938124181303</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.1067247788496641</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-0.9831826576040495</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.544897300574175</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.307196299511167</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.1829148518629671</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.110821602218038</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.473827130924424</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.340849138019641</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.1918934327819204</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.211234970135076</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.418061664658638</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.267379306352192</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1471337986215198</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.137765138467627</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.477515265152528</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.442503723738735</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.2026283448286206</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.312889555854171</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.386995835468119</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.676955817753225</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.3036283473360122</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.312889555854171</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.379776670566523</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.781330548779671</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.3520504305205669</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.417264286880617</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.310479641176679</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-8.943844014478255</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.4159400269614446</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.514897717299303</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.253015372764023</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.069880807846545</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.4636610156796457</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489646094489561</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.270860075078983</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.012809035950614</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4368419712348723</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489646094489561</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.274850410765384</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.154480877674734</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.4949859348232621</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.489646094489561</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.273375183866643</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.1048900332499</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.4600961868884563</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.440055250064727</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.318183100686415</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-8.955971698778043</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4135799867463965</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.408805659329554</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.323881721480836</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.730126546058631</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.3136628526224232</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.36687898374239</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.358616799869343</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.60554788972104</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.2626922455313276</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.36687898374239</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.359755944425402</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.658443177765326</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.2812165865869343</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.361923637653944</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.365362926240577</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.586310002477445</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2466296122331455</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.361923637653944</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.371096630479213</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.514943609867798</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2278203175831517</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.290557245044296</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.404179203651137</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.421484575882573</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.2003201853019694</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.290557245044296</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.39429572233823</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.410831394329142</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.1978934731799709</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.290557245044296</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.392461161838856</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.312924355652651</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.1590309726828352</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.22257149518374</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.432952296781729</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.288970814676693</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1487810501469586</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.198617954207782</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.447992927512797</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.024910876353896</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.05641739097959197</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9345580158849862</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.593168574344722</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.597401606198926</v>
+        <v>-7.317831252849058</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1117992834220951</v>
+        <v>0.2236274247620424</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9345580158849862</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.590381540684422</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.557217307832736</v>
+        <v>-7.277646954482868</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1282166266564126</v>
+        <v>0.24004476799636</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.8943737175187955</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.614835743591978</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.393817436893373</v>
+        <v>-7.114247083543505</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1929433962529146</v>
+        <v>0.3047715375928619</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.730973846579433</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.712242487376352</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.160336214663775</v>
+        <v>-6.880765861313907</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2942603139826065</v>
+        <v>0.4060884553225539</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.4974926243498344</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.860255649551963</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.01066982365626</v>
+        <v>-6.731099470306392</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3512346600726532</v>
+        <v>0.4630628014126006</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.4045891331072985</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.913105533984526</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.878394350025373</v>
+        <v>-6.598823996675505</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3995123362720352</v>
+        <v>0.5113404776119821</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.2723136594764118</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.987838304910085</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.722656017465631</v>
+        <v>-6.443085664115763</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4646227299835686</v>
+        <v>0.5764508713235159</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.1165753269166703</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.084096365133567</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.637691350736311</v>
+        <v>-6.358120997386443</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5115149378989554</v>
+        <v>0.6233430792389023</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.0316106601873507</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.147981506394817</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.743281340509416</v>
+        <v>-6.463710987159548</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3413030123904948</v>
+        <v>0.4531311537304421</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.1372006499604551</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.956651582931736</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.675046755883988</v>
+        <v>-6.39547640253412</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.417141188117752</v>
+        <v>0.5289693294576994</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.1187853270879191</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>3.016245118532344</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.527106714476389</v>
+        <v>-6.247536361126521</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3564382819926242</v>
+        <v>0.4682664233325715</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.0984644111793615</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.90855874538931</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.4741371922224</v>
+        <v>-6.194566838872532</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3689121046407413</v>
+        <v>0.4807402459806887</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.931626472488226</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.30834899626211</v>
+        <v>-6.028778642912242</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4282667709297647</v>
+        <v>0.5400949122697121</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.924665860393133</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.274985789783341</v>
+        <v>-5.995415436433473</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.456074407902415</v>
+        <v>0.5679025492423624</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.939128214774276</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.166726652660819</v>
+        <v>-5.887156299310951</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4939101832106187</v>
+        <v>0.6057383245505661</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.04549488892537262</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.933660335233471</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.043435517843688</v>
+        <v>-5.76386516449382</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5407247311480483</v>
+        <v>0.6525528724879956</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.07779624589175788</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>3.005133110134326</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.990738650712397</v>
+        <v>-5.711168297362529</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5695044562378899</v>
+        <v>0.6813325975778373</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1304931130230491</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>3.044452208650426</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.746973208728953</v>
+        <v>-5.467402855379085</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6627913413783184</v>
+        <v>0.7746194827182658</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1304931130230491</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>3.040232916997477</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.657197536352481</v>
+        <v>-5.377627183002613</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7008259242489232</v>
+        <v>0.8126540655888705</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920925579373591</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.079316897866078</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.407347142403406</v>
+        <v>-5.127776789053538</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7935081568122553</v>
+        <v>0.9053362981522026</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920925579373591</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.07205897284978</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.231455049935974</v>
+        <v>-4.951884696586106</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8674641173198769</v>
+        <v>0.9792922586598241</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1920925579373591</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.075658096370429</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.060008586913511</v>
+        <v>-4.780438233563642</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9493702085834159</v>
+        <v>1.061198349923363</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.3635390209598222</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.191853480238461</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.97998629980439</v>
+        <v>-4.700415946454521</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9803996010433611</v>
+        <v>1.092227742383308</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.4435613080689432</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.23888733012023</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.916350557570455</v>
+        <v>-4.636780204220587</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.010548698991252</v>
+        <v>1.1223768403312</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.5071970503028778</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.281763576514908</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.82265323935406</v>
+        <v>-4.543082886004192</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.029221885061606</v>
+        <v>1.141050026401553</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.5071970503028778</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.262957835298704</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.833155862419349</v>
+        <v>-4.553585509069481</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.026763912460368</v>
+        <v>1.138592053800315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4966944272375888</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.258399338084408</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.760913294248154</v>
+        <v>-4.481342940898286</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.059590253563666</v>
+        <v>1.171418394903613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4966944272375888</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.262328651919228</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.743199607370289</v>
+        <v>-4.463629254020421</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.067354312232152</v>
+        <v>1.179182453572099</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4998757561345056</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.264916033174718</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.634394721890562</v>
+        <v>-4.354824368540694</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.107874337644036</v>
+        <v>1.219702478983983</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4998757561345056</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.261914104394712</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.414373923853551</v>
+        <v>-4.134803570503683</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.197461693869455</v>
+        <v>1.309289835209402</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6410956012024859</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.348225048446114</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.281506234790274</v>
+        <v>-4.001935881440405</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.266502952296589</v>
+        <v>1.378331093636536</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6410956012024859</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.364119231247937</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.161333151425775</v>
+        <v>-3.881762798075906</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.31571803008269</v>
+        <v>1.427546171422638</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.7612686845669848</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.437368925706939</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.026079790095798</v>
+        <v>-3.746509436745928</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.379907477176121</v>
+        <v>1.491735618516069</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.8965220458969619</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.528609045066365</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.08595461745349</v>
+        <v>-3.806384264103621</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.34199503763447</v>
+        <v>1.453823178974418</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.8366472185392698</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.478721640053176</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.966134386542653</v>
+        <v>-3.686564033192783</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.405212299233013</v>
+        <v>1.517040440572961</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.8366472185392698</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.494010809287384</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.968604093004459</v>
+        <v>-3.689033739654589</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.311868615970733</v>
+        <v>1.42369675731068</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.8341775120774637</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.400173184732742</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.036974279328469</v>
+        <v>-3.757403925978599</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.20378240292643</v>
+        <v>1.315610544266378</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.325000465639772</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.050762332175515</v>
+        <v>-3.771191978825646</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.188703890419503</v>
+        <v>1.30053203175945</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.315437174271664</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.106282408068105</v>
+        <v>-3.826712054718235</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.303526696754669</v>
+        <v>1.415354838094617</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.452468010963866</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.930808148275636</v>
+        <v>-3.651237794925766</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.378283632663445</v>
+        <v>1.490111774003392</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.457035242955654</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.922883773690721</v>
+        <v>-3.643313420340852</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.357195411258618</v>
+        <v>1.469023552598565</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8434532111136787</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.432777271716861</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.88922022821844</v>
+        <v>-3.60964987486857</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.29919914284898</v>
+        <v>1.411027284188928</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8771167565859606</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.362268482219687</v>
+        <v>3.38151371240168</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.829367609014716</v>
+        <v>-3.549797255664847</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.333312576962602</v>
+        <v>1.445140718302549</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8771167565859606</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.372440868651819</v>
+        <v>3.391686098833812</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.743124145988339</v>
+        <v>-3.463553792638469</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.362756232747013</v>
+        <v>1.474584374086961</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.8771167565859606</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.367387139225679</v>
+        <v>3.386632369407672</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.788430965387318</v>
+        <v>-3.508860612037449</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.336409280431947</v>
+        <v>1.448237421771894</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8363065935767298</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.334676816864667</v>
+        <v>3.353922047046659</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.81746407008962</v>
+        <v>-3.537893716739751</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.325347911584128</v>
+        <v>1.437176052924075</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8363065935767298</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.335228689897768</v>
+        <v>3.354473920079761</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.724653588638761</v>
+        <v>-3.445083235288891</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.291744796055837</v>
+        <v>1.403572937395785</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8970416913909339</v>
+        <v>0.9291170750275891</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.320187670659649</v>
+        <v>3.339432900841642</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.769043057968188</v>
+        <v>-3.489472704618319</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.275862484248667</v>
+        <v>1.387690625588614</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8526522220615063</v>
+        <v>0.8847276056981614</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.295427464986593</v>
+        <v>3.314672695168587</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.885584663073531</v>
+        <v>-3.606014309723662</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.224321550718253</v>
+        <v>1.3361496920582</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.7681860005928187</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220578210435111</v>
+        <v>3.239823440617104</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.925508757656103</v>
+        <v>-3.645938404306234</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.213843208715891</v>
+        <v>1.325671350055839</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.7681860005928187</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.226069506265778</v>
+        <v>3.245314736447771</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.953289155557456</v>
+        <v>-3.673718802207587</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.214228251323889</v>
+        <v>1.326056392663836</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7083302190548104</v>
+        <v>0.7404056026914656</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220898469293505</v>
+        <v>3.240143699475498</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.071669828287594</v>
+        <v>-3.792099474937725</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.005231702232487</v>
+        <v>1.117059843572434</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6731877505404894</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018923478003573</v>
+        <v>3.038168708185566</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.180283906730925</v>
+        <v>-3.900713553381056</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.08193573157436</v>
+        <v>1.193763872914308</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6731877505404894</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.139073138722778</v>
+        <v>3.158318368904772</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.144874868482782</v>
+        <v>-3.865304515132913</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.11061237297594</v>
+        <v>1.222440514315888</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.6731877505404894</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153586164825101</v>
+        <v>3.172831395007095</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.106491205924631</v>
+        <v>-3.826920852574762</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.12338527934157</v>
+        <v>1.235213420681517</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7115714130986406</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.174035803702361</v>
+        <v>3.193281033884354</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.929374875889465</v>
+        <v>-3.649804522539596</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.190960840200938</v>
+        <v>1.302788981540885</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7115714130986406</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170764832547663</v>
+        <v>3.190010062729656</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.974467120723011</v>
+        <v>-3.694896767373141</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.173607334029433</v>
+        <v>1.28543547536938</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6175999862925956</v>
+        <v>0.6496753699292508</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134310598407942</v>
+        <v>3.153555828589935</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.795091699484243</v>
+        <v>-3.515521346134374</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.239144477831354</v>
+        <v>1.350972619171302</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7743767444633143</v>
+        <v>0.8064521280999695</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.222163628616787</v>
+        <v>3.24140885879878</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.840105913004849</v>
+        <v>-3.56053555965498</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.201946247754701</v>
+        <v>1.313774389094649</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7440278491487097</v>
+        <v>0.7761032327853649</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.184761746759615</v>
+        <v>3.204006976941607</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.107110423277285</v>
+        <v>-3.827540069927415</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.100836005984673</v>
+        <v>1.21266414732462</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5496648111057612</v>
+        <v>0.5817401947424163</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073835486272791</v>
+        <v>3.093080716454784</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.208308204714458</v>
+        <v>-3.928737851364588</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.059560815306305</v>
+        <v>1.171388956646253</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.481255997560442</v>
+        <v>0.5133313811970972</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031994120042101</v>
+        <v>3.051239350224094</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.201797238100145</v>
+        <v>-3.922226884750275</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.059765163506347</v>
+        <v>1.171593304846295</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.481255997560442</v>
+        <v>0.5133313811970972</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029594081596418</v>
+        <v>3.048839311778411</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.182759110392848</v>
+        <v>-3.903188757042978</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.063905133797511</v>
+        <v>1.175733275137459</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.4551477698659027</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.991208634005946</v>
+        <v>3.010453864187939</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.235274912667668</v>
+        <v>-3.955704559317798</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.162193214521773</v>
+        <v>1.274021355861721</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.4551477698659027</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.110503035640136</v>
+        <v>3.129748265822129</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.249141674001586</v>
+        <v>-3.969571320651716</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.157479838974339</v>
+        <v>1.269307980314287</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.4172898531320797</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088621614585976</v>
+        <v>3.107866844767969</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.204337502461656</v>
+        <v>-3.924767149111786</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.181410037987237</v>
+        <v>1.293238179327185</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.4172898531320797</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094630144982902</v>
+        <v>3.113875375164895</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.056594532226653</v>
+        <v>-3.777024178876784</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.138457447358438</v>
+        <v>1.250285588698386</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.5850972103669629</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.093264780601031</v>
+        <v>3.112510010783025</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.140415753501352</v>
+        <v>-3.860845400151482</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.107722580380039</v>
+        <v>1.219550721719987</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.5850972103669629</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.115303632314506</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.134263047448568</v>
+        <v>-3.854692694098697</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.110846011192812</v>
+        <v>1.22267415253276</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5591745327830919</v>
+        <v>0.5912499164197472</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.119657604337835</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.151072345599069</v>
+        <v>-3.871501992249199</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.103202768672721</v>
+        <v>1.215030910012669</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5423652346325902</v>
+        <v>0.5744406182692456</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.108652502187644</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.088774346822947</v>
+        <v>-3.809203993473077</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.194457521979991</v>
+        <v>1.306285663319939</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5876594989070323</v>
+        <v>0.6197348825436877</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.20216461454913</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.886984149157789</v>
+        <v>-3.607413795807919</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.077465602760181</v>
+        <v>1.189293744100129</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7856776910761867</v>
+        <v>0.8177530747128421</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.12326753156475</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.937870861843984</v>
+        <v>-3.658300508494114</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.127401150007878</v>
+        <v>1.239229291347826</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7347909783899922</v>
+        <v>0.7668663620266476</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.163025736275208</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.851260119194177</v>
+        <v>-3.571689765844306</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.176673183183845</v>
+        <v>1.288501324523793</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8134167095951504</v>
+        <v>0.8454920932318059</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.224828911114347</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.911469417199461</v>
+        <v>-3.631899063849591</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.151125444806403</v>
+        <v>1.262953586146351</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.7852827952265213</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.187239313135848</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.835047370767534</v>
+        <v>-3.555477017417664</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.180185881419102</v>
+        <v>1.29201402275905</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.7852827952265213</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.185730931175776</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.790674239128966</v>
+        <v>-3.511103885779095</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.197798001509966</v>
+        <v>1.309626142849914</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.8296559268650899</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.212217677594353</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.813154589987851</v>
+        <v>-3.53358423663798</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.183199655305002</v>
+        <v>1.29502779664495</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.8296559268650899</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.206611471732944</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.765498859426795</v>
+        <v>-3.485928506076924</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.208643704557229</v>
+        <v>1.320471845897177</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8452362737894902</v>
+        <v>0.8773116574261456</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.241586667097382</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.66498070092804</v>
+        <v>-3.38541034757817</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.253743341331456</v>
+        <v>1.365571482671404</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9457544322882447</v>
+        <v>0.9778298159249001</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.30678993557136</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.649075371495687</v>
+        <v>-3.369505018145817</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.246860145580269</v>
+        <v>1.358688286920217</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8666417715790058</v>
+        <v>0.8987171552156612</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.246077011621689</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.604236969887289</v>
+        <v>-3.324666616537419</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.268893208834257</v>
+        <v>1.380721350174205</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8711852045238753</v>
+        <v>0.9032605881605307</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.252900773999239</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.623735426129298</v>
+        <v>-3.344165072779427</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.265254765968532</v>
+        <v>1.37708290730848</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.823100563243971</v>
+        <v>0.8551759468806264</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.228210928862374</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.579532589043397</v>
+        <v>-3.299962235693527</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.288815503330729</v>
+        <v>1.400643644670677</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8673034003298714</v>
+        <v>0.8993787839665268</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.260612233641751</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.587092254880444</v>
+        <v>-3.307521901530574</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.284201637465158</v>
+        <v>1.396029778805106</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.9541821879763461</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.291904276516891</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.428800837341172</v>
+        <v>-3.149230483991301</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.398765969663907</v>
+        <v>1.510594111003854</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.9541821879763461</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.343152041699931</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.221158833706696</v>
+        <v>-2.941588480356825</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.48026347571195</v>
+        <v>1.592091617051898</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.129748807974167</v>
+        <v>1.161824191610822</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.466177948474869</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.170126740984168</v>
+        <v>-2.890556387634297</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.495624541039231</v>
+        <v>1.607452682379179</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.180780900696695</v>
+        <v>1.21285628433335</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.491745432346656</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.104902559856962</v>
+        <v>-2.825332206507091</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.538901617582819</v>
+        <v>1.650729758922767</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.246005081823901</v>
+        <v>1.278080465460556</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.548067345115684</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.067475539785828</v>
+        <v>-2.787905186435958</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.549833397910553</v>
+        <v>1.661661539250501</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.251256619853082</v>
+        <v>1.283332003489738</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.547179240232474</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.087587195820536</v>
+        <v>-2.808016842470666</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.543045527827909</v>
+        <v>1.654873669167857</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.262283964850502</v>
+        <v>1.294359348487157</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.555052439562166</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.033842381393332</v>
+        <v>-2.754272028043461</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.725101224620002</v>
+        <v>1.83692936595995</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.272347274290964</v>
+        <v>1.304422657927619</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.721648196247653</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.959060120368319</v>
+        <v>-2.679489767018449</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.875127038247824</v>
+        <v>1.986955179587772</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.347129535315976</v>
+        <v>1.379204918952631</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.886630462080478</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.932976036104511</v>
+        <v>-2.653405682754641</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.877268647967206</v>
+        <v>1.989096789307155</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.347129535315976</v>
+        <v>1.379204918952631</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.878338438094337</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.84509812299539</v>
+        <v>-2.56552776964552</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.910613008794634</v>
+        <v>2.022441150134582</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.463055177739327</v>
+        <v>1.495130561375983</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.946087019132127</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.836205661602107</v>
+        <v>-2.556635308252237</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.931724399078739</v>
+        <v>2.043552540418687</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.463055177739327</v>
+        <v>1.495130561375983</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.963641424858919</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.004681778571985</v>
+        <v>-2.725111425222114</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.856188999695372</v>
+        <v>1.96801714103532</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.435107342022747</v>
+        <v>1.467182725659402</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.938727770833554</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.558425585942545</v>
+        <v>-2.278855232592675</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.015961173935009</v>
+        <v>2.127789315274958</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.340388672353114</v>
+        <v>1.372464055989769</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.863166266219637</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.535704482259392</v>
+        <v>-2.256134128909522</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.015713637905175</v>
+        <v>2.127541779245123</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.340388672353114</v>
+        <v>1.372464055989769</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.853830288716541</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.664906295553435</v>
+        <v>-2.385335942203564</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.122939038438727</v>
+        <v>2.234767179778675</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.211186859059072</v>
+        <v>1.243262242695727</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.935215326591285</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.81968730233169</v>
+        <v>-2.54011694898182</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.098104458221071</v>
+        <v>2.20993259956102</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177819185004596</v>
+        <v>1.209894568641251</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.952272544652246</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.812632612116517</v>
+        <v>-2.533062258766646</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.097601690296686</v>
+        <v>2.209429831636634</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184873875219769</v>
+        <v>1.216949258856425</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.953180714770895</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.785681387790029</v>
+        <v>-2.506111034440158</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.118388333672023</v>
+        <v>2.230216475011971</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199754221247489</v>
+        <v>1.231829604884144</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.972115076032268</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921634395846345</v>
+        <v>-2.642064042496475</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.248110262594456</v>
+        <v>2.359938403934404</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199754221247489</v>
+        <v>1.231829604884144</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.156218208177227</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.944042513651217</v>
+        <v>-2.664472160301347</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.2312637103755</v>
+        <v>2.343091851715449</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199754221247489</v>
+        <v>1.231829604884144</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.148334903080221</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.972266749228818</v>
+        <v>-2.692696395878947</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.222028015694097</v>
+        <v>2.333856157034046</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217730973698797</v>
+        <v>1.249806357335452</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.161174954100644</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981707675117347</v>
+        <v>-2.702137321767477</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.274505363060533</v>
+        <v>2.386333504400481</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340158091242189</v>
+        <v>1.372233474878844</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.290884942348526</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.033981282452989</v>
+        <v>-2.754410929103118</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.256487014671577</v>
+        <v>2.368315156011525</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.287884483906547</v>
+        <v>1.319959867543202</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.262411872492442</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.110311260053895</v>
+        <v>-2.830740906704024</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.22406683652499</v>
+        <v>2.335894977864938</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.287884483906547</v>
+        <v>1.319959867543202</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.260523685386217</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.312564980378248</v>
+        <v>-3.032994627028378</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.137985577998111</v>
+        <v>2.249813719338059</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.085630763582194</v>
+        <v>1.117706147218849</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.133991682794467</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.474133405905503</v>
+        <v>-3.194563052555633</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.071792217997361</v>
+        <v>2.183620359337309</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.9909232234209697</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>4.056355938725892</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.606434698003056</v>
+        <v>-3.326864344653186</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.031945108024258</v>
+        <v>2.143773249364207</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.9909232234209697</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>4.069429345591811</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.792303008842286</v>
+        <v>-3.512732655492416</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.949602980471506</v>
+        <v>2.061431121811454</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8002822464643667</v>
+        <v>0.832357630101022</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.966295186382782</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.820203795951759</v>
+        <v>-3.540633442601889</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.93696670675472</v>
+        <v>2.048794848094667</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7656853223214319</v>
+        <v>0.7977607059580872</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.944061073024023</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.942729898654653</v>
+        <v>-3.663159545304783</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.884720709650761</v>
+        <v>1.996548850990709</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6431592196185381</v>
+        <v>0.6752346032551934</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.867309855379486</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.173244394840242</v>
+        <v>-3.893674041490371</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.859220870767029</v>
+        <v>1.971049012106977</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4126447234329493</v>
+        <v>0.4447201070696046</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.795707117258636</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.429965212835066</v>
+        <v>-4.150394859485196</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.896844262570946</v>
+        <v>2.008672403910894</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.870970091774194</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.583951630611207</v>
+        <v>-4.304381277261337</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.90422996460613</v>
+        <v>2.016058105946078</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.939950360919834</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.533429726783541</v>
+        <v>-4.253859373433671</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.910489928257317</v>
+        <v>2.022318069597265</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.926001563039955</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.785904880791265</v>
+        <v>-4.506334527441395</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.821370355709641</v>
+        <v>1.933198497049589</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.937872052095369</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.078800637270677</v>
+        <v>-4.799230283920807</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.70542258763682</v>
+        <v>1.817250728976768</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3363055329257898</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.939082586614313</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.265464765405485</v>
+        <v>-4.985894412055615</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.634878678610218</v>
+        <v>1.746706819950166</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2774911784645746</v>
+        <v>0.3095665621012299</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.907915716164905</v>
+        <v>3.927160946346897</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.411485452319448</v>
+        <v>-5.131915098969578</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.571548256580823</v>
+        <v>1.683376397920771</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2684080866707176</v>
+        <v>0.3004834703073729</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.89754371382478</v>
+        <v>3.916788944006774</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.528453144958339</v>
+        <v>-5.248882791608469</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.686965236224311</v>
+        <v>1.798793377564258</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2684080866707176</v>
+        <v>0.3004834703073729</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.059747770523824</v>
+        <v>4.078993000705817</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.613171087179292</v>
+        <v>-5.333600733829422</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.647924697299743</v>
+        <v>1.759752838639691</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1832920577426713</v>
+        <v>0.2153674413793266</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.00352479113081</v>
+        <v>4.022770021312803</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.695105905448175</v>
+        <v>-5.415535552098305</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.625380187560681</v>
+        <v>1.737208328900629</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1733573121555911</v>
+        <v>0.2054326957922464</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.007793361347053</v>
+        <v>4.027038591529046</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.797082027696582</v>
+        <v>-5.517511674346713</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.593515377117221</v>
+        <v>1.705343518457169</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07138118990718351</v>
+        <v>0.1034565735438388</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.955533326453911</v>
+        <v>3.974778556635904</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.687075744219361</v>
+        <v>-5.407505390869491</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.629670777752285</v>
+        <v>1.741498919092233</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09458576182445871</v>
+        <v>0.126661145461114</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.961608956848452</v>
+        <v>3.980854187030445</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.544016168478436</v>
+        <v>-5.264445815128566</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.691144618770629</v>
+        <v>1.802972760110577</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.102599188414438</v>
+        <v>0.1346745720510933</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.970667023524414</v>
+        <v>3.989912253706407</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.242569443006598</v>
+        <v>-4.962999089656728</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.8189841918419</v>
+        <v>1.930812333181848</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4361212975229306</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.158795941690052</v>
+        <v>4.178041171872045</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.267159687241782</v>
+        <v>-4.987589333891912</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.810119271900537</v>
+        <v>1.921947413240485</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4361212975229306</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.159767119442763</v>
+        <v>4.179012349624756</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.216121311235262</v>
+        <v>-4.936550957885392</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.8313775266829</v>
+        <v>1.943205668022848</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4361212975229306</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.160610023822517</v>
+        <v>4.179855254004511</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.174982016368631</v>
+        <v>-4.895411663018761</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.866871343503698</v>
+        <v>1.978699484843646</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4451852087529061</v>
+        <v>0.4772605923895614</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.204331699616642</v>
+        <v>4.223576929798635</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.078347104349991</v>
+        <v>-4.798776751000121</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.721709304435089</v>
+        <v>1.833537445775037</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5418201207715461</v>
+        <v>0.5738955044082013</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.078496642951761</v>
+        <v>4.097741873133753</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.208927838880833</v>
+        <v>-4.929357485530963</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.672979054696715</v>
+        <v>1.784807196036663</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4433147698773587</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.003650246307219</v>
+        <v>4.022895476489212</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.044431504689872</v>
+        <v>-4.764861151340002</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.723204407449183</v>
+        <v>1.835032548789131</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4433147698773587</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.988077065383301</v>
+        <v>4.007322295565294</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.071801437374304</v>
+        <v>-4.792231084024434</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.71144414481184</v>
+        <v>1.823272286151788</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4433147698773587</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.987264775819731</v>
+        <v>4.006510006001724</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.082186632264193</v>
+        <v>-4.802616278914323</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.717158845980956</v>
+        <v>1.828986987320904</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4008541913508142</v>
+        <v>0.4329295749874694</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.99090243801087</v>
+        <v>4.010147668192863</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.100774790986418</v>
+        <v>-4.821204437636548</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.780560588268492</v>
+        <v>1.892388729608439</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3822660326285889</v>
+        <v>0.4143414162652441</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.05058654855396</v>
+        <v>4.069831778735953</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.101073337682454</v>
+        <v>-4.821502984332584</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.777310180408376</v>
+        <v>1.889138321748324</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3822660326285889</v>
+        <v>0.4143414162652441</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.047455559372258</v>
+        <v>4.066700789554251</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.000250203992026</v>
+        <v>-4.720679850642156</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.822170328823938</v>
+        <v>1.933998470163886</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3947302481129427</v>
+        <v>0.4268056317495979</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.059464983602262</v>
+        <v>4.078710213784255</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.809468843239619</v>
+        <v>-4.529898489889749</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.898612126603444</v>
+        <v>2.010440267943392</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.58551160886535</v>
+        <v>0.6175869925020052</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.174063053532249</v>
+        <v>4.193308283714242</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.790951989197799</v>
+        <v>-4.511381635847929</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.885855713957769</v>
+        <v>1.997683855297717</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5984417382905582</v>
+        <v>0.6305171219272134</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.161657976924971</v>
+        <v>4.180903207106964</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.765758804696481</v>
+        <v>-4.486188451346611</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.930899924370355</v>
+        <v>2.042728065710302</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6236349227918766</v>
+        <v>0.6557103064285318</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.21174082423782</v>
+        <v>4.230986054419813</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.753704677783518</v>
+        <v>-4.474134324433648</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.929408143036977</v>
+        <v>2.041236284376925</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6356890497048394</v>
+        <v>0.6677644333414946</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.212659868287036</v>
+        <v>4.231905098469029</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.760327924473876</v>
+        <v>-4.480757571124006</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.92863947454497</v>
+        <v>2.040467615884918</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6290658030144811</v>
+        <v>0.6611411866511363</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.210566550456956</v>
+        <v>4.22981178063895</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.657447334945283</v>
+        <v>-4.377876981595413</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.98264273623429</v>
+        <v>2.094470877574238</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.285145930051995</v>
+        <v>4.304391160233988</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.68088937412537</v>
+        <v>-4.4013190207755</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.993468590735849</v>
+        <v>2.105296732075797</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.305348600225589</v>
+        <v>4.324593830407582</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.698961882416982</v>
+        <v>-4.419391529067112</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.986239587419204</v>
+        <v>2.098067728759152</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.305348600225589</v>
+        <v>4.324593830407582</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.930135676293614</v>
+        <v>-4.650565322943744</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.854021983462018</v>
+        <v>1.965850124801966</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.731946392543074</v>
+        <v>0.7640217761797292</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.265600513819056</v>
+        <v>4.284845744001049</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.898849655753159</v>
+        <v>-4.619279302403289</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.87355901067514</v>
+        <v>1.985387152015088</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7632324130835294</v>
+        <v>0.7953077967201846</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.291394745140269</v>
+        <v>4.310639975322262</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.745824263639874</v>
+        <v>-4.466253910290004</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.033940167093358</v>
+        <v>2.145768308433306</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9162578051968135</v>
+        <v>0.9483331888334687</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.482380979981143</v>
+        <v>4.501626210163137</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.774131577513145</v>
+        <v>-4.494561224163275</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.210083466452343</v>
+        <v>2.32191160779229</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9162578051968135</v>
+        <v>0.9483331888334687</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.669847204889436</v>
+        <v>4.689092435071429</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.940724802626667</v>
+        <v>-4.661154449276797</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.112849127761016</v>
+        <v>2.224677269100964</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.7817399637199463</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.539294221175405</v>
+        <v>4.558539451357397</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.767660423244367</v>
+        <v>-4.488090069894497</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.185751282175653</v>
+        <v>2.297579423515602</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.7817399637199463</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.542970623837123</v>
+        <v>4.562215854019115</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.73841444278867</v>
+        <v>-4.4588440894388</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.195067729481427</v>
+        <v>2.306895870821375</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.7817399637199463</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.540588678960618</v>
+        <v>4.559833909142611</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.845339990666521</v>
+        <v>-4.565769637316651</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.149590749487922</v>
+        <v>2.26141889082787</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6427390322054397</v>
+        <v>0.6748144158420949</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.473726589391542</v>
+        <v>4.492971819573535</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.505899308054224</v>
+        <v>3.886228925002296</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.992226622453786</v>
+        <v>-4.7107881958239</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.09226489891625</v>
+        <v>2.204840269568205</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4958524004181749</v>
+        <v>0.5297958573348464</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.387023412462417</v>
+        <v>4.40738948661242</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>105.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-632.7%</t>
+          <t>-644.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-160.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-349.1%</t>
+          <t>-330.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-171.0%</t>
+          <t>-174.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-29.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2057"/>
+  <dimension ref="A1:G2058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.967160419040002</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.329941562892845</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7766563720186828</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.651168331611383</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.153880127349304</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2512273750347207</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7766563720186828</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.64714202707698</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.536881516091936</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09792471821608428</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7766563720186828</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.647039925755396</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.541367961293324</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09870165610695869</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7811428172200714</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.646919574605993</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.900898283797326</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.03976016959659168</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7811428172200714</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.652269877904044</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.951247347251548</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05198377502110274</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8314918806742935</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.629976459788688</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.048866624672945</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.08798973536789267</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9291111580956901</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.574446643957619</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.102938124181303</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1067247788496641</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9831826576040495</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.544897300574175</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.307196299511167</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1829148518629671</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.110821602218038</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.473827130924424</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.340849138019641</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1918934327819204</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.211234970135076</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.418061664658638</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.267379306352192</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1471337986215198</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.137765138467627</v>
+        <v>-1.169840522104282</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.477515265152528</v>
+        <v>2.458270034970535</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.442503723738735</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2026283448286206</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.312889555854171</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.386995835468119</v>
+        <v>2.367750605286126</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.676955817753225</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3036283473360122</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.312889555854171</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.379776670566523</v>
+        <v>2.36053144038453</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.781330548779671</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3520504305205669</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.417264286880617</v>
+        <v>-1.449339670517272</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.310479641176679</v>
+        <v>2.291234410994686</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.943844014478255</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4159400269614446</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.514897717299303</v>
+        <v>-1.546973100935959</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.253015372764023</v>
+        <v>2.23377014258203</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.069880807846545</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4636610156796457</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.489646094489561</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.270860075078983</v>
+        <v>2.25161484489699</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.012809035950614</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4368419712348723</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.489646094489561</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.274850410765384</v>
+        <v>2.255605180583391</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.154480877674734</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4949859348232621</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.489646094489561</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.273375183866643</v>
+        <v>2.254129953684649</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.1048900332499</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4600961868884563</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.440055250064727</v>
+        <v>-1.472130633701382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.318183100686415</v>
+        <v>2.298937870504422</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770575</v>
+        <v>3.676841549770574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.955971698778043</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4135799867463965</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.408805659329554</v>
+        <v>-1.440881042966209</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.323881721480836</v>
+        <v>2.304636491298843</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615278</v>
+        <v>3.685161381615277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.730126546058631</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3136628526224232</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.36687898374239</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.358616799869343</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.60554788972104</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2626922455313276</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.36687898374239</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.359755944425402</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646212</v>
+        <v>3.710935533646211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.658443177765326</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2812165865869343</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.361923637653944</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.365362926240577</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.586310002477445</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2466296122331455</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.361923637653944</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.371096630479213</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.514943609867798</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2278203175831517</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.290557245044296</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.404179203651137</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232408</v>
+        <v>3.747702660232407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.421484575882573</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2003201853019694</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.290557245044296</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.39429572233823</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.410831394329142</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1978934731799709</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.290557245044296</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.392461161838856</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.312924355652651</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1590309726828352</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.22257149518374</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.432952296781729</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.288970814676693</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1487810501469586</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.198617954207782</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.447992927512797</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017766</v>
+        <v>3.789311112017765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.024910876353896</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05641739097959197</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9345580158849862</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.593168574344722</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783972</v>
+        <v>3.833252747839719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.317831252849058</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2236274247620424</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9345580158849862</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.590381540684422</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.277646954482868</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.24004476799636</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.8943737175187955</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.614835743591978</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626469</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.114247083543505</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3047715375928619</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.730973846579433</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.712242487376352</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.880765861313907</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4060884553225539</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.4974926243498344</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.860255649551963</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.731099470306392</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4630628014126006</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4045891331072985</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.913105533984526</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.598823996675505</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5113404776119821</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.2723136594764118</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.987838304910085</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.443085664115763</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5764508713235159</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1165753269166703</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.084096365133567</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.358120997386443</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6233430792389023</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.0316106601873507</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.147981506394817</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.463710987159548</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4531311537304421</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1372006499604551</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.956651582931736</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.39547640253412</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5289693294576994</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1187853270879191</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.016245118532344</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.247536361126521</v>
+        <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4682664233325715</v>
+        <v>0.4062864355632176</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.0984644111793615</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.90855874538931</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.194566838872532</v>
+        <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4807402459806887</v>
+        <v>0.4187602582113348</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.931626472488226</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.028778642912242</v>
+        <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5400949122697121</v>
+        <v>0.4781149245003582</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.924665860393133</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.995415436433473</v>
+        <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5679025492423624</v>
+        <v>0.5059225614730085</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.939128214774276</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.887156299310951</v>
+        <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6057383245505661</v>
+        <v>0.5437583367812122</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.04549488892537262</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.933660335233471</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.76386516449382</v>
+        <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6525528724879956</v>
+        <v>0.5905728847186418</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.07779624589175788</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.005133110134326</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.711168297362529</v>
+        <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6813325975778373</v>
+        <v>0.6193526098084834</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1304931130230491</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.044452208650426</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.467402855379085</v>
+        <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7746194827182658</v>
+        <v>0.7126394949489119</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1304931130230491</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.040232916997477</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.377627183002613</v>
+        <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8126540655888705</v>
+        <v>0.7506740778195167</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1920925579373591</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.079316897866078</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.127776789053538</v>
+        <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9053362981522026</v>
+        <v>0.8433563103828488</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1920925579373591</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.07205897284978</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.951884696586106</v>
+        <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9792922586598241</v>
+        <v>0.9173122708904704</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1920925579373591</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.075658096370429</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.780438233563642</v>
+        <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.061198349923363</v>
+        <v>0.9992183621540094</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3635390209598222</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.191853480238461</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.700415946454521</v>
+        <v>-4.855365915877906</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.092227742383308</v>
+        <v>1.030247754613955</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4435613080689432</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.23888733012023</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.636780204220587</v>
+        <v>-4.791730173643971</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.1223768403312</v>
+        <v>1.060396852561846</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.5071970503028778</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.281763576514908</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.543082886004192</v>
+        <v>-4.698032855427576</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.141050026401553</v>
+        <v>1.079070038632199</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.5071970503028778</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.262957835298704</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.553585509069481</v>
+        <v>-4.708535478492865</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.138592053800315</v>
+        <v>1.076612066030961</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4966944272375888</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.258399338084408</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.481342940898286</v>
+        <v>-4.636292910321671</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.171418394903613</v>
+        <v>1.109438407134259</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4966944272375888</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.262328651919228</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.463629254020421</v>
+        <v>-4.618579223443805</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.179182453572099</v>
+        <v>1.117202465802746</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4998757561345056</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.264916033174718</v>
+        <v>3.245670802992725</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.354824368540694</v>
+        <v>-4.473922120740671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.219702478983983</v>
+        <v>1.172063378103993</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4998757561345056</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.261914104394712</v>
+        <v>3.242668874212719</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.134803570503683</v>
+        <v>-4.25390132270366</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.309289835209402</v>
+        <v>1.261650734329411</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6410956012024859</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.348225048446114</v>
+        <v>3.328979818264121</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539946</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.001935881440405</v>
+        <v>-4.121033633640383</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.378331093636536</v>
+        <v>1.330691992756545</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6410956012024859</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.364119231247937</v>
+        <v>3.344874001065945</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.881762798075906</v>
+        <v>-4.000860550275884</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.427546171422638</v>
+        <v>1.379907070542647</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7612686845669848</v>
+        <v>0.7291933009303296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.437368925706939</v>
+        <v>3.418123695524946</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.746509436745928</v>
+        <v>-3.865607188945907</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.491735618516069</v>
+        <v>1.444096517636078</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8965220458969619</v>
+        <v>0.8644466622603068</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.528609045066365</v>
+        <v>3.509363814884372</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.806384264103621</v>
+        <v>-3.925482016303599</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.453823178974418</v>
+        <v>1.406184078094426</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8366472185392698</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.478721640053176</v>
+        <v>3.459476409871182</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.686564033192783</v>
+        <v>-3.805661785392762</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.517040440572961</v>
+        <v>1.46940133969297</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8366472185392698</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.494010809287384</v>
+        <v>3.474765579105391</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.689033739654589</v>
+        <v>-3.808131491854568</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.42369675731068</v>
+        <v>1.376057656430689</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8341775120774637</v>
+        <v>0.8021021284408085</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.400173184732742</v>
+        <v>3.380927954550749</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.757403925978599</v>
+        <v>-3.876501678178577</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.315610544266378</v>
+        <v>1.267971443386386</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.325000465639772</v>
+        <v>3.305755235457779</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.771191978825646</v>
+        <v>-3.890289731025624</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.30053203175945</v>
+        <v>1.252892930879459</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.315437174271664</v>
+        <v>3.29619194408967</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.826712054718235</v>
+        <v>-3.945809806918214</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.415354838094617</v>
+        <v>1.367715737214626</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.452468010963866</v>
+        <v>3.433222780781873</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.651237794925766</v>
+        <v>-3.770335547125744</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.490111774003392</v>
+        <v>1.442472673123401</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.457035242955654</v>
+        <v>3.43779001277366</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.643313420340852</v>
+        <v>-3.76241117254083</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.469023552598565</v>
+        <v>1.421384451718574</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8434532111136787</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.432777271716861</v>
+        <v>3.413532041534868</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.60964987486857</v>
+        <v>-3.728747627068548</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.411027284188928</v>
+        <v>1.363388183308937</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8771167565859606</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.38151371240168</v>
+        <v>3.362268482219687</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.549797255664847</v>
+        <v>-3.668895007864825</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.445140718302549</v>
+        <v>1.397501617422558</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8771167565859606</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.391686098833812</v>
+        <v>3.372440868651819</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.463553792638469</v>
+        <v>-3.582651544838447</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.474584374086961</v>
+        <v>1.426945273206969</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8771167565859606</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.386632369407672</v>
+        <v>3.367387139225679</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.508860612037449</v>
+        <v>-3.627958364237427</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.448237421771894</v>
+        <v>1.400598320891903</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8363065935767298</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.353922047046659</v>
+        <v>3.334676816864667</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.537893716739751</v>
+        <v>-3.656991468939729</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.437176052924075</v>
+        <v>1.389536952044084</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8363065935767298</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.354473920079761</v>
+        <v>3.335228689897768</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.445083235288891</v>
+        <v>-3.56418098748887</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.403572937395785</v>
+        <v>1.355933836515793</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9291170750275891</v>
+        <v>0.8970416913909339</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.339432900841642</v>
+        <v>3.320187670659649</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.489472704618319</v>
+        <v>-3.608570456818297</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.387690625588614</v>
+        <v>1.340051524708623</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8847276056981614</v>
+        <v>0.8526522220615063</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.314672695168587</v>
+        <v>3.295427464986593</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.606014309723662</v>
+        <v>-3.72511206192364</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.3361496920582</v>
+        <v>1.288510591178209</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7681860005928187</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.239823440617104</v>
+        <v>3.220578210435111</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.645938404306234</v>
+        <v>-3.765036156506212</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.325671350055839</v>
+        <v>1.278032249175848</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7681860005928187</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.245314736447771</v>
+        <v>3.226069506265778</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.673718802207587</v>
+        <v>-3.792816554407565</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.326056392663836</v>
+        <v>1.278417291783845</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7404056026914656</v>
+        <v>0.7083302190548104</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.240143699475498</v>
+        <v>3.220898469293505</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.792099474937725</v>
+        <v>-3.911197227137703</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.117059843572434</v>
+        <v>1.069420742692443</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6731877505404894</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.038168708185566</v>
+        <v>3.018923478003573</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.900713553381056</v>
+        <v>-4.019811305581035</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.193763872914308</v>
+        <v>1.146124772034316</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6731877505404894</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.158318368904772</v>
+        <v>3.139073138722778</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.865304515132913</v>
+        <v>-3.984402267332892</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.222440514315888</v>
+        <v>1.174801413435896</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6731877505404894</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.172831395007095</v>
+        <v>3.153586164825101</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.826920852574762</v>
+        <v>-3.946018604774741</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.235213420681517</v>
+        <v>1.187574319801526</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7115714130986406</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.193281033884354</v>
+        <v>3.174035803702361</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.649804522539596</v>
+        <v>-3.768902274739575</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.302788981540885</v>
+        <v>1.255149880660894</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7115714130986406</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.190010062729656</v>
+        <v>3.170764832547663</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.694896767373141</v>
+        <v>-3.813994519573121</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.28543547536938</v>
+        <v>1.237796374489389</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6496753699292508</v>
+        <v>0.6175999862925956</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.153555828589935</v>
+        <v>3.134310598407942</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.515521346134374</v>
+        <v>-3.634619098334353</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.350972619171302</v>
+        <v>1.30333351829131</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8064521280999695</v>
+        <v>0.7743767444633143</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.24140885879878</v>
+        <v>3.222163628616787</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.56053555965498</v>
+        <v>-3.679633311854959</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.313774389094649</v>
+        <v>1.266135288214657</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7761032327853649</v>
+        <v>0.7440278491487097</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.204006976941607</v>
+        <v>3.184761746759615</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.827540069927415</v>
+        <v>-3.946637822127395</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.21266414732462</v>
+        <v>1.165025046444629</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5817401947424163</v>
+        <v>0.5496648111057612</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.093080716454784</v>
+        <v>3.073835486272791</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.928737851364588</v>
+        <v>-4.047835603564567</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.171388956646253</v>
+        <v>1.123749855766261</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5133313811970972</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.051239350224094</v>
+        <v>3.031994120042101</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.922226884750275</v>
+        <v>-4.041324636950255</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.171593304846295</v>
+        <v>1.123954203966303</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5133313811970972</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.048839311778411</v>
+        <v>3.029594081596418</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.903188757042978</v>
+        <v>-4.022286509242957</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.175733275137459</v>
+        <v>1.128094174257467</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4551477698659027</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.010453864187939</v>
+        <v>2.991208634005946</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.955704559317798</v>
+        <v>-4.074802311517778</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.274021355861721</v>
+        <v>1.226382254981729</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4551477698659027</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.129748265822129</v>
+        <v>3.110503035640136</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.969571320651716</v>
+        <v>-4.088669072851696</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.269307980314287</v>
+        <v>1.221668879434296</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4172898531320797</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.107866844767969</v>
+        <v>3.088621614585976</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.924767149111786</v>
+        <v>-4.043864901311766</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.293238179327185</v>
+        <v>1.245599078447194</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4172898531320797</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.113875375164895</v>
+        <v>3.094630144982902</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.777024178876784</v>
+        <v>-3.896121931076764</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.250285588698386</v>
+        <v>1.202646487818394</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5850972103669629</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.112510010783025</v>
+        <v>3.093264780601031</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.860845400151482</v>
+        <v>-3.979943152351462</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.219550721719987</v>
+        <v>1.171911620839996</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5850972103669629</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.115303632314506</v>
+        <v>3.096058402132512</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.854692694098697</v>
+        <v>-3.973790446298677</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.22267415253276</v>
+        <v>1.175035051652768</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5912499164197472</v>
+        <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.119657604337835</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.871501992249199</v>
+        <v>-3.990599744449179</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.215030910012669</v>
+        <v>1.167391809132677</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5744406182692456</v>
+        <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.108652502187644</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.809203993473077</v>
+        <v>-3.928301745673057</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.306285663319939</v>
+        <v>1.258646562439947</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6197348825436877</v>
+        <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.20216461454913</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.607413795807919</v>
+        <v>-3.726511548007899</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.189293744100129</v>
+        <v>1.141654643220137</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8177530747128421</v>
+        <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.12326753156475</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.658300508494114</v>
+        <v>-3.777398260694094</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.239229291347826</v>
+        <v>1.191590190467835</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7668663620266476</v>
+        <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.163025736275208</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.571689765844306</v>
+        <v>-3.690787518044286</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.288501324523793</v>
+        <v>1.240862223643801</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8454920932318059</v>
+        <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.224828911114347</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.631899063849591</v>
+        <v>-3.750996816049571</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.262953586146351</v>
+        <v>1.215314485266359</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7852827952265213</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.187239313135848</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.555477017417664</v>
+        <v>-3.674574769617644</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.29201402275905</v>
+        <v>1.244374921879058</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7852827952265213</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.185730931175776</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.511103885779095</v>
+        <v>-3.630201637979075</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.309626142849914</v>
+        <v>1.261987041969922</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8296559268650899</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.212217677594353</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.53358423663798</v>
+        <v>-3.65268198883796</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.29502779664495</v>
+        <v>1.247388695764958</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8296559268650899</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.206611471732944</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.485928506076924</v>
+        <v>-3.605026258276904</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.320471845897177</v>
+        <v>1.272832745017185</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8773116574261456</v>
+        <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.241586667097382</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.38541034757817</v>
+        <v>-3.50450809977815</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.365571482671404</v>
+        <v>1.317932381791412</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9778298159249001</v>
+        <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.30678993557136</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.369505018145817</v>
+        <v>-3.488602770345797</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.358688286920217</v>
+        <v>1.311049186040225</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8987171552156612</v>
+        <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.246077011621689</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.324666616537419</v>
+        <v>-3.443764368737399</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.380721350174205</v>
+        <v>1.333082249294213</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9032605881605307</v>
+        <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.252900773999239</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.344165072779427</v>
+        <v>-3.463262824979407</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.37708290730848</v>
+        <v>1.329443806428488</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8551759468806264</v>
+        <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.228210928862374</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.299962235693527</v>
+        <v>-3.419059987893507</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.400643644670677</v>
+        <v>1.353004543790685</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8993787839665268</v>
+        <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.260612233641751</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.307521901530574</v>
+        <v>-3.426619653730554</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.396029778805106</v>
+        <v>1.348390677925114</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9541821879763461</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.291904276516891</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.149230483991301</v>
+        <v>-3.268328236191282</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.510594111003854</v>
+        <v>1.462955010123863</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9541821879763461</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.343152041699931</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.941588480356825</v>
+        <v>-3.060686232556805</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.592091617051898</v>
+        <v>1.544452516171906</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.161824191610822</v>
+        <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.466177948474869</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.890556387634297</v>
+        <v>-3.009654139834277</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.607452682379179</v>
+        <v>1.559813581499187</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.21285628433335</v>
+        <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.491745432346656</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.825332206507091</v>
+        <v>-2.944429958707071</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.650729758922767</v>
+        <v>1.603090658042775</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.278080465460556</v>
+        <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.548067345115684</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.787905186435958</v>
+        <v>-2.907002938635938</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.661661539250501</v>
+        <v>1.614022438370509</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.283332003489738</v>
+        <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.547179240232474</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.808016842470666</v>
+        <v>-2.927114594670646</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.654873669167857</v>
+        <v>1.607234568287865</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.294359348487157</v>
+        <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.555052439562166</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.754272028043461</v>
+        <v>-2.873369780243441</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.83692936595995</v>
+        <v>1.789290265079958</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.304422657927619</v>
+        <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.721648196247653</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.679489767018449</v>
+        <v>-2.798587519218429</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.986955179587772</v>
+        <v>1.939316078707781</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.379204918952631</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.886630462080478</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.653405682754641</v>
+        <v>-2.772503434954621</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.989096789307155</v>
+        <v>1.941457688427163</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.379204918952631</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.878338438094337</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.56552776964552</v>
+        <v>-2.6846255218455</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.022441150134582</v>
+        <v>1.97480204925459</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.495130561375983</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.946087019132127</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959861</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.556635308252237</v>
+        <v>-2.675733060452217</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.043552540418687</v>
+        <v>1.995913439538695</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.495130561375983</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.963641424858919</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.725111425222114</v>
+        <v>-2.844209177422095</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.96801714103532</v>
+        <v>1.920378040155328</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.467182725659402</v>
+        <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.938727770833554</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782712</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.278855232592675</v>
+        <v>-2.397952984792655</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.127789315274958</v>
+        <v>2.080150214394966</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.372464055989769</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.863166266219637</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563264</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.256134128909522</v>
+        <v>-2.375231881109502</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.127541779245123</v>
+        <v>2.079902678365131</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.372464055989769</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.853830288716541</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.385335942203564</v>
+        <v>-2.504433694403545</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.234767179778675</v>
+        <v>2.187128078898684</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.243262242695727</v>
+        <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.935215326591285</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644416</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.54011694898182</v>
+        <v>-2.6592147011818</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.20993259956102</v>
+        <v>2.162293498681028</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.209894568641251</v>
+        <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.952272544652246</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.533062258766646</v>
+        <v>-2.652160010966627</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.209429831636634</v>
+        <v>2.161790730756642</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.216949258856425</v>
+        <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.953180714770895</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331119</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.506111034440158</v>
+        <v>-2.625208786640139</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.230216475011971</v>
+        <v>2.182577374131979</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.231829604884144</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.972115076032268</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.642064042496475</v>
+        <v>-2.761161794696455</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.359938403934404</v>
+        <v>2.312299303054412</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.231829604884144</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.156218208177227</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.664472160301347</v>
+        <v>-2.783569912501327</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.343091851715449</v>
+        <v>2.295452750835457</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.231829604884144</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.148334903080221</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155036</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.692696395878947</v>
+        <v>-2.811794148078927</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.333856157034046</v>
+        <v>2.286217056154054</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.249806357335452</v>
+        <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.161174954100644</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.702137321767477</v>
+        <v>-2.821235073967457</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.386333504400481</v>
+        <v>2.338694403520489</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.372233474878844</v>
+        <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.290884942348526</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.754410929103118</v>
+        <v>-2.873508681303099</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.368315156011525</v>
+        <v>2.320676055131533</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.319959867543202</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.262411872492442</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.830740906704024</v>
+        <v>-2.949838658904004</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.335894977864938</v>
+        <v>2.288255876984946</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.319959867543202</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.260523685386217</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.032994627028378</v>
+        <v>-3.152092379228358</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.249813719338059</v>
+        <v>2.202174618458067</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.117706147218849</v>
+        <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.133991682794467</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234307</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.194563052555633</v>
+        <v>-3.313660804755613</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.183620359337309</v>
+        <v>2.135981258457317</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9909232234209697</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.056355938725892</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389353</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.326864344653186</v>
+        <v>-3.445962096853166</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.143773249364207</v>
+        <v>2.096134148484214</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9909232234209697</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.069429345591811</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378397</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.512732655492416</v>
+        <v>-3.631830407692396</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.061431121811454</v>
+        <v>2.013792020931462</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.832357630101022</v>
+        <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.966295186382782</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.540633442601889</v>
+        <v>-3.659731194801869</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.048794848094667</v>
+        <v>2.001155747214676</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7977607059580872</v>
+        <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.944061073024023</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787391</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.663159545304783</v>
+        <v>-3.782257297504763</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.996548850990709</v>
+        <v>1.948909750110717</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6752346032551934</v>
+        <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.867309855379486</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585942</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.893674041490371</v>
+        <v>-4.012771793690352</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.971049012106977</v>
+        <v>1.923409911226985</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4447201070696046</v>
+        <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.795707117258636</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814669</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.150394859485196</v>
+        <v>-4.269492611685175</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.008672403910894</v>
+        <v>1.961033303030903</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.870970091774194</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.304381277261337</v>
+        <v>-4.423479029461316</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.016058105946078</v>
+        <v>1.968419005066086</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.939950360919834</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423391</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.253859373433671</v>
+        <v>-4.37295712563365</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.022318069597265</v>
+        <v>1.974678968717273</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.926001563039955</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609757</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.506334527441395</v>
+        <v>-4.625432279641374</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.933198497049589</v>
+        <v>1.885559396169598</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.937872052095369</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.799230283920807</v>
+        <v>-4.918328036120786</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.817250728976768</v>
+        <v>1.769611628096777</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3363055329257898</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.939082586614313</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.985894412055615</v>
+        <v>-5.104992164255594</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.746706819950166</v>
+        <v>1.699067719070175</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3095665621012299</v>
+        <v>0.2774911784645746</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.927160946346897</v>
+        <v>3.907915716164905</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.131915098969578</v>
+        <v>-5.251012851169556</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.683376397920771</v>
+        <v>1.635737297040779</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3004834703073729</v>
+        <v>0.2684080866707176</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.916788944006774</v>
+        <v>3.89754371382478</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.248882791608469</v>
+        <v>-5.367980543808447</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.798793377564258</v>
+        <v>1.751154276684267</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3004834703073729</v>
+        <v>0.2684080866707176</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.078993000705817</v>
+        <v>4.059747770523824</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.333600733829422</v>
+        <v>-5.452698486029401</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759752838639691</v>
+        <v>1.7121137377597</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2153674413793266</v>
+        <v>0.1832920577426713</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.022770021312803</v>
+        <v>4.00352479113081</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.415535552098305</v>
+        <v>-5.534633304298284</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.737208328900629</v>
+        <v>1.689569228020638</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2054326957922464</v>
+        <v>0.1733573121555911</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.027038591529046</v>
+        <v>4.007793361347053</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.517511674346713</v>
+        <v>-5.636609426546691</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.705343518457169</v>
+        <v>1.657704417577177</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1034565735438388</v>
+        <v>0.07138118990718351</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.974778556635904</v>
+        <v>3.955533326453911</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.407505390869491</v>
+        <v>-5.52660314306947</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741498919092233</v>
+        <v>1.693859818212241</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.126661145461114</v>
+        <v>0.09458576182445871</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.980854187030445</v>
+        <v>3.961608956848452</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818525</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.264445815128566</v>
+        <v>-5.383543567328545</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802972760110577</v>
+        <v>1.755333659230585</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1346745720510933</v>
+        <v>0.102599188414438</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.989912253706407</v>
+        <v>3.970667023524414</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.962999089656728</v>
+        <v>-5.082096841856707</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.930812333181848</v>
+        <v>1.883173232301857</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4361212975229306</v>
+        <v>0.4040459138862753</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.178041171872045</v>
+        <v>4.158795941690052</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679627</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.987589333891912</v>
+        <v>-5.106687086091891</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.921947413240485</v>
+        <v>1.874308312360494</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4361212975229306</v>
+        <v>0.4040459138862753</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.179012349624756</v>
+        <v>4.159767119442763</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474162</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.936550957885392</v>
+        <v>-5.055648710085371</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.943205668022848</v>
+        <v>1.895566567142857</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4361212975229306</v>
+        <v>0.4040459138862753</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.179855254004511</v>
+        <v>4.160610023822517</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.895411663018761</v>
+        <v>-5.01450941521874</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978699484843646</v>
+        <v>1.931060383963655</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4772605923895614</v>
+        <v>0.4451852087529061</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.223576929798635</v>
+        <v>4.204331699616642</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700481</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.798776751000121</v>
+        <v>-4.9178745032001</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833537445775037</v>
+        <v>1.785898344895045</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5738955044082013</v>
+        <v>0.5418201207715461</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.097741873133753</v>
+        <v>4.078496642951761</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.929357485530963</v>
+        <v>-5.048455237730942</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784807196036663</v>
+        <v>1.737168095156672</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4433147698773587</v>
+        <v>0.4112393862407036</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.022895476489212</v>
+        <v>4.003650246307219</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.764861151340002</v>
+        <v>-4.88395890353998</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.835032548789131</v>
+        <v>1.787393447909139</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4433147698773587</v>
+        <v>0.4112393862407036</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.007322295565294</v>
+        <v>3.988077065383301</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077631</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.792231084024434</v>
+        <v>-4.911328836224413</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.823272286151788</v>
+        <v>1.775633185271796</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4433147698773587</v>
+        <v>0.4112393862407036</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.006510006001724</v>
+        <v>3.987264775819731</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.802616278914323</v>
+        <v>-4.921714031114302</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.828986987320904</v>
+        <v>1.781347886440913</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4329295749874694</v>
+        <v>0.4008541913508142</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.010147668192863</v>
+        <v>3.99090243801087</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735284</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.821204437636548</v>
+        <v>-4.940302189836527</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.892388729608439</v>
+        <v>1.844749628728448</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4143414162652441</v>
+        <v>0.3822660326285889</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.069831778735953</v>
+        <v>4.05058654855396</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496556</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.821502984332584</v>
+        <v>-4.940600736532563</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.889138321748324</v>
+        <v>1.841499220868332</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4143414162652441</v>
+        <v>0.3822660326285889</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.066700789554251</v>
+        <v>4.047455559372258</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108859</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.720679850642156</v>
+        <v>-4.839777602842135</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.933998470163886</v>
+        <v>1.886359369283894</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4268056317495979</v>
+        <v>0.3947302481129427</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.078710213784255</v>
+        <v>4.059464983602262</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.529898489889749</v>
+        <v>-4.648996242089728</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.010440267943392</v>
+        <v>1.962801167063401</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6175869925020052</v>
+        <v>0.58551160886535</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.193308283714242</v>
+        <v>4.174063053532249</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.511381635847929</v>
+        <v>-4.630479388047908</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.997683855297717</v>
+        <v>1.950044754417725</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6305171219272134</v>
+        <v>0.5984417382905582</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.180903207106964</v>
+        <v>4.161657976924971</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912988</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.486188451346611</v>
+        <v>-4.60528620354659</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.042728065710302</v>
+        <v>1.995088964830311</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6557103064285318</v>
+        <v>0.6236349227918766</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.230986054419813</v>
+        <v>4.21174082423782</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539897</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.474134324433648</v>
+        <v>-4.593232076633627</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.041236284376925</v>
+        <v>1.993597183496933</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6677644333414946</v>
+        <v>0.6356890497048394</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.231905098469029</v>
+        <v>4.212659868287036</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.480757571124006</v>
+        <v>-4.599855323323985</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.040467615884918</v>
+        <v>1.992828515004926</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6611411866511363</v>
+        <v>0.6290658030144811</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.22981178063895</v>
+        <v>4.210566550456956</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.377876981595413</v>
+        <v>-4.496974733795392</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.094470877574238</v>
+        <v>2.046831776694246</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.304391160233988</v>
+        <v>4.285145930051995</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760318</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.4013190207755</v>
+        <v>-4.520416772975479</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.105296732075797</v>
+        <v>2.057657631195806</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.324593830407582</v>
+        <v>4.305348600225589</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781709</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.419391529067112</v>
+        <v>-4.538489281267091</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.098067728759152</v>
+        <v>2.050428627879161</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.324593830407582</v>
+        <v>4.305348600225589</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082838</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.650565322943744</v>
+        <v>-4.769663075143723</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.965850124801966</v>
+        <v>1.918211023921975</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7640217761797292</v>
+        <v>0.731946392543074</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.284845744001049</v>
+        <v>4.265600513819056</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.619279302403289</v>
+        <v>-4.738377054603268</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.985387152015088</v>
+        <v>1.937748051135097</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7953077967201846</v>
+        <v>0.7632324130835294</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.310639975322262</v>
+        <v>4.291394745140269</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677827</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.466253910290004</v>
+        <v>-4.585351662489983</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.145768308433306</v>
+        <v>2.098129207553314</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9483331888334687</v>
+        <v>0.9162578051968135</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.501626210163137</v>
+        <v>4.482380979981143</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.494561224163275</v>
+        <v>-4.613658976363253</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.32191160779229</v>
+        <v>2.274272506912299</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9483331888334687</v>
+        <v>0.9162578051968135</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.689092435071429</v>
+        <v>4.669847204889436</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903171</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.661154449276797</v>
+        <v>-4.780252201476776</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.224677269100964</v>
+        <v>2.177038168220972</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7817399637199463</v>
+        <v>0.7496645800832911</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.558539451357397</v>
+        <v>4.539294221175405</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568386</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.488090069894497</v>
+        <v>-4.607187822094476</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.297579423515602</v>
+        <v>2.24994032263561</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7817399637199463</v>
+        <v>0.7496645800832911</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.562215854019115</v>
+        <v>4.542970623837123</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682208</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.4588440894388</v>
+        <v>-4.577941841638779</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.306895870821375</v>
+        <v>2.259256769941384</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7817399637199463</v>
+        <v>0.7496645800832911</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.559833909142611</v>
+        <v>4.540588678960618</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539111</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.565769637316651</v>
+        <v>-4.68486738951663</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.26141889082787</v>
+        <v>2.213779789947878</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6748144158420949</v>
+        <v>0.6427390322054397</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.492971819573535</v>
+        <v>4.473726589391542</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,45 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.886228925002296</v>
+        <v>3.689962785983738</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.7107881958239</v>
+        <v>-4.829885948023879</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.204840269568205</v>
+        <v>2.157201168688213</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5297958573348464</v>
+        <v>0.4977204736981912</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.40738948661242</v>
+        <v>4.388144256430427</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="2" t="n">
+        <v>45520</v>
+      </c>
+      <c r="B2058" t="n">
+        <v>3.847744786329221</v>
+      </c>
+      <c r="C2058" t="n">
+        <v>4.167701195141556</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>-4.829885948023879</v>
+      </c>
+      <c r="E2058" t="n">
+        <v>2.157201168688213</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>0.4977204736981912</v>
+      </c>
+      <c r="G2058" t="n">
+        <v>4.160764992127924</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>97.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.6%</t>
+          <t>-648.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.5%</t>
+          <t>-169.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297395</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940714</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770574</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615277</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812097</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646211</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611563</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955322</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232407</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436223</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311943</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097238</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017765</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839719</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388723</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987897</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.473922120740671</v>
+        <v>-4.509774337964078</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.172063378103993</v>
+        <v>1.15772249121463</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.25390132270366</v>
+        <v>-4.289753539927068</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.261650734329411</v>
+        <v>1.247309847440048</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.121033633640383</v>
+        <v>-4.15688585086379</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.330691992756545</v>
+        <v>1.316351105867182</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.000860550275884</v>
+        <v>-4.036712767499291</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.379907070542647</v>
+        <v>1.365566183653284</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.865607188945907</v>
+        <v>-3.901459406169314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.444096517636078</v>
+        <v>1.429755630746715</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.925482016303599</v>
+        <v>-3.961334233527007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.406184078094426</v>
+        <v>1.391843191205064</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.805661785392762</v>
+        <v>-3.841514002616169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.46940133969297</v>
+        <v>1.455060452803607</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.808131491854568</v>
+        <v>-3.843983709077975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.376057656430689</v>
+        <v>1.361716769541326</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.876501678178577</v>
+        <v>-3.912353895401985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.267971443386386</v>
+        <v>1.253630556497024</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.890289731025624</v>
+        <v>-3.926141948249032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.252892930879459</v>
+        <v>1.238552043990096</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.945809806918214</v>
+        <v>-3.981662024141621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.367715737214626</v>
+        <v>1.353374850325263</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.770335547125744</v>
+        <v>-3.806187764349152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.442472673123401</v>
+        <v>1.428131786234038</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.76241117254083</v>
+        <v>-3.798263389764238</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.421384451718574</v>
+        <v>1.407043564829211</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.728747627068548</v>
+        <v>-3.764599844291956</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.363388183308937</v>
+        <v>1.349047296419573</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8450413729493054</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.668895007864825</v>
+        <v>-3.704747225088233</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.397501617422558</v>
+        <v>1.383160730533195</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8450413729493054</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.582651544838447</v>
+        <v>-3.618503762061855</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.426945273206969</v>
+        <v>1.412604386317607</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8450413729493054</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.627958364237427</v>
+        <v>-3.663810581460835</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.400598320891903</v>
+        <v>1.38625743400254</v>
       </c>
       <c r="F1944" t="n">
         <v>0.8042312099400746</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.656991468939729</v>
+        <v>-3.692843686163136</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.389536952044084</v>
+        <v>1.375196065154721</v>
       </c>
       <c r="F1945" t="n">
         <v>0.8042312099400746</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.56418098748887</v>
+        <v>-3.600033204712277</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.355933836515793</v>
+        <v>1.34159294962643</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8970416913909339</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.608570456818297</v>
+        <v>-3.644422674041705</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.340051524708623</v>
+        <v>1.32571063781926</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8526522220615063</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.72511206192364</v>
+        <v>-3.760964279147048</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.288510591178209</v>
+        <v>1.274169704288846</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7361106169561635</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.765036156506212</v>
+        <v>-3.800888373729619</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.278032249175848</v>
+        <v>1.263691362286484</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7361106169561635</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.792816554407565</v>
+        <v>-3.828668771630972</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.278417291783845</v>
+        <v>1.264076404894482</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7083302190548104</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.911197227137703</v>
+        <v>-3.947049444361111</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.069420742692443</v>
+        <v>1.05507985580308</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6411123669038342</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.019811305581035</v>
+        <v>-4.055663522804442</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.146124772034316</v>
+        <v>1.131783885144953</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6411123669038342</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.984402267332892</v>
+        <v>-4.0202544845563</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.174801413435896</v>
+        <v>1.160460526546534</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.946018604774741</v>
+        <v>-3.981870821998148</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.187574319801526</v>
+        <v>1.173233432912163</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.768902274739575</v>
+        <v>-3.804754491962982</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.255149880660894</v>
+        <v>1.240808993771531</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.813994519573121</v>
+        <v>-3.849846736796528</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.237796374489389</v>
+        <v>1.223455487600026</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.634619098334353</v>
+        <v>-3.67047131555776</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.30333351829131</v>
+        <v>1.288992631401947</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.679633311854959</v>
+        <v>-3.715485529078367</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.266135288214657</v>
+        <v>1.251794401325294</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.946637822127395</v>
+        <v>-3.982490039350802</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.165025046444629</v>
+        <v>1.150684159555266</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.047835603564567</v>
+        <v>-4.083687820787975</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.123749855766261</v>
+        <v>1.109408968876898</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.041324636950255</v>
+        <v>-4.077176854173662</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.123954203966303</v>
+        <v>1.10961331707694</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.022286509242957</v>
+        <v>-4.058138726466365</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.128094174257467</v>
+        <v>1.113753287368104</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.074802311517778</v>
+        <v>-4.110654528741185</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.226382254981729</v>
+        <v>1.212041368092366</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.088669072851696</v>
+        <v>-4.124521290075103</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.221668879434296</v>
+        <v>1.207327992544933</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.043864901311766</v>
+        <v>-4.079717118535173</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.245599078447194</v>
+        <v>1.23125819155783</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.896121931076764</v>
+        <v>-3.931974148300171</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.202646487818394</v>
+        <v>1.188305600929031</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.979943152351462</v>
+        <v>-4.015795369574869</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.171911620839996</v>
+        <v>1.157570733950632</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.685441663544013</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.973790446298677</v>
+        <v>-4.009642663522085</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.175035051652768</v>
+        <v>1.081228173821432</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.020946383213869</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.684522140284124</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.990599744449179</v>
+        <v>-4.026451961672587</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.167391809132677</v>
+        <v>1.073584931301342</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.009941281063678</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.750857694080945</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.928301745673057</v>
+        <v>-3.964153962896465</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.258646562439947</v>
+        <v>1.164839684608611</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.103453393425164</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.553149695795072</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.726511548007899</v>
+        <v>-3.762363765231307</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.141654643220137</v>
+        <v>1.047847765388802</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.024556310440784</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.623439928117247</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.777398260694094</v>
+        <v>-3.813250477917502</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.191590190467835</v>
+        <v>1.097783312636499</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.064314515151243</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.638067664233291</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.690787518044286</v>
+        <v>-3.726639735267694</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.240862223643801</v>
+        <v>1.147055345812465</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.126117689990381</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.636603645057962</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.750996816049571</v>
+        <v>-3.786849033272979</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.215314485266359</v>
+        <v>1.121507607435023</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.088528092011882</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.635095263097891</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.674574769617644</v>
+        <v>-3.710426986841052</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.244374921879058</v>
+        <v>1.150568044047723</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.08701971005181</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.634958130533327</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.630201637979075</v>
+        <v>-3.666053855202483</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.261987041969922</v>
+        <v>1.168180164138586</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.113506456470388</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.629351924671917</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.65268198883796</v>
+        <v>-3.688534206061368</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.247388695764958</v>
+        <v>1.153581817933623</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.107900250608978</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.635733681699722</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.605026258276904</v>
+        <v>-3.640878475500313</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.272832745017185</v>
+        <v>1.179025867185849</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.142875445973416</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.640626055074446</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.50450809977815</v>
+        <v>-3.540360317001558</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.317932381791412</v>
+        <v>1.224125503960076</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.208078714447394</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.627380727550319</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.488602770345797</v>
+        <v>-3.524454987569205</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.311049186040225</v>
+        <v>1.217242308208889</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.147365790497723</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.631478430160947</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.443764368737399</v>
+        <v>-3.479616585960807</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.333082249294213</v>
+        <v>1.239275371462877</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.154189552875273</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.635639369792025</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.463262824979407</v>
+        <v>-3.499115042202816</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.329443806428488</v>
+        <v>1.235636928597152</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.129499707738408</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.641518972319862</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.419059987893507</v>
+        <v>-3.454912205116915</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.353004543790685</v>
+        <v>1.259197665959349</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.161901012517785</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.63992897278911</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.426619653730554</v>
+        <v>-3.462471870953962</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.348390677925114</v>
+        <v>1.254583800093778</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.193193055392925</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.69117673797215</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.268328236191282</v>
+        <v>-3.30418045341469</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.462955010123863</v>
+        <v>1.369148132292526</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.244440820575965</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.689617442566403</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.060686232556805</v>
+        <v>-3.096538449780214</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.544452516171906</v>
+        <v>1.45064563834057</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.367466727350903</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.684565670804673</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.009654139834277</v>
+        <v>-3.045506357057686</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.559813581499187</v>
+        <v>1.466006703667851</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.39303421122269</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.701753074897378</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.944429958707071</v>
+        <v>-2.98028217593048</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.603090658042775</v>
+        <v>1.509283780211438</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.449356123991718</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.697714047196658</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.907002938635938</v>
+        <v>-2.942855155859346</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.614022438370509</v>
+        <v>1.520215560539173</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.448468019108508</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.698970839527898</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.927114594670646</v>
+        <v>-2.962966811894054</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.607234568287865</v>
+        <v>1.513427690456529</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.4563412184382</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.859528610549109</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.873369780243441</v>
+        <v>-2.90922199746685</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.789290265079958</v>
+        <v>1.695483387248622</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.622936975123688</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>2.979641519766926</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.798587519218429</v>
+        <v>-2.834439736441837</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.939316078707781</v>
+        <v>1.845509200876444</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.787919240956512</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>2.971349495780785</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.772503434954621</v>
+        <v>-2.808355652178029</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.941457688427163</v>
+        <v>1.847650810595826</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.779627216970371</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>2.969542691364565</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.6846255218455</v>
+        <v>-2.720477739068909</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.97480204925459</v>
+        <v>1.880995171423254</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.847375798008161</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>2.987097097091356</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.675733060452217</v>
+        <v>-2.711585277675625</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.995913439538695</v>
+        <v>1.902106561707359</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.864930203734953</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>2.97895214449594</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.844209177422095</v>
+        <v>-2.880061394645503</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.920378040155328</v>
+        <v>1.826571162323992</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.840016549709588</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.960221841683802</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.397952984792655</v>
+        <v>-2.433805202016063</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.080150214394966</v>
+        <v>1.98634333656363</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.764455045095671</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.950885864180707</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.375231881109502</v>
+        <v>-2.41108409833291</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.079902678365131</v>
+        <v>1.986095800533795</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.755119067592575</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777676</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.109791990031876</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.504433694403545</v>
+        <v>-2.540285911626953</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.187128078898684</v>
+        <v>2.093321201067347</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.836504105467319</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.146869812525522</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.6592147011818</v>
+        <v>-2.695066918405209</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.162293498681028</v>
+        <v>2.068486620849692</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.85356132352828</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.143545168515067</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.652160010966627</v>
+        <v>-2.688012228190035</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.161790730756642</v>
+        <v>2.067983852925306</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.854469493646929</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.153551322159809</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.625208786640139</v>
+        <v>-2.661061003863547</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.182577374131979</v>
+        <v>2.088770496300643</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.873403854908302</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.337654454304769</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.761161794696455</v>
+        <v>-2.797014011919863</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.312299303054412</v>
+        <v>2.218492425223076</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.057506987053262</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.329771149207762</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.783569912501327</v>
+        <v>-2.819422129724735</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.295452750835457</v>
+        <v>2.201645873004121</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.049623681956255</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.331825148757399</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.811794148078927</v>
+        <v>-2.847646365302336</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.286217056154054</v>
+        <v>2.192410178322718</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.062463732976678</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.388078866479246</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.821235073967457</v>
+        <v>-2.857087291190866</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.338694403520489</v>
+        <v>2.244887525689153</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.19217372122456</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.390969961024547</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.873508681303099</v>
+        <v>-2.909360898526507</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.320676055131533</v>
+        <v>2.226869177300197</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.163700651368476</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.389081773918322</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.949838658904004</v>
+        <v>-2.985690876127413</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.288255876984946</v>
+        <v>2.19444899915361</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.161812464262251</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887751</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.383902003521185</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.152092379228358</v>
+        <v>-3.187944596451766</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.202174618458067</v>
+        <v>2.108367740626731</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.035280461670501</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.382336013731337</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.313660804755613</v>
+        <v>-3.349513021979021</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.135981258457317</v>
+        <v>2.042174380625981</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>3.957644717601926</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.395409420597256</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.445962096853166</v>
+        <v>-3.481814314076574</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.096134148484214</v>
+        <v>2.002327270652879</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>3.970718124467845</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.387414617380196</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.631830407692396</v>
+        <v>-3.667682624915805</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.013792020931462</v>
+        <v>1.919985143100126</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.867583965258816</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.385938658507198</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.659731194801869</v>
+        <v>-3.695583412025278</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.001155747214676</v>
+        <v>1.907348869383339</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.845349851900057</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.382703102484396</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.782257297504763</v>
+        <v>-3.818109514728171</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.948909750110717</v>
+        <v>1.855102872279381</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.76859863425552</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.4494090620749</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.012771793690352</v>
+        <v>-4.04862401091376</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.923409911226985</v>
+        <v>1.829603033395649</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.69699589613467</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.589720781076747</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.269492611685175</v>
+        <v>-4.305344828908584</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.961033303030903</v>
+        <v>1.867226425199566</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.772258870650228</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.658701050222387</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.423479029461316</v>
+        <v>-4.459331246684725</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.968419005066086</v>
+        <v>1.87461212723475</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.841239139795868</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.644752252342508</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.37295712563365</v>
+        <v>-4.408809342857059</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.974678968717273</v>
+        <v>1.880872090885937</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.827290341915989</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.656622741397922</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.625432279641374</v>
+        <v>-4.661284496864783</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.885559396169598</v>
+        <v>1.791752518338261</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.839160830971403</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.657833275916865</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.918328036120786</v>
+        <v>-4.954180253344195</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.769611628096777</v>
+        <v>1.67580475026544</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.840371365490347</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.661955018144187</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.104992164255594</v>
+        <v>-5.140844381479003</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.699067719070175</v>
+        <v>1.605260841238838</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2774911784645746</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.907915716164905</v>
+        <v>3.828449725222932</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.657032870880376</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.251012851169556</v>
+        <v>-5.286865068392966</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.635737297040779</v>
+        <v>1.541930419209443</v>
       </c>
       <c r="F2022" t="n">
         <v>0.2684080866707176</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.89754371382478</v>
+        <v>3.818077722882807</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.81923692757942</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.367980543808447</v>
+        <v>-5.403832761031857</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.751154276684267</v>
+        <v>1.65734739885293</v>
       </c>
       <c r="F2023" t="n">
         <v>0.2684080866707176</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.059747770523824</v>
+        <v>3.980281779581851</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.814083565543235</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.452698486029401</v>
+        <v>-5.48855070325281</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.7121137377597</v>
+        <v>1.618306859928363</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1832920577426713</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.00352479113081</v>
+        <v>3.924058800188837</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.824312983111726</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.534633304298284</v>
+        <v>-5.570485521521693</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.689569228020638</v>
+        <v>1.595762350189301</v>
       </c>
       <c r="F2025" t="n">
         <v>0.1733573121555911</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.007793361347053</v>
+        <v>3.92832737040508</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.833238621567628</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.636609426546691</v>
+        <v>-5.672461643770101</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.657704417577177</v>
+        <v>1.563897539745841</v>
       </c>
       <c r="F2026" t="n">
         <v>0.07138118990718351</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.955533326453911</v>
+        <v>3.876067335511939</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.825391508811804</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.52660314306947</v>
+        <v>-5.562455360292879</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.693859818212241</v>
+        <v>1.600052940380905</v>
       </c>
       <c r="F2027" t="n">
         <v>0.09458576182445871</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.961608956848452</v>
+        <v>3.882142965906479</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.829641519533778</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.383543567328545</v>
+        <v>-5.419395784551954</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.755333659230585</v>
+        <v>1.661526781399249</v>
       </c>
       <c r="F2028" t="n">
         <v>0.102599188414438</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.970667023524414</v>
+        <v>3.891201032582441</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.836902402416314</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.082096841856707</v>
+        <v>-5.117949059080116</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.883173232301857</v>
+        <v>1.78936635447052</v>
       </c>
       <c r="F2029" t="n">
         <v>0.4040459138862753</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.158795941690052</v>
+        <v>4.079329950748079</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.837873580169024</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.106687086091891</v>
+        <v>-5.1425393033153</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.874308312360494</v>
+        <v>1.780501434529157</v>
       </c>
       <c r="F2030" t="n">
         <v>0.4040459138862753</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.159767119442763</v>
+        <v>4.08030112850079</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.83871648454878</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.055648710085371</v>
+        <v>-5.09150092730878</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.895566567142857</v>
+        <v>1.801759689311521</v>
       </c>
       <c r="F2031" t="n">
         <v>0.4040459138862753</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.160610023822517</v>
+        <v>4.081144032880546</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.857754583422925</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.01450941521874</v>
+        <v>-5.050361632442149</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.931060383963655</v>
+        <v>1.837253506132319</v>
       </c>
       <c r="F2032" t="n">
         <v>0.4451852087529061</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.204331699616642</v>
+        <v>4.124865708674669</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700481</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.67393857954686</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.9178745032001</v>
+        <v>-4.953726720423509</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.785898344895045</v>
+        <v>1.692091467063709</v>
       </c>
       <c r="F2033" t="n">
         <v>0.5418201207715461</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.078496642951761</v>
+        <v>3.999030652009788</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.677440623620824</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.048455237730942</v>
+        <v>-5.084307454954351</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.737168095156672</v>
+        <v>1.643361217325336</v>
       </c>
       <c r="F2034" t="n">
         <v>0.4112393862407036</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.003650246307219</v>
+        <v>3.924184255365247</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.661867442696907</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.88395890353998</v>
+        <v>-4.91981112076339</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.787393447909139</v>
+        <v>1.693586570077803</v>
       </c>
       <c r="F2035" t="n">
         <v>0.4112393862407036</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.988077065383301</v>
+        <v>3.908611074441329</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.661055153133336</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.911328836224413</v>
+        <v>-4.947181053447822</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.775633185271796</v>
+        <v>1.68182630744046</v>
       </c>
       <c r="F2036" t="n">
         <v>0.4112393862407036</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.987264775819731</v>
+        <v>3.907798784877759</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.670923932258409</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.921714031114302</v>
+        <v>-4.957566248337711</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.781347886440913</v>
+        <v>1.687541008609577</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4008541913508142</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.99090243801087</v>
+        <v>3.911436447068898</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.741760938034834</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.940302189836527</v>
+        <v>-4.976154407059936</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.844749628728448</v>
+        <v>1.750942750897112</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3822660326285889</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.05058654855396</v>
+        <v>3.971120557611988</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.738629948853132</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.940600736532563</v>
+        <v>-4.976452953755972</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.841499220868332</v>
+        <v>1.747692343036996</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3822660326285889</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.047455559372258</v>
+        <v>3.967989568430286</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.743160843792524</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.839777602842135</v>
+        <v>-4.875629820065544</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.886359369283894</v>
+        <v>1.792552491452559</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3947302481129427</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.059464983602262</v>
+        <v>3.97999899266029</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.743290097271067</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.648996242089728</v>
+        <v>-4.684848459313137</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.962801167063401</v>
+        <v>1.868994289232065</v>
       </c>
       <c r="F2041" t="n">
         <v>0.58551160886535</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.174063053532249</v>
+        <v>4.094597062590277</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.723126943008664</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.630479388047908</v>
+        <v>-4.666331605271317</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.950044754417725</v>
+        <v>1.85623787658639</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5984417382905582</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.161657976924971</v>
+        <v>4.082191985982999</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.758093879620722</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.60528620354659</v>
+        <v>-4.641138420769999</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.995088964830311</v>
+        <v>1.901282086998975</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6236349227918766</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.21174082423782</v>
+        <v>4.132274833295848</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.75178044752216</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.593232076633627</v>
+        <v>-4.629084293857036</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.993597183496933</v>
+        <v>1.899790305665598</v>
       </c>
       <c r="F2044" t="n">
         <v>0.6356890497048394</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.212659868287036</v>
+        <v>4.133193877345064</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811011</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.753661077706296</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.599855323323985</v>
+        <v>-4.635707540547394</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.992828515004926</v>
+        <v>1.899021637173591</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6290658030144811</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.210566550456956</v>
+        <v>4.131100559514985</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382921</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.766512103584178</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.496974733795392</v>
+        <v>-4.532826951018802</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.046831776694246</v>
+        <v>1.95302489886291</v>
       </c>
       <c r="F2046" t="n">
         <v>0.731946392543074</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.285145930051995</v>
+        <v>4.205679939110023</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.786714773757772</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.520416772975479</v>
+        <v>-4.556268990198888</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.057657631195806</v>
+        <v>1.96385075336447</v>
       </c>
       <c r="F2047" t="n">
         <v>0.731946392543074</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.305348600225589</v>
+        <v>4.225882609283617</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.786714773757772</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.538489281267091</v>
+        <v>-4.5743414984905</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.050428627879161</v>
+        <v>1.956621750047825</v>
       </c>
       <c r="F2048" t="n">
         <v>0.731946392543074</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.305348600225589</v>
+        <v>4.225882609283617</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.746966687351239</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.769663075143723</v>
+        <v>-4.805515292367132</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.918211023921975</v>
+        <v>1.824404146090639</v>
       </c>
       <c r="F2049" t="n">
         <v>0.731946392543074</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.265600513819056</v>
+        <v>4.186134522877084</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.753989306348179</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.738377054603268</v>
+        <v>-4.774229271826677</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.937748051135097</v>
+        <v>1.843941173303761</v>
       </c>
       <c r="F2050" t="n">
         <v>0.7632324130835294</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.291394745140269</v>
+        <v>4.211928754198297</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.853160305921083</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.585351662489983</v>
+        <v>-4.621203879713392</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.098129207553314</v>
+        <v>2.004322329721979</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9162578051968135</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.482380979981143</v>
+        <v>4.402914989039171</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>4.040626530829376</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.613658976363253</v>
+        <v>-4.649511193586663</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.274272506912299</v>
+        <v>2.180465629080963</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9162578051968135</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.669847204889436</v>
+        <v>4.590381213947464</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>4.010029482183458</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.780252201476776</v>
+        <v>-4.816104418700185</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.177038168220972</v>
+        <v>2.083231290389636</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7496645800832911</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.539294221175405</v>
+        <v>4.459828230233433</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.093171875787148</v>
+        <v>4.013705884845176</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.607187822094476</v>
+        <v>-4.643040039317885</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.24994032263561</v>
+        <v>2.156133444804274</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7496645800832911</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.542970623837123</v>
+        <v>4.463504632895151</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.090789930910643</v>
+        <v>4.011323939968671</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.577941841638779</v>
+        <v>-4.613794058862188</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.259256769941384</v>
+        <v>2.165449892110048</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7496645800832911</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.540588678960618</v>
+        <v>4.461122688018646</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.088083170068278</v>
+        <v>4.008617179126306</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.68486738951663</v>
+        <v>-4.720719606740039</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.213779789947878</v>
+        <v>2.119972912116543</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6427390322054397</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.473726589391542</v>
+        <v>4.39426059844957</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.68996278598374</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.089511972211512</v>
+        <v>4.01004598126954</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.829885948023879</v>
+        <v>-4.865738165247288</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.157201168688213</v>
+        <v>2.063394290856878</v>
       </c>
       <c r="F2057" t="n">
         <v>0.4977204736981912</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.388144256430427</v>
+        <v>4.308678265488455</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.847744786329221</v>
+        <v>3.845590528253562</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.167701195141556</v>
+        <v>4.088859691564339</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.829885948023879</v>
+        <v>-4.865738165247288</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.157201168688213</v>
+        <v>2.063394290856878</v>
       </c>
       <c r="F2058" t="n">
         <v>0.4977204736981912</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.160764992127924</v>
+        <v>4.081923488550707</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>114.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.2%</t>
+          <t>430.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-648.1%</t>
+          <t>-643.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.9%</t>
+          <t>-160.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.9%</t>
+          <t>-332.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.2%</t>
+          <t>-166.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-20.3%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317609</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.83325274783972</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.685441663544013</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.009642663522085</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.081228173821432</v>
+        <v>1.160694164763405</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.020946383213869</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.684522140284124</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.026451961672587</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.073584931301342</v>
+        <v>1.153050922243314</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.009941281063678</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.750857694080945</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.964153962896465</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.164839684608611</v>
+        <v>1.244305675550584</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.103453393425164</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.553149695795072</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.762363765231307</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.047847765388802</v>
+        <v>1.127313756330774</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.024556310440784</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.623439928117247</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.813250477917502</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.097783312636499</v>
+        <v>1.177249303578471</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.064314515151243</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.638067664233291</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.726639735267694</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.147055345812465</v>
+        <v>1.226521336754438</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.126117689990381</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.636603645057962</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.786849033272979</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.121507607435023</v>
+        <v>1.200973598376996</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.088528092011882</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.635095263097891</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.710426986841052</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.150568044047723</v>
+        <v>1.230034034989695</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.08701971005181</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.634958130533327</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.666053855202483</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.168180164138586</v>
+        <v>1.247646155080559</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.113506456470388</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.629351924671917</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.688534206061368</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.153581817933623</v>
+        <v>1.233047808875595</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.107900250608978</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.635733681699722</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.640878475500313</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.179025867185849</v>
+        <v>1.258491858127822</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.142875445973416</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.640626055074446</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.540360317001558</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.224125503960076</v>
+        <v>1.303591494902049</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.208078714447394</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.627380727550319</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.524454987569205</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.217242308208889</v>
+        <v>1.296708299150862</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.147365790497723</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.631478430160947</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.479616585960807</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.239275371462877</v>
+        <v>1.31874136240485</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.154189552875273</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.635639369792025</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.499115042202816</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.235636928597152</v>
+        <v>1.315102919539125</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.129499707738408</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.641518972319862</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.454912205116915</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.259197665959349</v>
+        <v>1.338663656901322</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.161901012517785</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.63992897278911</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.462471870953962</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.254583800093778</v>
+        <v>1.334049791035751</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.193193055392925</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.69117673797215</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.30418045341469</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.369148132292526</v>
+        <v>1.448614123234499</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.244440820575965</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.689617442566403</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.096538449780214</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.45064563834057</v>
+        <v>1.530111629282543</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.367466727350903</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.684565670804673</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.045506357057686</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.466006703667851</v>
+        <v>1.545472694609824</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.39303421122269</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.701753074897378</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.98028217593048</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.509283780211438</v>
+        <v>1.588749771153411</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.449356123991718</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.697714047196658</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.942855155859346</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.520215560539173</v>
+        <v>1.599681551481145</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.448468019108508</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.698970839527898</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.962966811894054</v>
+        <v>-2.920290358801181</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.513427690456529</v>
+        <v>1.609964262635652</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.262283964850502</v>
+        <v>1.336991912322051</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.4563412184382</v>
+        <v>3.580631977863102</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.859528610549109</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.90922199746685</v>
+        <v>-2.866545544373976</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.695483387248622</v>
+        <v>1.792019959427744</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.272347274290964</v>
+        <v>1.347055221762513</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.622936975123688</v>
+        <v>3.74722773454859</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.979641519766926</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.834439736441837</v>
+        <v>-2.791763283348963</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.845509200876444</v>
+        <v>1.942045773055566</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.347129535315976</v>
+        <v>1.421837482787526</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.787919240956512</v>
+        <v>3.912210000381415</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.971349495780785</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.808355652178029</v>
+        <v>-2.765679199085155</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.847650810595826</v>
+        <v>1.944187382774949</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.347129535315976</v>
+        <v>1.421837482787526</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.779627216970371</v>
+        <v>3.903917976395274</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.969542691364565</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.720477739068909</v>
+        <v>-2.677801285976035</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.880995171423254</v>
+        <v>1.977531743602376</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.463055177739327</v>
+        <v>1.537763125210877</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.847375798008161</v>
+        <v>3.971666557433064</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.987097097091356</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.711585277675625</v>
+        <v>-2.668908824582751</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.902106561707359</v>
+        <v>1.998643133886481</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.463055177739327</v>
+        <v>1.537763125210877</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.864930203734953</v>
+        <v>3.989220963159855</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.97895214449594</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.880061394645503</v>
+        <v>-2.837384941552629</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.826571162323992</v>
+        <v>1.923107734503114</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.435107342022747</v>
+        <v>1.509815289494296</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.840016549709588</v>
+        <v>3.964307309134491</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.960221841683802</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.433805202016063</v>
+        <v>-2.391128748923189</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.98634333656363</v>
+        <v>2.082879908742752</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.340388672353114</v>
+        <v>1.415096619824664</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.764455045095671</v>
+        <v>3.888745804520573</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.950885864180707</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.41108409833291</v>
+        <v>-2.368407645240037</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.986095800533795</v>
+        <v>2.082632372712917</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.340388672353114</v>
+        <v>1.415096619824664</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.755119067592575</v>
+        <v>3.879409827017478</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777676</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.109791990031876</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.540285911626953</v>
+        <v>-2.497609458534079</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.093321201067347</v>
+        <v>2.189857773246469</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.211186859059072</v>
+        <v>1.285894806530621</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.836504105467319</v>
+        <v>3.960794864892222</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.146869812525522</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.695066918405209</v>
+        <v>-2.652390465312335</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.068486620849692</v>
+        <v>2.165023193028814</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177819185004596</v>
+        <v>1.252527132476145</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.85356132352828</v>
+        <v>3.977852082953182</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.143545168515067</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.688012228190035</v>
+        <v>-2.645335775097161</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.067983852925306</v>
+        <v>2.164520425104429</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184873875219769</v>
+        <v>1.259581822691319</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.854469493646929</v>
+        <v>3.978760253071831</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.153551322159809</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.661061003863547</v>
+        <v>-2.618384550770673</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.088770496300643</v>
+        <v>2.185307068479765</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199754221247489</v>
+        <v>1.274462168719038</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.873403854908302</v>
+        <v>3.997694614333205</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.337654454304769</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.797014011919863</v>
+        <v>-2.75433755882699</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.218492425223076</v>
+        <v>2.315028997402198</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199754221247489</v>
+        <v>1.274462168719038</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.057506987053262</v>
+        <v>4.181797746478164</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.329771149207762</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.819422129724735</v>
+        <v>-2.776745676631862</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.201645873004121</v>
+        <v>2.298182445183243</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199754221247489</v>
+        <v>1.274462168719038</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.049623681956255</v>
+        <v>4.173914441381157</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.331825148757399</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.847646365302336</v>
+        <v>-2.804969912209462</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.192410178322718</v>
+        <v>2.28894675050184</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217730973698797</v>
+        <v>1.292438921170347</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.062463732976678</v>
+        <v>4.18675449240158</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.388078866479246</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.857087291190866</v>
+        <v>-2.814410838097992</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.244887525689153</v>
+        <v>2.341424097868275</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340158091242189</v>
+        <v>1.414866038713738</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.19217372122456</v>
+        <v>4.316464480649462</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.390969961024547</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.909360898526507</v>
+        <v>-2.866684445433633</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.226869177300197</v>
+        <v>2.32340574947932</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.287884483906547</v>
+        <v>1.362592431378097</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.163700651368476</v>
+        <v>4.287991410793379</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347707</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.389081773918322</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.985690876127413</v>
+        <v>-2.943014423034539</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.19444899915361</v>
+        <v>2.290985571332732</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.287884483906547</v>
+        <v>1.362592431378097</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.161812464262251</v>
+        <v>4.286103223687154</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.383902003521185</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.187944596451766</v>
+        <v>-3.145268143358892</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.108367740626731</v>
+        <v>2.204904312805853</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.085630763582194</v>
+        <v>1.160338711053744</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.035280461670501</v>
+        <v>4.159571221095404</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.382336013731337</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.349513021979021</v>
+        <v>-3.306836568886148</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.042174380625981</v>
+        <v>2.138710952805103</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9588478397843144</v>
+        <v>1.033555787255864</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.957644717601926</v>
+        <v>4.081935477026828</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.395409420597256</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.481814314076574</v>
+        <v>-3.439137860983701</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.002327270652879</v>
+        <v>2.098863842832001</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9588478397843144</v>
+        <v>1.033555787255864</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.970718124467845</v>
+        <v>4.095008883892747</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.387414617380196</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.667682624915805</v>
+        <v>-3.625006171822931</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.919985143100126</v>
+        <v>2.016521715279249</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8002822464643667</v>
+        <v>0.8749901939359166</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.867583965258816</v>
+        <v>3.991874724683719</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.385938658507198</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.695583412025278</v>
+        <v>-3.652906958932404</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.907348869383339</v>
+        <v>2.003885441562462</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7656853223214319</v>
+        <v>0.8403932697929818</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.845349851900057</v>
+        <v>3.96964061132496</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.382703102484396</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.818109514728171</v>
+        <v>-3.775433061635298</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.855102872279381</v>
+        <v>1.951639444458503</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6431592196185381</v>
+        <v>0.7178671670900879</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.76859863425552</v>
+        <v>3.892889393680422</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.4494090620749</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.04862401091376</v>
+        <v>-4.005947557820886</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.829603033395649</v>
+        <v>1.926139605574771</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4126447234329493</v>
+        <v>0.4873526709044992</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.69699589613467</v>
+        <v>3.821286655559573</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.589720781076747</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.305344828908584</v>
+        <v>-4.262668375815711</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.867226425199566</v>
+        <v>1.963762997378688</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3789380967606844</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.772258870650228</v>
+        <v>3.896549630075131</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.658701050222387</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.459331246684725</v>
+        <v>-4.416654793591851</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.87461212723475</v>
+        <v>1.971148699413872</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3789380967606844</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.841239139795868</v>
+        <v>3.965529899220771</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.644752252342508</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.408809342857059</v>
+        <v>-4.366132889764185</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.880872090885937</v>
+        <v>1.977408663065059</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3789380967606844</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.827290341915989</v>
+        <v>3.951581101340891</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.656622741397922</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.661284496864783</v>
+        <v>-4.61860804377191</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.791752518338261</v>
+        <v>1.888289090517383</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3789380967606844</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.839160830971403</v>
+        <v>3.963451590396305</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.657833275916865</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.954180253344195</v>
+        <v>-4.911503800251322</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.67580475026544</v>
+        <v>1.772341322444562</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3789380967606844</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.840371365490347</v>
+        <v>3.964662124915249</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.661955018144187</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.140844381479003</v>
+        <v>-5.09816792838613</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.605260841238838</v>
+        <v>1.70179741341796</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2774911784645746</v>
+        <v>0.3521991259361245</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.828449725222932</v>
+        <v>3.952740484647834</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.657032870880376</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.286865068392966</v>
+        <v>-5.244188615300092</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.541930419209443</v>
+        <v>1.638466991388565</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2684080866707176</v>
+        <v>0.3431160341422675</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.818077722882807</v>
+        <v>3.94236848230771</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.81923692757942</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.403832761031857</v>
+        <v>-5.361156307938983</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.65734739885293</v>
+        <v>1.753883971032053</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2684080866707176</v>
+        <v>0.3431160341422675</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.980281779581851</v>
+        <v>4.104572539006754</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.814083565543235</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.48855070325281</v>
+        <v>-5.445874250159936</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.618306859928363</v>
+        <v>1.714843432107485</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1832920577426713</v>
+        <v>0.2580000052142211</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.924058800188837</v>
+        <v>4.04834955961374</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.824312983111726</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.570485521521693</v>
+        <v>-5.527809068428819</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.595762350189301</v>
+        <v>1.692298922368423</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1733573121555911</v>
+        <v>0.2480652596271409</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.92832737040508</v>
+        <v>4.052618129829983</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.833238621567628</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.672461643770101</v>
+        <v>-5.629785190677227</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.563897539745841</v>
+        <v>1.660434111924963</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07138118990718351</v>
+        <v>0.1460891373787334</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.876067335511939</v>
+        <v>4.000358094936841</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.825391508811804</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.562455360292879</v>
+        <v>-5.519778907200005</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.600052940380905</v>
+        <v>1.696589512560027</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09458576182445871</v>
+        <v>0.1692937092960086</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.882142965906479</v>
+        <v>4.006433725331382</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.829641519533778</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.419395784551954</v>
+        <v>-5.37671933145908</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.661526781399249</v>
+        <v>1.758063353578371</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.102599188414438</v>
+        <v>0.1773071358859878</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.891201032582441</v>
+        <v>4.015491792007344</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.836902402416314</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.117949059080116</v>
+        <v>-5.075272605987243</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.78936635447052</v>
+        <v>1.885902926649643</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4787538613578251</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.079329950748079</v>
+        <v>4.203620710172982</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.837873580169024</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.1425393033153</v>
+        <v>-5.099862850222427</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.780501434529157</v>
+        <v>1.877038006708279</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4787538613578251</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.08030112850079</v>
+        <v>4.204591887925693</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.83871648454878</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.09150092730878</v>
+        <v>-5.048824474215906</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.801759689311521</v>
+        <v>1.898296261490643</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4040459138862753</v>
+        <v>0.4787538613578251</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.081144032880546</v>
+        <v>4.205434792305447</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.857754583422925</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.050361632442149</v>
+        <v>-5.007685179349275</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.837253506132319</v>
+        <v>1.93379007831144</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4451852087529061</v>
+        <v>0.519893156224456</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.124865708674669</v>
+        <v>4.249156468099572</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700481</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.67393857954686</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.953726720423509</v>
+        <v>-4.911050267330635</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.692091467063709</v>
+        <v>1.788628039242831</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5418201207715461</v>
+        <v>0.6165280682430959</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.999030652009788</v>
+        <v>4.123321411434691</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.677440623620824</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.084307454954351</v>
+        <v>-5.041631001861478</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.643361217325336</v>
+        <v>1.739897789504458</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4859473337122534</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.924184255365247</v>
+        <v>4.048475014790148</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.661867442696907</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.91981112076339</v>
+        <v>-4.877134667670516</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.693586570077803</v>
+        <v>1.790123142256925</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4859473337122534</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.908611074441329</v>
+        <v>4.032901833866231</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.661055153133336</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.947181053447822</v>
+        <v>-4.904504600354948</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.68182630744046</v>
+        <v>1.778362879619582</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4112393862407036</v>
+        <v>0.4859473337122534</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.907798784877759</v>
+        <v>4.032089544302661</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.670923932258409</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.957566248337711</v>
+        <v>-4.914889795244838</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.687541008609577</v>
+        <v>1.784077580788698</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4008541913508142</v>
+        <v>0.4755621388223641</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.911436447068898</v>
+        <v>4.035727206493799</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.741760938034834</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.976154407059936</v>
+        <v>-4.933477953967063</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.750942750897112</v>
+        <v>1.847479323076234</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3822660326285889</v>
+        <v>0.4569739801001387</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.971120557611988</v>
+        <v>4.09541131703689</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.738629948853132</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.976452953755972</v>
+        <v>-4.933776500663098</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.747692343036996</v>
+        <v>1.844228915216118</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3822660326285889</v>
+        <v>0.4569739801001387</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.967989568430286</v>
+        <v>4.092280327855188</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.743160843792524</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.875629820065544</v>
+        <v>-4.832953366972671</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.792552491452559</v>
+        <v>1.88908906363168</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3947302481129427</v>
+        <v>0.4694381955844926</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.97999899266029</v>
+        <v>4.104289752085192</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.743290097271067</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.684848459313137</v>
+        <v>-4.642172006220264</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.868994289232065</v>
+        <v>1.965530861411186</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.58551160886535</v>
+        <v>0.6602195563369</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.094597062590277</v>
+        <v>4.218887822015179</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.723126943008664</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.666331605271317</v>
+        <v>-4.623655152178443</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.85623787658639</v>
+        <v>1.952774448765511</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5984417382905582</v>
+        <v>0.6731496857621082</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.082191985982999</v>
+        <v>4.206482745407901</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.758093879620722</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.641138420769999</v>
+        <v>-4.598461967677125</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.901282086998975</v>
+        <v>1.997818659178097</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6236349227918766</v>
+        <v>0.6983428702634266</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.132274833295848</v>
+        <v>4.25656559272075</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.75178044752216</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.629084293857036</v>
+        <v>-4.586407840764163</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.899790305665598</v>
+        <v>1.996326877844719</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6356890497048394</v>
+        <v>0.7103969971763894</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.133193877345064</v>
+        <v>4.257484636769965</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811011</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.753661077706296</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.635707540547394</v>
+        <v>-4.593031087454521</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.899021637173591</v>
+        <v>1.995558209352712</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6290658030144811</v>
+        <v>0.7037737504860311</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.131100559514985</v>
+        <v>4.255391318939886</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382921</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.766512103584178</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.532826951018802</v>
+        <v>-4.490150497925928</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.95302489886291</v>
+        <v>2.049561471042032</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.731946392543074</v>
+        <v>0.806654340014624</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.205679939110023</v>
+        <v>4.329970698534924</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.786714773757772</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.556268990198888</v>
+        <v>-4.513592537106015</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.96385075336447</v>
+        <v>2.060387325543591</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.731946392543074</v>
+        <v>0.806654340014624</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.225882609283617</v>
+        <v>4.350173368708519</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.786714773757772</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.5743414984905</v>
+        <v>-4.531665045397626</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.956621750047825</v>
+        <v>2.053158322226946</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.731946392543074</v>
+        <v>0.806654340014624</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.225882609283617</v>
+        <v>4.350173368708519</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.746966687351239</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.805515292367132</v>
+        <v>-4.762838839274258</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824404146090639</v>
+        <v>1.92094071826976</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.731946392543074</v>
+        <v>0.806654340014624</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.186134522877084</v>
+        <v>4.310425282301986</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.753989306348179</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.774229271826677</v>
+        <v>-4.731552818733803</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.843941173303761</v>
+        <v>1.940477745482883</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7632324130835294</v>
+        <v>0.8379403605550794</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.211928754198297</v>
+        <v>4.336219513623199</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.853160305921083</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.621203879713392</v>
+        <v>-4.578527426620519</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.004322329721979</v>
+        <v>2.1008589019011</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9162578051968135</v>
+        <v>0.9909657526683635</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.402914989039171</v>
+        <v>4.527205748464073</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.040626530829376</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.649511193586663</v>
+        <v>-4.606834740493789</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.180465629080963</v>
+        <v>2.277002201260085</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9162578051968135</v>
+        <v>0.9909657526683635</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.590381213947464</v>
+        <v>4.714671973372366</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.010029482183458</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.816104418700185</v>
+        <v>-4.773427965607311</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.083231290389636</v>
+        <v>2.179767862568758</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.824372527554841</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.459828230233433</v>
+        <v>4.584118989658335</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.013705884845176</v>
+        <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.643040039317885</v>
+        <v>-4.600363586225011</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.156133444804274</v>
+        <v>2.252670016983396</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.824372527554841</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.463504632895151</v>
+        <v>4.587795392320053</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.011323939968671</v>
+        <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.613794058862188</v>
+        <v>-4.571117605769315</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.165449892110048</v>
+        <v>2.26198646428917</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7496645800832911</v>
+        <v>0.824372527554841</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.461122688018646</v>
+        <v>4.585413447443548</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.008617179126306</v>
+        <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.720719606740039</v>
+        <v>-4.678043153647166</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.119972912116543</v>
+        <v>2.216509484295664</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6427390322054397</v>
+        <v>0.7174469796769897</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.39426059844957</v>
+        <v>4.518551357874472</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.68996278598374</v>
+        <v>3.689962785983736</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.01004598126954</v>
+        <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.865738165247288</v>
+        <v>-4.823061712154415</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.063394290856878</v>
+        <v>2.159930863035999</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4977204736981912</v>
+        <v>0.5724284211697411</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.308678265488455</v>
+        <v>4.432969024913357</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.845590528253562</v>
+        <v>3.864080250139895</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.088859691564339</v>
+        <v>4.264207686147855</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.865738165247288</v>
+        <v>-4.823061712154415</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.063394290856878</v>
+        <v>2.159930863035999</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4977204736981912</v>
+        <v>0.5724284211697411</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.081923488550707</v>
+        <v>4.257271483134223</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>101.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>132.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.1%</t>
+          <t>430.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.9%</t>
+          <t>-618.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-150.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-332.6%</t>
+          <t>-335.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-152.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317609</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388723</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.856161751626469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987897</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675932</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539944</v>
+        <v>3.843274527539946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.982490039350802</v>
+        <v>-3.728282445306716</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.150684159555266</v>
+        <v>1.2523671971729</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5496648111057612</v>
+        <v>0.6973893427183362</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073835486272791</v>
+        <v>3.162470205240336</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.083687820787975</v>
+        <v>-3.829480226743889</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.109408968876898</v>
+        <v>1.211092006494533</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.481255997560442</v>
+        <v>0.6289805291730171</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031994120042101</v>
+        <v>3.120628839009646</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.077176854173662</v>
+        <v>-3.822969260129577</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.10961331707694</v>
+        <v>1.211296354694574</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.481255997560442</v>
+        <v>0.6289805291730171</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029594081596418</v>
+        <v>3.118228800563963</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.058138726466365</v>
+        <v>-3.803931132422279</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.113753287368104</v>
+        <v>1.215436324985738</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.5707969178418225</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.991208634005946</v>
+        <v>3.079843352973491</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.110654528741185</v>
+        <v>-3.856446934697099</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.212041368092366</v>
+        <v>1.313724405710001</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.5707969178418225</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.110503035640136</v>
+        <v>3.199137754607681</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.124521290075103</v>
+        <v>-3.870313696031017</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.207327992544933</v>
+        <v>1.309011030162567</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.5329390011079995</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088621614585976</v>
+        <v>3.177256333553521</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.079717118535173</v>
+        <v>-3.825509524491087</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.23125819155783</v>
+        <v>1.332941229175465</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.5329390011079995</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094630144982902</v>
+        <v>3.183264863950447</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.931974148300171</v>
+        <v>-3.677766554256085</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.188305600929031</v>
+        <v>1.289988638546665</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.7007463583428827</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.093264780601031</v>
+        <v>3.181899499568576</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.015795369574869</v>
+        <v>-3.761587775530783</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.157570733950632</v>
+        <v>1.259253771568267</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.7007463583428827</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.184693121100057</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.009642663522085</v>
+        <v>-3.755435069477998</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.160694164763405</v>
+        <v>1.262377202381039</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5591745327830919</v>
+        <v>0.706899064395667</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.189047093123386</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.026451961672587</v>
+        <v>-3.7722443676285</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.153050922243314</v>
+        <v>1.254733959860949</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5423652346325902</v>
+        <v>0.6900897662451653</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.178041990973195</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.964153962896465</v>
+        <v>-3.709946368852378</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.244305675550584</v>
+        <v>1.345988713168218</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5876594989070323</v>
+        <v>0.7353840305196073</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.271554103334682</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.762363765231307</v>
+        <v>-3.50815617118722</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.127313756330774</v>
+        <v>1.228996793948409</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7856776910761867</v>
+        <v>0.9334022226887617</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.192657020350302</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.813250477917502</v>
+        <v>-3.559042883873415</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.177249303578471</v>
+        <v>1.278932341196106</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7347909783899922</v>
+        <v>0.8825155100025672</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.23241522506076</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.726639735267694</v>
+        <v>-3.472432141223607</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.226521336754438</v>
+        <v>1.328204374372073</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8134167095951504</v>
+        <v>0.9611412412077255</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.294218399899898</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.786849033272979</v>
+        <v>-3.532641439228892</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.200973598376996</v>
+        <v>1.302656635994631</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.900931943202441</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.2566288019214</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.710426986841052</v>
+        <v>-3.456219392796965</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.230034034989695</v>
+        <v>1.33171707260733</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.900931943202441</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.255120419961328</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.666053855202483</v>
+        <v>-3.411846261158396</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.247646155080559</v>
+        <v>1.349329192698193</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.9453050748410096</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.281607166379906</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.688534206061368</v>
+        <v>-3.434326612017281</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.233047808875595</v>
+        <v>1.33473084649323</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.9453050748410096</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.276000960518496</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.640878475500313</v>
+        <v>-3.386670881456226</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.258491858127822</v>
+        <v>1.360174895745457</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8452362737894902</v>
+        <v>0.9929608054020651</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.310976155882934</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.540360317001558</v>
+        <v>-3.286152722957471</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.303591494902049</v>
+        <v>1.405274532519684</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9457544322882447</v>
+        <v>1.09347896390082</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.376179424356911</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.524454987569205</v>
+        <v>-3.270247393525119</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.296708299150862</v>
+        <v>1.398391336768497</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8666417715790058</v>
+        <v>1.014366303191581</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.31546650040724</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.479616585960807</v>
+        <v>-3.225408991916721</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.31874136240485</v>
+        <v>1.420424400022485</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8711852045238753</v>
+        <v>1.01890973613645</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.322290262784791</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.499115042202816</v>
+        <v>-3.244907448158729</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.315102919539125</v>
+        <v>1.416785957156759</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.823100563243971</v>
+        <v>0.970825094856546</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.297600417647926</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.454912205116915</v>
+        <v>-3.200704611072828</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.338663656901322</v>
+        <v>1.440346694518957</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8673034003298714</v>
+        <v>1.015027931942446</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.330001722427304</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.462471870953962</v>
+        <v>-3.208264276909875</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.334049791035751</v>
+        <v>1.435732828653385</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9221068043396907</v>
+        <v>1.069831335952266</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.361293765302443</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.30418045341469</v>
+        <v>-3.049972859370603</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.448614123234499</v>
+        <v>1.550297160852134</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9221068043396907</v>
+        <v>1.069831335952266</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.412541530485482</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.096538449780214</v>
+        <v>-2.842330855736127</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.530111629282543</v>
+        <v>1.631794666900178</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.129748807974167</v>
+        <v>1.277473339586742</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.535567437260421</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.045506357057686</v>
+        <v>-2.791298763013599</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.545472694609824</v>
+        <v>1.647155732227459</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.180780900696695</v>
+        <v>1.32850543230927</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.561134921132208</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.98028217593048</v>
+        <v>-2.726074581886393</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.588749771153411</v>
+        <v>1.690432808771046</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.246005081823901</v>
+        <v>1.393729613436476</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.617456833901236</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.942855155859346</v>
+        <v>-2.688647561815259</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.599681551481145</v>
+        <v>1.70136458909878</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.251256619853082</v>
+        <v>1.398981151465657</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.616568729018026</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.920290358801181</v>
+        <v>-2.666082764757094</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.609964262635652</v>
+        <v>1.711647300253286</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.336991912322051</v>
+        <v>1.484716443934626</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.580631977863102</v>
+        <v>3.669266696830647</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.866545544373976</v>
+        <v>-2.612337950329889</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.792019959427744</v>
+        <v>1.893702997045379</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.347055221762513</v>
+        <v>1.494779753375088</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.74722773454859</v>
+        <v>3.835862453516135</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.791763283348963</v>
+        <v>-2.537555689304877</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.942045773055566</v>
+        <v>2.043728810673201</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.421837482787526</v>
+        <v>1.569562014400101</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.912210000381415</v>
+        <v>4.00084471934896</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.765679199085155</v>
+        <v>-2.511471605041069</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.944187382774949</v>
+        <v>2.045870420392584</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.421837482787526</v>
+        <v>1.569562014400101</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.903917976395274</v>
+        <v>3.992552695362819</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.677801285976035</v>
+        <v>-2.423593691931948</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.977531743602376</v>
+        <v>2.079214781220011</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.537763125210877</v>
+        <v>1.685487656823452</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.971666557433064</v>
+        <v>4.060301276400609</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.668908824582751</v>
+        <v>-2.414701230538665</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.998643133886481</v>
+        <v>2.100326171504116</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.537763125210877</v>
+        <v>1.685487656823452</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.989220963159855</v>
+        <v>4.0778556821274</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.837384941552629</v>
+        <v>-2.583177347508542</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.923107734503114</v>
+        <v>2.024790772120749</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.509815289494296</v>
+        <v>1.657539821106871</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.964307309134491</v>
+        <v>4.052942028102036</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.391128748923189</v>
+        <v>-2.136921154879103</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.082879908742752</v>
+        <v>2.184562946360387</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.415096619824664</v>
+        <v>1.562821151437239</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.888745804520573</v>
+        <v>3.977380523488119</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.368407645240037</v>
+        <v>-2.11420005119595</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.082632372712917</v>
+        <v>2.184315410330552</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.415096619824664</v>
+        <v>1.562821151437239</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.879409827017478</v>
+        <v>3.968044545985023</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.497609458534079</v>
+        <v>-2.243401864489992</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.189857773246469</v>
+        <v>2.291540810864104</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.285894806530621</v>
+        <v>1.433619338143197</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.960794864892222</v>
+        <v>4.049429583859767</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.652390465312335</v>
+        <v>-2.398182871268248</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.165023193028814</v>
+        <v>2.266706230646449</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.252527132476145</v>
+        <v>1.40025166408872</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.977852082953182</v>
+        <v>4.066486801920727</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.645335775097161</v>
+        <v>-2.391128181053074</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.164520425104429</v>
+        <v>2.266203462722063</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.259581822691319</v>
+        <v>1.407306354303894</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.978760253071831</v>
+        <v>4.067394972039377</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.618384550770673</v>
+        <v>-2.364176956726586</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.185307068479765</v>
+        <v>2.2869901060974</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.274462168719038</v>
+        <v>1.422186700331613</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.997694614333205</v>
+        <v>4.08632933330075</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.75433755882699</v>
+        <v>-2.500129964782903</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.315028997402198</v>
+        <v>2.416712035019833</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.274462168719038</v>
+        <v>1.422186700331613</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.181797746478164</v>
+        <v>4.27043246544571</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.776745676631862</v>
+        <v>-2.522538082587775</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.298182445183243</v>
+        <v>2.399865482800878</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.274462168719038</v>
+        <v>1.422186700331613</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.173914441381157</v>
+        <v>4.262549160348703</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.804969912209462</v>
+        <v>-2.550762318165375</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.28894675050184</v>
+        <v>2.390629788119475</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.292438921170347</v>
+        <v>1.440163452782922</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.18675449240158</v>
+        <v>4.275389211369125</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.814410838097992</v>
+        <v>-2.560203244053905</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.341424097868275</v>
+        <v>2.44310713548591</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.414866038713738</v>
+        <v>1.562590570326313</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.316464480649462</v>
+        <v>4.405099199617007</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.866684445433633</v>
+        <v>-2.612476851389546</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.32340574947932</v>
+        <v>2.425088787096954</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.362592431378097</v>
+        <v>1.510316962990672</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.287991410793379</v>
+        <v>4.376626129760924</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.943014423034539</v>
+        <v>-2.688806828990452</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.290985571332732</v>
+        <v>2.392668608950367</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.362592431378097</v>
+        <v>1.510316962990672</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.286103223687154</v>
+        <v>4.374737942654699</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.145268143358892</v>
+        <v>-2.891060549314806</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.204904312805853</v>
+        <v>2.306587350423488</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.160338711053744</v>
+        <v>1.308063242666319</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.159571221095404</v>
+        <v>4.248205940062949</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.306836568886148</v>
+        <v>-3.052628974842061</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.138710952805103</v>
+        <v>2.240393990422738</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.033555787255864</v>
+        <v>1.181280318868439</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.081935477026828</v>
+        <v>4.170570195994373</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.439137860983701</v>
+        <v>-3.184930266939614</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.098863842832001</v>
+        <v>2.200546880449636</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.033555787255864</v>
+        <v>1.181280318868439</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.095008883892747</v>
+        <v>4.183643602860292</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378395</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.625006171822931</v>
+        <v>-3.370798577778844</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.016521715279249</v>
+        <v>2.118204752896883</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8749901939359166</v>
+        <v>1.022714725548492</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.991874724683719</v>
+        <v>4.080509443651263</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006978</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.652906958932404</v>
+        <v>-3.398699364888317</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.003885441562462</v>
+        <v>2.105568479180096</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8403932697929818</v>
+        <v>0.9881178014055568</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.96964061132496</v>
+        <v>4.058275330292505</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.775433061635298</v>
+        <v>-3.521225467591211</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.951639444458503</v>
+        <v>2.053322482076138</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7178671670900879</v>
+        <v>0.8655916987026629</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.892889393680422</v>
+        <v>3.981524112647967</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.61934808158594</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.005947557820886</v>
+        <v>-3.751739963776799</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.926139605574771</v>
+        <v>2.027822643192406</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4873526709044992</v>
+        <v>0.6350772025170742</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.821286655559573</v>
+        <v>3.909921374527118</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.262668375815711</v>
+        <v>-4.008460781771623</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.963762997378688</v>
+        <v>2.065446034996323</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3789380967606844</v>
+        <v>0.5266626283732594</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.896549630075131</v>
+        <v>3.985184349042676</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.416654793591851</v>
+        <v>-4.162447199547763</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.971148699413872</v>
+        <v>2.072831737031507</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3789380967606844</v>
+        <v>0.5266626283732594</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.965529899220771</v>
+        <v>4.054164618188316</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.366132889764185</v>
+        <v>-4.111925295720098</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.977408663065059</v>
+        <v>2.079091700682694</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3789380967606844</v>
+        <v>0.5266626283732594</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.951581101340891</v>
+        <v>4.040215820308436</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.61860804377191</v>
+        <v>-4.364400449727822</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.888289090517383</v>
+        <v>1.989972128135018</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3789380967606844</v>
+        <v>0.5266626283732594</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.963451590396305</v>
+        <v>4.05208630936385</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.911503800251322</v>
+        <v>-4.657296206207234</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.772341322444562</v>
+        <v>1.874024360062197</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3789380967606844</v>
+        <v>0.5266626283732594</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.964662124915249</v>
+        <v>4.053296843882794</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.09816792838613</v>
+        <v>-4.843960334342042</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.70179741341796</v>
+        <v>1.803480451035596</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3521991259361245</v>
+        <v>0.4999236575486995</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.952740484647834</v>
+        <v>4.04137520361538</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.244188615300092</v>
+        <v>-4.989981021256004</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.638466991388565</v>
+        <v>1.7401500290062</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3431160341422675</v>
+        <v>0.4908405657548425</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.94236848230771</v>
+        <v>4.031003201275255</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.361156307938983</v>
+        <v>-5.106948713894895</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.753883971032053</v>
+        <v>1.855567008649688</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3431160341422675</v>
+        <v>0.4908405657548425</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.104572539006754</v>
+        <v>4.193207257974299</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.445874250159936</v>
+        <v>-5.191666656115848</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.714843432107485</v>
+        <v>1.816526469725121</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2580000052142211</v>
+        <v>0.4057245368267961</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.04834955961374</v>
+        <v>4.136984278581285</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868148</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.527809068428819</v>
+        <v>-5.273601474384732</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.692298922368423</v>
+        <v>1.793981959986059</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2480652596271409</v>
+        <v>0.3957897912397159</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.052618129829983</v>
+        <v>4.141252848797528</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.629785190677227</v>
+        <v>-5.375577596633139</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.660434111924963</v>
+        <v>1.762117149542598</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1460891373787334</v>
+        <v>0.2938136689913083</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.000358094936841</v>
+        <v>4.088992813904386</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.519778907200005</v>
+        <v>-5.265571313155918</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.696589512560027</v>
+        <v>1.798272550177662</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1692937092960086</v>
+        <v>0.3170182409085835</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.006433725331382</v>
+        <v>4.095068444298927</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.37671933145908</v>
+        <v>-5.122511737414992</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.758063353578371</v>
+        <v>1.859746391196007</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1773071358859878</v>
+        <v>0.3250316674985628</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.015491792007344</v>
+        <v>4.104126510974889</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.075272605987243</v>
+        <v>-4.821065011943155</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.885902926649643</v>
+        <v>1.987585964267278</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4787538613578251</v>
+        <v>0.6264783929704001</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.203620710172982</v>
+        <v>4.292255429140527</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.099862850222427</v>
+        <v>-4.845655256178339</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.877038006708279</v>
+        <v>1.978721044325915</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4787538613578251</v>
+        <v>0.6264783929704001</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.204591887925693</v>
+        <v>4.293226606893238</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.048824474215906</v>
+        <v>-4.794616880171819</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.898296261490643</v>
+        <v>1.999979299108277</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4787538613578251</v>
+        <v>0.6264783929704001</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.205434792305447</v>
+        <v>4.294069511272992</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.007685179349275</v>
+        <v>-4.753477585305188</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.93379007831144</v>
+        <v>2.035473115929076</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.519893156224456</v>
+        <v>0.6676176878370309</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.249156468099572</v>
+        <v>4.337791187067117</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.911050267330635</v>
+        <v>-4.656842673286548</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.788628039242831</v>
+        <v>1.890311076860466</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6165280682430959</v>
+        <v>0.7642525998556708</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.123321411434691</v>
+        <v>4.211956130402235</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.041631001861478</v>
+        <v>-4.78742340781739</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.739897789504458</v>
+        <v>1.841580827122093</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4859473337122534</v>
+        <v>0.6336718653248283</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.048475014790148</v>
+        <v>4.137109733757693</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.877134667670516</v>
+        <v>-4.622927073626428</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.790123142256925</v>
+        <v>1.89180617987456</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4859473337122534</v>
+        <v>0.6336718653248283</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.032901833866231</v>
+        <v>4.121536552833776</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.904504600354948</v>
+        <v>-4.65029700631086</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.778362879619582</v>
+        <v>1.880045917237217</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4859473337122534</v>
+        <v>0.6336718653248283</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.032089544302661</v>
+        <v>4.120724263270206</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.914889795244838</v>
+        <v>-4.66068220120075</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.784077580788698</v>
+        <v>1.885760618406334</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4755621388223641</v>
+        <v>0.623286670434939</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.035727206493799</v>
+        <v>4.124361925461344</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.933477953967063</v>
+        <v>-4.679270359922975</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.847479323076234</v>
+        <v>1.949162360693869</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4569739801001387</v>
+        <v>0.6046985117127137</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09541131703689</v>
+        <v>4.184046036004434</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.933776500663098</v>
+        <v>-4.679568906619011</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.844228915216118</v>
+        <v>1.945911952833753</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4569739801001387</v>
+        <v>0.6046985117127137</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.092280327855188</v>
+        <v>4.180915046822733</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.832953366972671</v>
+        <v>-4.578745772928583</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.88908906363168</v>
+        <v>1.990772101249315</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4694381955844926</v>
+        <v>0.6171627271970676</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.104289752085192</v>
+        <v>4.192924471052737</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.642172006220264</v>
+        <v>-4.387964412176176</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.965530861411186</v>
+        <v>2.067213899028821</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6602195563369</v>
+        <v>0.8079440879494749</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.218887822015179</v>
+        <v>4.307522540982724</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.623655152178443</v>
+        <v>-4.369447558134356</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.952774448765511</v>
+        <v>2.054457486383146</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6731496857621082</v>
+        <v>0.8208742173746831</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.206482745407901</v>
+        <v>4.295117464375446</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.598461967677125</v>
+        <v>-4.344254373633038</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.997818659178097</v>
+        <v>2.099501696795732</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6983428702634266</v>
+        <v>0.8460674018760015</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.25656559272075</v>
+        <v>4.345200311688295</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.586407840764163</v>
+        <v>-4.332200246720075</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.996326877844719</v>
+        <v>2.098009915462355</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7103969971763894</v>
+        <v>0.8581215287889643</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.257484636769965</v>
+        <v>4.34611935573751</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.593031087454521</v>
+        <v>-4.338823493410433</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.995558209352712</v>
+        <v>2.097241246970347</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7037737504860311</v>
+        <v>0.8514982820986059</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.255391318939886</v>
+        <v>4.344026037907431</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.490150497925928</v>
+        <v>-4.23594290388184</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.049561471042032</v>
+        <v>2.151244508659667</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.806654340014624</v>
+        <v>0.9543788716271988</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.329970698534924</v>
+        <v>4.418605417502469</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.513592537106015</v>
+        <v>-4.259384943061927</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.060387325543591</v>
+        <v>2.162070363161226</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.806654340014624</v>
+        <v>0.9543788716271988</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.350173368708519</v>
+        <v>4.438808087676064</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.531665045397626</v>
+        <v>-4.277457451353539</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.053158322226946</v>
+        <v>2.154841359844582</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.806654340014624</v>
+        <v>0.9543788716271988</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.350173368708519</v>
+        <v>4.438808087676064</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.762838839274258</v>
+        <v>-4.508631245230171</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.92094071826976</v>
+        <v>2.022623755887396</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.806654340014624</v>
+        <v>0.9543788716271988</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.310425282301986</v>
+        <v>4.399060001269531</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.731552818733803</v>
+        <v>-4.477345224689715</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.940477745482883</v>
+        <v>2.042160783100518</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8379403605550794</v>
+        <v>0.9856648921676542</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.336219513623199</v>
+        <v>4.424854232590744</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.578527426620519</v>
+        <v>-4.324319832576431</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.1008589019011</v>
+        <v>2.202541939518735</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9909657526683635</v>
+        <v>1.138690284280938</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.527205748464073</v>
+        <v>4.615840467431618</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.606834740493789</v>
+        <v>-4.352627146449701</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.277002201260085</v>
+        <v>2.37868523887772</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9909657526683635</v>
+        <v>1.138690284280938</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.714671973372366</v>
+        <v>4.803306692339911</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.773427965607311</v>
+        <v>-4.519220371563224</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.179767862568758</v>
+        <v>2.281450900186393</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.824372527554841</v>
+        <v>0.9720970591674158</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.584118989658335</v>
+        <v>4.67275370862588</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.600363586225011</v>
+        <v>-4.346155992180924</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.252670016983396</v>
+        <v>2.354353054601031</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.824372527554841</v>
+        <v>0.9720970591674158</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.587795392320053</v>
+        <v>4.676430111287598</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.571117605769315</v>
+        <v>-4.316910011725227</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.26198646428917</v>
+        <v>2.363669501906805</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.824372527554841</v>
+        <v>0.9720970591674158</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.585413447443548</v>
+        <v>4.674048166411093</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.678043153647166</v>
+        <v>-4.423835559603078</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.216509484295664</v>
+        <v>2.318192521913299</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7174469796769897</v>
+        <v>0.8651715112895645</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.518551357874472</v>
+        <v>4.607186076842017</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983736</v>
+        <v>3.689962785983738</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.823061712154415</v>
+        <v>-4.568854118110327</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.159930863035999</v>
+        <v>2.261613900653634</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5724284211697411</v>
+        <v>0.7201529527823159</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.432969024913357</v>
+        <v>4.521603743880902</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.864080250139895</v>
+        <v>3.935050020393827</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.264207686147855</v>
+        <v>4.437342881205361</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.823061712154415</v>
+        <v>-4.568854118110327</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.159930863035999</v>
+        <v>2.261613900653634</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5724284211697411</v>
+        <v>0.7201529527823159</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.257271483134223</v>
+        <v>4.430406678191729</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>84.2%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>32.9%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>80.5%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>33.6%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>132.1%</t>
+          <t>119.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-45.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.7%</t>
+          <t>428.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-618.5%</t>
+          <t>-633.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.1%</t>
+          <t>-133.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-335.7%</t>
+          <t>-278.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-167.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317609</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783972</v>
+        <v>3.833252747839719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.296796316350473</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.2323850232493179</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.7906484935996724</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.677070877943451</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626469</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.133396445411111</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.2971117928458198</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.6272486226603099</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.774477621727826</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-6.899915223181512</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.3984287105755113</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.3937674004307113</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.922490783903437</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.750248832173997</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.4554030566655585</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.3008639091881754</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.975340668336</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.617973358543111</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.50368073286494</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.1685884355572888</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>3.050073439261558</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.462235025983369</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.5687911265764733</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.01285010299754719</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.14633149948504</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.37727035925405</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.6156833344918597</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>0.07211456373177239</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.210216640746291</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.482860349027154</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.4454714089833995</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.03347542604133197</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>3.018886717283209</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.414625764401727</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.5213095847106568</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.01506010316879597</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>3.078480252883817</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.266685722994128</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.460606678585529</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>0.005260812739761589</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.970793879740784</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.213716200740139</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.4730805012336461</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.05823033499375047</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.9938616068397</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.047928004779848</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.5324351675226691</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.05823033499375047</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.986900994744607</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-6.014564798301079</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.5602428044953198</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.05823033499375047</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>3.00136334912575</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-5.906305661178558</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.5980785798035235</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.05823033499375047</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.995895469584945</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-5.783014526361427</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.6448931277409526</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.181521469810881</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>3.0673682444858</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-5.730317659230136</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.6736728528307947</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.2342183369421721</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>3.1066873430019</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.486552217246691</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.7669597379712227</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.2342183369421721</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>3.10246805134895</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.396776544870219</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.804994320841828</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.2958177818564822</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.141552032217552</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.146926150921145</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.8976765534051596</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.2958177818564822</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.134294107201255</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-4.971034058453712</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.9716325139127813</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.2958177818564822</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.137893230721903</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-4.799587595431249</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>1.05353860517632</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.4672642448789453</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.254088614589935</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.855365915877906</v>
+        <v>-4.719565308322128</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.030247754613955</v>
+        <v>1.084567997636266</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.5472865319880662</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.301122464471704</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.791730173643971</v>
+        <v>-4.655929566088194</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.060396852561846</v>
+        <v>1.114717095584157</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.6109222742220007</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.343998710866382</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.698032855427576</v>
+        <v>-4.562232247871798</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.079070038632199</v>
+        <v>1.133390281654511</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.6109222742220007</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.325192969650178</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.708535478492865</v>
+        <v>-4.572734870937087</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.076612066030961</v>
+        <v>1.130932309053272</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.6004196511567119</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.320634472435882</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.636292910321671</v>
+        <v>-4.500492302765893</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.109438407134259</v>
+        <v>1.16375865015657</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.6004196511567119</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.324563786270702</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.618579223443805</v>
+        <v>-4.482778615888027</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.117202465802746</v>
+        <v>1.171522708825057</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.6036009800536287</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.327151167526192</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.509774337964078</v>
+        <v>-4.3739737304083</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.15772249121463</v>
+        <v>1.212042734236941</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.6036009800536287</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.324149238746186</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.289753539927068</v>
+        <v>-4.254933952413722</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.247309847440048</v>
+        <v>1.261237682445387</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6729916395593221</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.367362671460216</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539946</v>
+        <v>3.843274527539943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.122066263350444</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.330278940872521</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6729916395593221</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.383256854262039</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-4.001893179985945</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.379494018658622</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.793164722923821</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.45650654872104</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.866639818655968</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.443683465752053</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.9284180842537981</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.547746668080467</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.92651464601366</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.405771026210402</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.868543256896106</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.497859263067277</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.806694415102823</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.468988287808945</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.868543256896106</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.513148432301485</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.809164121564629</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.375644604546665</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.8660735504342998</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.419310807746843</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.877534307888639</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.267558391502362</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8753492494705147</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.344138088653874</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.891322360735685</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.252479878995435</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8753492494705147</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.334574797285765</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-3.946842436628275</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.367302685330601</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8753492494705147</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.471605633977967</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.771368176835806</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.442059621239377</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8753492494705147</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.476172865969755</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225437</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.798263389764238</v>
+        <v>-3.763443802250892</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.407043564829211</v>
+        <v>1.420971399834549</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.8753492494705147</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.451914894730963</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.764599844291956</v>
+        <v>-3.72978025677861</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.349047296419573</v>
+        <v>1.362975131424912</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.9090127949427966</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.362268482219687</v>
+        <v>3.400651335415781</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.704747225088233</v>
+        <v>-3.669927637574887</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.383160730533195</v>
+        <v>1.397088565538533</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.9090127949427966</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.372440868651819</v>
+        <v>3.410823721847914</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.618503762061855</v>
+        <v>-3.583684174548509</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.412604386317607</v>
+        <v>1.426532221322945</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.9090127949427966</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.367387139225679</v>
+        <v>3.405769992421774</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.663810581460835</v>
+        <v>-3.628990993947489</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.38625743400254</v>
+        <v>1.400185269007879</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8682026319335658</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.334676816864667</v>
+        <v>3.373059670060761</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.692843686163136</v>
+        <v>-3.65802409864979</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.375196065154721</v>
+        <v>1.389123900160059</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8682026319335658</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.335228689897768</v>
+        <v>3.373611543093863</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.600033204712277</v>
+        <v>-3.565213617198931</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.34159294962643</v>
+        <v>1.355520784631769</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8970416913909339</v>
+        <v>0.9610131133844252</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.320187670659649</v>
+        <v>3.358570523855744</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.644422674041705</v>
+        <v>-3.609603086528359</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.32571063781926</v>
+        <v>1.339638472824599</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8526522220615063</v>
+        <v>0.9166236440549975</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.295427464986593</v>
+        <v>3.333810318182688</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.760964279147048</v>
+        <v>-3.726144691633702</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.274169704288846</v>
+        <v>1.288097539294184</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.8000820389496548</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220578210435111</v>
+        <v>3.258961063631205</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.800888373729619</v>
+        <v>-3.766068786216273</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.263691362286484</v>
+        <v>1.277619197291823</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.8000820389496548</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.226069506265778</v>
+        <v>3.264452359461873</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.828668771630972</v>
+        <v>-3.793849184117626</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.264076404894482</v>
+        <v>1.278004239899821</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7083302190548104</v>
+        <v>0.7723016410483017</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220898469293505</v>
+        <v>3.2592813224896</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.947049444361111</v>
+        <v>-3.912229856847765</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.05507985580308</v>
+        <v>1.069007690808419</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.7050837888973255</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018923478003573</v>
+        <v>3.057306331199667</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.055663522804442</v>
+        <v>-4.020843935291095</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.131783885144953</v>
+        <v>1.145711720150292</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.7050837888973255</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.139073138722778</v>
+        <v>3.177455991918873</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.0202544845563</v>
+        <v>-3.985434897042953</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.160460526546534</v>
+        <v>1.174388361551872</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.7050837888973255</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153586164825101</v>
+        <v>3.191969018021196</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.981870821998148</v>
+        <v>-3.947051234484801</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.173233432912163</v>
+        <v>1.187161267917501</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7434674514554767</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.174035803702361</v>
+        <v>3.212418656898456</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.804754491962982</v>
+        <v>-3.769934904449635</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.240808993771531</v>
+        <v>1.25473682877687</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7434674514554767</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170764832547663</v>
+        <v>3.209147685743758</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.849846736796528</v>
+        <v>-3.815027149283181</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.223455487600026</v>
+        <v>1.237383322605365</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6175999862925956</v>
+        <v>0.6815714082860869</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134310598407942</v>
+        <v>3.172693451604037</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.67047131555776</v>
+        <v>-3.635651728044413</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.288992631401947</v>
+        <v>1.302920466407286</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7743767444633143</v>
+        <v>0.8383481664568055</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.222163628616787</v>
+        <v>3.260546481812882</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.715485529078367</v>
+        <v>-3.68066594156502</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.251794401325294</v>
+        <v>1.265722236330633</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7440278491487097</v>
+        <v>0.8079992711422009</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.184761746759615</v>
+        <v>3.223144599955709</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.728282445306716</v>
+        <v>-3.947670451837455</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.2523671971729</v>
+        <v>1.164611994560605</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6973893427183362</v>
+        <v>0.6136362330992524</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.162470205240336</v>
+        <v>3.112218339468886</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.829480226743889</v>
+        <v>-4.048868233274628</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.211092006494533</v>
+        <v>1.123336803882237</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.6289805291730171</v>
+        <v>0.5452274195539333</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.120628839009646</v>
+        <v>3.070376973238196</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.822969260129577</v>
+        <v>-4.042357266660315</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.211296354694574</v>
+        <v>1.123541152082279</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.6289805291730171</v>
+        <v>0.5452274195539333</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.118228800563963</v>
+        <v>3.067976934792513</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.803931132422279</v>
+        <v>-4.023319138953018</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.215436324985738</v>
+        <v>1.127681122373443</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5707969178418225</v>
+        <v>0.4870438082227387</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.079843352973491</v>
+        <v>3.029591487202041</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.856446934697099</v>
+        <v>-4.075834941227838</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.313724405710001</v>
+        <v>1.225969203097705</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5707969178418225</v>
+        <v>0.4870438082227387</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.199137754607681</v>
+        <v>3.148885888836231</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.870313696031017</v>
+        <v>-4.089701702561756</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.309011030162567</v>
+        <v>1.221255827550271</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5329390011079995</v>
+        <v>0.4491858914889158</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.177256333553521</v>
+        <v>3.127004467782071</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.825509524491087</v>
+        <v>-4.044897531021826</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.332941229175465</v>
+        <v>1.245186026563169</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5329390011079995</v>
+        <v>0.4491858914889158</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.183264863950447</v>
+        <v>3.133012998178997</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.677766554256085</v>
+        <v>-3.897154560786824</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.289988638546665</v>
+        <v>1.20223343593437</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.7007463583428827</v>
+        <v>0.616993248723799</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.181899499568576</v>
+        <v>3.131647633797126</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.761587775530783</v>
+        <v>-3.980975782061522</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.259253771568267</v>
+        <v>1.171498568955971</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.7007463583428827</v>
+        <v>0.616993248723799</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.184693121100057</v>
+        <v>3.134441255328607</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.755435069477998</v>
+        <v>-3.974823076008738</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.262377202381039</v>
+        <v>1.174621999768743</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.706899064395667</v>
+        <v>0.6231459547765833</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.189047093123386</v>
+        <v>3.138795227351936</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.7722443676285</v>
+        <v>-3.991632374159239</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.254733959860949</v>
+        <v>1.166978757248653</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6900897662451653</v>
+        <v>0.6063366566260817</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.178041990973195</v>
+        <v>3.127790125201745</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.709946368852378</v>
+        <v>-3.929334375383117</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.345988713168218</v>
+        <v>1.258233510555923</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7353840305196073</v>
+        <v>0.6516309209005238</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.271554103334682</v>
+        <v>3.221302237563231</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.50815617118722</v>
+        <v>-3.727544177717959</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.228996793948409</v>
+        <v>1.141241591336113</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9334022226887617</v>
+        <v>0.8496491130696782</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.192657020350302</v>
+        <v>3.142405154578851</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.559042883873415</v>
+        <v>-3.778430890404154</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.278932341196106</v>
+        <v>1.19117713858381</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8825155100025672</v>
+        <v>0.7987624003834837</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.23241522506076</v>
+        <v>3.182163359289309</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.472432141223607</v>
+        <v>-3.691820147754347</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.328204374372073</v>
+        <v>1.240449171759777</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9611412412077255</v>
+        <v>0.8773881315886419</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.294218399899898</v>
+        <v>3.243966534128448</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.532641439228892</v>
+        <v>-3.752029445759631</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.302656635994631</v>
+        <v>1.214901433382335</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.900931943202441</v>
+        <v>0.8171788335833574</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.2566288019214</v>
+        <v>3.206376936149949</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.456219392796965</v>
+        <v>-3.675607399327705</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.33171707260733</v>
+        <v>1.243961869995034</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.900931943202441</v>
+        <v>0.8171788335833574</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.255120419961328</v>
+        <v>3.204868554189878</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.411846261158396</v>
+        <v>-3.631234267689136</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.349329192698193</v>
+        <v>1.261573990085898</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9453050748410096</v>
+        <v>0.861551965221926</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.281607166379906</v>
+        <v>3.231355300608455</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.434326612017281</v>
+        <v>-3.653714618548021</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.33473084649323</v>
+        <v>1.246975643880934</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9453050748410096</v>
+        <v>0.861551965221926</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.276000960518496</v>
+        <v>3.225749094747046</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.386670881456226</v>
+        <v>-3.606058887986965</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.360174895745457</v>
+        <v>1.272419693133161</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9929608054020651</v>
+        <v>0.9092076957829817</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.310976155882934</v>
+        <v>3.260724290111484</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.286152722957471</v>
+        <v>-3.50554072948821</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.405274532519684</v>
+        <v>1.317519329907388</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.09347896390082</v>
+        <v>1.009725854281736</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.376179424356911</v>
+        <v>3.325927558585462</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.270247393525119</v>
+        <v>-3.489635400055858</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.398391336768497</v>
+        <v>1.310636134156201</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.014366303191581</v>
+        <v>0.9306131935724973</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.31546650040724</v>
+        <v>3.26521463463579</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.225408991916721</v>
+        <v>-3.44479699844746</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.420424400022485</v>
+        <v>1.332669197410189</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.01890973613645</v>
+        <v>0.9351566265173668</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.322290262784791</v>
+        <v>3.272038397013341</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.244907448158729</v>
+        <v>-3.464295454689468</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.416785957156759</v>
+        <v>1.329030754544464</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.970825094856546</v>
+        <v>0.8870719852374624</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.297600417647926</v>
+        <v>3.247348551876476</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.200704611072828</v>
+        <v>-3.420092617603567</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.440346694518957</v>
+        <v>1.352591491906661</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.015027931942446</v>
+        <v>0.9312748223233629</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.330001722427304</v>
+        <v>3.279749856655853</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.208264276909875</v>
+        <v>-3.427652283440614</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.435732828653385</v>
+        <v>1.34797762604109</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.069831335952266</v>
+        <v>0.9860782263331822</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.361293765302443</v>
+        <v>3.311041899530992</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.049972859370603</v>
+        <v>-3.269360865901342</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.550297160852134</v>
+        <v>1.462541958239838</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.069831335952266</v>
+        <v>0.9860782263331822</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.412541530485482</v>
+        <v>3.362289664714032</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.842330855736127</v>
+        <v>-3.061718862266866</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.631794666900178</v>
+        <v>1.544039464287882</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.277473339586742</v>
+        <v>1.193720229967658</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.535567437260421</v>
+        <v>3.485315571488971</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.791298763013599</v>
+        <v>-3.010686769544338</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.647155732227459</v>
+        <v>1.559400529615163</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.32850543230927</v>
+        <v>1.244752322690186</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.561134921132208</v>
+        <v>3.510883055360758</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.726074581886393</v>
+        <v>-2.945462588417132</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.690432808771046</v>
+        <v>1.60267760615875</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.393729613436476</v>
+        <v>1.309976503817392</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.617456833901236</v>
+        <v>3.567204968129786</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.688647561815259</v>
+        <v>-2.908035568345998</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.70136458909878</v>
+        <v>1.613609386486484</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.398981151465657</v>
+        <v>1.315228041846574</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.616568729018026</v>
+        <v>3.566316863246575</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.666082764757094</v>
+        <v>-2.928147224380707</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.711647300253286</v>
+        <v>1.606821516403841</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.484716443934626</v>
+        <v>1.326255386843993</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.669266696830647</v>
+        <v>3.574190062576267</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.612337950329889</v>
+        <v>-2.874402409953502</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.893702997045379</v>
+        <v>1.788877213195934</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.494779753375088</v>
+        <v>1.336318696284455</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.835862453516135</v>
+        <v>3.740785819261755</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.537555689304877</v>
+        <v>-2.799620148928489</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.043728810673201</v>
+        <v>1.938903026823756</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.569562014400101</v>
+        <v>1.411100957309467</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.00084471934896</v>
+        <v>3.90576808509458</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.511471605041069</v>
+        <v>-2.773536064664681</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.045870420392584</v>
+        <v>1.941044636543138</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.569562014400101</v>
+        <v>1.411100957309467</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.992552695362819</v>
+        <v>3.897476061108439</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.423593691931948</v>
+        <v>-2.685658151555561</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.079214781220011</v>
+        <v>1.974388997370566</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.685487656823452</v>
+        <v>1.527026599732819</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.060301276400609</v>
+        <v>3.965224642146229</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.414701230538665</v>
+        <v>-2.676765690162277</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.100326171504116</v>
+        <v>1.995500387654671</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.685487656823452</v>
+        <v>1.527026599732819</v>
       </c>
       <c r="G1995" t="n">
-        <v>4.0778556821274</v>
+        <v>3.98277904787302</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.583177347508542</v>
+        <v>-2.845241807132155</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.024790772120749</v>
+        <v>1.919964988271304</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.657539821106871</v>
+        <v>1.499078764016238</v>
       </c>
       <c r="G1996" t="n">
-        <v>4.052942028102036</v>
+        <v>3.957865393847656</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.136921154879103</v>
+        <v>-2.398985614502715</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.184562946360387</v>
+        <v>2.079737162510941</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.562821151437239</v>
+        <v>1.404360094346605</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.977380523488119</v>
+        <v>3.882303889233738</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.11420005119595</v>
+        <v>-2.376264510819563</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.184315410330552</v>
+        <v>2.079489626481107</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.562821151437239</v>
+        <v>1.404360094346605</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.968044545985023</v>
+        <v>3.872967911730643</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.243401864489992</v>
+        <v>-2.505466324113605</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.291540810864104</v>
+        <v>2.186715027014659</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.433619338143197</v>
+        <v>1.275158281052563</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.049429583859767</v>
+        <v>3.954352949605386</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.398182871268248</v>
+        <v>-2.660247330891861</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.266706230646449</v>
+        <v>2.161880446797003</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.40025166408872</v>
+        <v>1.241790606998087</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.066486801920727</v>
+        <v>3.971410167666347</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.391128181053074</v>
+        <v>-2.653192640676687</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.266203462722063</v>
+        <v>2.161377678872618</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.407306354303894</v>
+        <v>1.248845297213261</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.067394972039377</v>
+        <v>3.972318337784997</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.364176956726586</v>
+        <v>-2.626241416350199</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.2869901060974</v>
+        <v>2.182164322247955</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.422186700331613</v>
+        <v>1.26372564324098</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.08632933330075</v>
+        <v>3.991252699046369</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.500129964782903</v>
+        <v>-2.762194424406515</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.416712035019833</v>
+        <v>2.311886251170388</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.422186700331613</v>
+        <v>1.26372564324098</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.27043246544571</v>
+        <v>4.17535583119133</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.522538082587775</v>
+        <v>-2.784602542211387</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.399865482800878</v>
+        <v>2.295039698951432</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.422186700331613</v>
+        <v>1.26372564324098</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.262549160348703</v>
+        <v>4.167472526094323</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.550762318165375</v>
+        <v>-2.812826777788988</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.390629788119475</v>
+        <v>2.285804004270029</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.440163452782922</v>
+        <v>1.281702395692288</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.275389211369125</v>
+        <v>4.180312577114745</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.560203244053905</v>
+        <v>-2.822267703677518</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.44310713548591</v>
+        <v>2.338281351636465</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.562590570326313</v>
+        <v>1.40412951323568</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.405099199617007</v>
+        <v>4.310022565362627</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.612476851389546</v>
+        <v>-2.874541311013159</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.425088787096954</v>
+        <v>2.320263003247509</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.510316962990672</v>
+        <v>1.351855905900039</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.376626129760924</v>
+        <v>4.281549495506543</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.688806828990452</v>
+        <v>-2.950871288614065</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.392668608950367</v>
+        <v>2.287842825100922</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.510316962990672</v>
+        <v>1.351855905900039</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.374737942654699</v>
+        <v>4.279661308400319</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.891060549314806</v>
+        <v>-3.153125008938418</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.306587350423488</v>
+        <v>2.201761566574043</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.308063242666319</v>
+        <v>1.149602185575685</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.248205940062949</v>
+        <v>4.153129305808569</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.052628974842061</v>
+        <v>-3.314693434465673</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.240393990422738</v>
+        <v>2.135568206573293</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.181280318868439</v>
+        <v>1.022819261777806</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.170570195994373</v>
+        <v>4.075493561739994</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.184930266939614</v>
+        <v>-3.446994726563227</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.200546880449636</v>
+        <v>2.09572109660019</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.181280318868439</v>
+        <v>1.022819261777806</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.183643602860292</v>
+        <v>4.088566968605912</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378395</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.370798577778844</v>
+        <v>-3.632863037402457</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.118204752896883</v>
+        <v>2.013378969047438</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.022714725548492</v>
+        <v>0.8642536684578581</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.080509443651263</v>
+        <v>3.985432809396883</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006978</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.398699364888317</v>
+        <v>-3.66076382451193</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.105568479180096</v>
+        <v>2.000742695330652</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9881178014055568</v>
+        <v>0.8296567443149233</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.058275330292505</v>
+        <v>3.963198696038124</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.521225467591211</v>
+        <v>-3.783289927214823</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.053322482076138</v>
+        <v>1.948496698226692</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8655916987026629</v>
+        <v>0.7071306416120294</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.981524112647967</v>
+        <v>3.886447478393587</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61934808158594</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.751739963776799</v>
+        <v>-4.013804423400412</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.027822643192406</v>
+        <v>1.922996859342961</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6350772025170742</v>
+        <v>0.4766161454264407</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.909921374527118</v>
+        <v>3.814844740272738</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.008460781771623</v>
+        <v>-4.270525241395235</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.065446034996323</v>
+        <v>1.960620251146878</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5266626283732594</v>
+        <v>0.3682015712826259</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.985184349042676</v>
+        <v>3.890107714788296</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.162447199547763</v>
+        <v>-4.424511659171376</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.072831737031507</v>
+        <v>1.968005953182062</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5266626283732594</v>
+        <v>0.3682015712826259</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.054164618188316</v>
+        <v>3.959087983933935</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.111925295720098</v>
+        <v>-4.37398975534371</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.079091700682694</v>
+        <v>1.974265916833249</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5266626283732594</v>
+        <v>0.3682015712826259</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.040215820308436</v>
+        <v>3.945139186054057</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.364400449727822</v>
+        <v>-4.626464909351435</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.989972128135018</v>
+        <v>1.885146344285574</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5266626283732594</v>
+        <v>0.3682015712826259</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.05208630936385</v>
+        <v>3.957009675109471</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.657296206207234</v>
+        <v>-4.919360665830847</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.874024360062197</v>
+        <v>1.769198576212752</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5266626283732594</v>
+        <v>0.3682015712826259</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.053296843882794</v>
+        <v>3.958220209628414</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.843960334342042</v>
+        <v>-5.106024793965655</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.803480451035596</v>
+        <v>1.698654667186151</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4999236575486995</v>
+        <v>0.341462600458066</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.04137520361538</v>
+        <v>3.946298569361</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.989981021256004</v>
+        <v>-5.252045480879617</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.7401500290062</v>
+        <v>1.635324245156755</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4908405657548425</v>
+        <v>0.332379508664209</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.031003201275255</v>
+        <v>3.935926567020875</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.106948713894895</v>
+        <v>-5.369013173518508</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.855567008649688</v>
+        <v>1.750741224800243</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4908405657548425</v>
+        <v>0.332379508664209</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.193207257974299</v>
+        <v>4.098130623719919</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.191666656115848</v>
+        <v>-5.453731115739461</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.816526469725121</v>
+        <v>1.711700685875676</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4057245368267961</v>
+        <v>0.2472634797361626</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.136984278581285</v>
+        <v>4.041907644326905</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868148</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.273601474384732</v>
+        <v>-5.535665934008344</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.793981959986059</v>
+        <v>1.689156176136613</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3957897912397159</v>
+        <v>0.2373287341490825</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.141252848797528</v>
+        <v>4.046176214543149</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.375577596633139</v>
+        <v>-5.637642056256752</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.762117149542598</v>
+        <v>1.657291365693153</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2938136689913083</v>
+        <v>0.1353526119006749</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.088992813904386</v>
+        <v>3.993916179650006</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.265571313155918</v>
+        <v>-5.52763577277953</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.798272550177662</v>
+        <v>1.693446766328217</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3170182409085835</v>
+        <v>0.1585571838179501</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.095068444298927</v>
+        <v>3.999991810044547</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.122511737414992</v>
+        <v>-5.384576197038605</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.859746391196007</v>
+        <v>1.754920607346561</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3250316674985628</v>
+        <v>0.1665706104079294</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.104126510974889</v>
+        <v>4.009049876720509</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.821065011943155</v>
+        <v>-5.083129471566767</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.987585964267278</v>
+        <v>1.882760180417832</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6264783929704001</v>
+        <v>0.4680173358797666</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.292255429140527</v>
+        <v>4.197178794886147</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.845655256178339</v>
+        <v>-5.107719715801951</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.978721044325915</v>
+        <v>1.873895260476469</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6264783929704001</v>
+        <v>0.4680173358797666</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.293226606893238</v>
+        <v>4.198149972638857</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.794616880171819</v>
+        <v>-5.056681339795431</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.999979299108277</v>
+        <v>1.895153515258833</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6264783929704001</v>
+        <v>0.4680173358797666</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.294069511272992</v>
+        <v>4.198992877018613</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.753477585305188</v>
+        <v>-5.0155420449288</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.035473115929076</v>
+        <v>1.93064733207963</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6676176878370309</v>
+        <v>0.5091566307463975</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.337791187067117</v>
+        <v>4.242714552812736</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.656842673286548</v>
+        <v>-4.91890713291016</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.890311076860466</v>
+        <v>1.785485293011021</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7642525998556708</v>
+        <v>0.6057915427650374</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.211956130402235</v>
+        <v>4.116879496147855</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.78742340781739</v>
+        <v>-5.049487867441003</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.841580827122093</v>
+        <v>1.736755043272648</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6336718653248283</v>
+        <v>0.4752108082341949</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.137109733757693</v>
+        <v>4.042033099503313</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.622927073626428</v>
+        <v>-4.884991533250041</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.89180617987456</v>
+        <v>1.786980396025115</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6336718653248283</v>
+        <v>0.4752108082341949</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.121536552833776</v>
+        <v>4.026459918579396</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.65029700631086</v>
+        <v>-4.912361465934473</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.880045917237217</v>
+        <v>1.775220133387772</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6336718653248283</v>
+        <v>0.4752108082341949</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.120724263270206</v>
+        <v>4.025647629015825</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.66068220120075</v>
+        <v>-4.922746660824362</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.885760618406334</v>
+        <v>1.780934834556889</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.623286670434939</v>
+        <v>0.4648256133443056</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.124361925461344</v>
+        <v>4.029285291206964</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.679270359922975</v>
+        <v>-4.941334819546587</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.949162360693869</v>
+        <v>1.844336576844424</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6046985117127137</v>
+        <v>0.4462374546220803</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.184046036004434</v>
+        <v>4.088969401750054</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.679568906619011</v>
+        <v>-4.941633366242623</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.945911952833753</v>
+        <v>1.841086168984308</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6046985117127137</v>
+        <v>0.4462374546220803</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.180915046822733</v>
+        <v>4.085838412568353</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.578745772928583</v>
+        <v>-4.840810232552196</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.990772101249315</v>
+        <v>1.88594631739987</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6171627271970676</v>
+        <v>0.4587016701064341</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.192924471052737</v>
+        <v>4.097847836798357</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.387964412176176</v>
+        <v>-4.650028871799789</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.067213899028821</v>
+        <v>1.962388115179377</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8079440879494749</v>
+        <v>0.6494830308588415</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.307522540982724</v>
+        <v>4.212445906728345</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.369447558134356</v>
+        <v>-4.631512017757968</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.054457486383146</v>
+        <v>1.949631702533701</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8208742173746831</v>
+        <v>0.6624131602840497</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.295117464375446</v>
+        <v>4.200040830121066</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.344254373633038</v>
+        <v>-4.60631883325665</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.099501696795732</v>
+        <v>1.994675912946287</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8460674018760015</v>
+        <v>0.6876063447853681</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.345200311688295</v>
+        <v>4.250123677433916</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.332200246720075</v>
+        <v>-4.594264706343687</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.098009915462355</v>
+        <v>1.993184131612909</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8581215287889643</v>
+        <v>0.6996604716983309</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.34611935573751</v>
+        <v>4.251042721483131</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.338823493410433</v>
+        <v>-4.600887953034046</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.097241246970347</v>
+        <v>1.992415463120902</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8514982820986059</v>
+        <v>0.6930372250079726</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.344026037907431</v>
+        <v>4.248949403653052</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.23594290388184</v>
+        <v>-4.498007363505453</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.151244508659667</v>
+        <v>2.046418724810222</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9543788716271988</v>
+        <v>0.7959178145365655</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.418605417502469</v>
+        <v>4.32352878324809</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.259384943061927</v>
+        <v>-4.52144940268554</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.162070363161226</v>
+        <v>2.057244579311782</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9543788716271988</v>
+        <v>0.7959178145365655</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.438808087676064</v>
+        <v>4.343731453421684</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.277457451353539</v>
+        <v>-4.539521910977151</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.154841359844582</v>
+        <v>2.050015575995137</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9543788716271988</v>
+        <v>0.7959178145365655</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.438808087676064</v>
+        <v>4.343731453421684</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.508631245230171</v>
+        <v>-4.770695704853783</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.022623755887396</v>
+        <v>1.91779797203795</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9543788716271988</v>
+        <v>0.7959178145365655</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.399060001269531</v>
+        <v>4.30398336701515</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.477345224689715</v>
+        <v>-4.739409684313328</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.042160783100518</v>
+        <v>1.937334999251072</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9856648921676542</v>
+        <v>0.8272038350770209</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.424854232590744</v>
+        <v>4.329777598336364</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.324319832576431</v>
+        <v>-4.586384292200044</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.202541939518735</v>
+        <v>2.09771615566929</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.138690284280938</v>
+        <v>0.980229227190305</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.615840467431618</v>
+        <v>4.520763833177238</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.352627146449701</v>
+        <v>-4.614691606073314</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.37868523887772</v>
+        <v>2.273859455028274</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.138690284280938</v>
+        <v>0.980229227190305</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.803306692339911</v>
+        <v>4.708230058085531</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.519220371563224</v>
+        <v>-4.781284831186836</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.281450900186393</v>
+        <v>2.176625116336948</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9720970591674158</v>
+        <v>0.8136360020767825</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.67275370862588</v>
+        <v>4.5776770743715</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.346155992180924</v>
+        <v>-4.608220451804536</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.354353054601031</v>
+        <v>2.249527270751586</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9720970591674158</v>
+        <v>0.8136360020767825</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.676430111287598</v>
+        <v>4.581353477033217</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.316910011725227</v>
+        <v>-4.57897447134884</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.363669501906805</v>
+        <v>2.25884371805736</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9720970591674158</v>
+        <v>0.8136360020767825</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.674048166411093</v>
+        <v>4.578971532156713</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.423835559603078</v>
+        <v>-4.685900019226691</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.318192521913299</v>
+        <v>2.213366738063854</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8651715112895645</v>
+        <v>0.7067104541989312</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.607186076842017</v>
+        <v>4.512109442587636</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.568854118110327</v>
+        <v>-4.830918577733939</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.261613900653634</v>
+        <v>2.156788116804189</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7201529527823159</v>
+        <v>0.5616918956916827</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.521603743880902</v>
+        <v>4.426527109626522</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.935050020393827</v>
+        <v>3.552240899647581</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.437342881205361</v>
+        <v>4.314362672757079</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.568854118110327</v>
+        <v>-4.723727364555519</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.261613900653634</v>
+        <v>2.424515302621124</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7201529527823159</v>
+        <v>0.5616918956916827</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.430406678191729</v>
+        <v>4.65137781017209</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240816.xlsx
+++ b/tame_output/ON/bt/strategyON_20240816.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>119.8%</t>
+          <t>96.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>428.5%</t>
+          <t>428.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-633.9%</t>
+          <t>-645.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-133.8%</t>
+          <t>-161.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-278.1%</t>
+          <t>-323.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-179.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>-11.0%</t>
         </is>
       </c>
     </row>
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.296796316350473</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2323850232493179</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.7906484935996724</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.677070877943451</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.133396445411111</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2971117928458198</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.6272486226603099</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.774477621727826</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.899915223181512</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3984287105755113</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.3937674004307113</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.922490783903437</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.750248832173997</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4554030566655585</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.3008639091881754</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.975340668336</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.617973358543111</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.50368073286494</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.1685884355572888</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.050073439261558</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.462235025983369</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5687911265764733</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.01285010299754719</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.14633149948504</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.37727035925405</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6156833344918597</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.07211456373177239</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.210216640746291</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.482860349027154</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4454714089833995</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.03347542604133197</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.018886717283209</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.414625764401727</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5213095847106568</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.01506010316879597</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.078480252883817</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.266685722994128</v>
+        <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.460606678585529</v>
+        <v>0.4062864355632176</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.005260812739761589</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.970793879740784</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.213716200740139</v>
+        <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4730805012336461</v>
+        <v>0.4187602582113348</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.05823033499375047</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.9938616068397</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.047928004779848</v>
+        <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5324351675226691</v>
+        <v>0.4781149245003582</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.05823033499375047</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.986900994744607</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.014564798301079</v>
+        <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5602428044953198</v>
+        <v>0.5059225614730085</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.05823033499375047</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.00136334912575</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.906305661178558</v>
+        <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5980785798035235</v>
+        <v>0.5437583367812122</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.05823033499375047</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.995895469584945</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.783014526361427</v>
+        <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6448931277409526</v>
+        <v>0.5905728847186418</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.181521469810881</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.0673682444858</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.730317659230136</v>
+        <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6736728528307947</v>
+        <v>0.6193526098084834</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.2342183369421721</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.1066873430019</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.486552217246691</v>
+        <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7669597379712227</v>
+        <v>0.7126394949489119</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.2342183369421721</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.10246805134895</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.396776544870219</v>
+        <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.804994320841828</v>
+        <v>0.7506740778195167</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.2958177818564822</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.141552032217552</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.146926150921145</v>
+        <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8976765534051596</v>
+        <v>0.8433563103828488</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.2958177818564822</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.134294107201255</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.971034058453712</v>
+        <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9716325139127813</v>
+        <v>0.9173122708904704</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.2958177818564822</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.137893230721903</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.799587595431249</v>
+        <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.05353860517632</v>
+        <v>0.9992183621540094</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.4672642448789453</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.254088614589935</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.719565308322128</v>
+        <v>-4.855365915877906</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.084567997636266</v>
+        <v>1.030247754613955</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.5472865319880662</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.301122464471704</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.655929566088194</v>
+        <v>-4.791730173643971</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.114717095584157</v>
+        <v>1.060396852561846</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.6109222742220007</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.343998710866382</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.562232247871798</v>
+        <v>-4.698032855427576</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.133390281654511</v>
+        <v>1.079070038632199</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.6109222742220007</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.325192969650178</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.572734870937087</v>
+        <v>-4.708535478492865</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.130932309053272</v>
+        <v>1.076612066030961</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.6004196511567119</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.320634472435882</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.500492302765893</v>
+        <v>-4.636292910321671</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.16375865015657</v>
+        <v>1.109438407134259</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.6004196511567119</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.324563786270702</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.482778615888027</v>
+        <v>-4.618579223443805</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.171522708825057</v>
+        <v>1.117202465802746</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.6036009800536287</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.327151167526192</v>
+        <v>3.245670802992725</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.3739737304083</v>
+        <v>-4.509774337964078</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.212042734236941</v>
+        <v>1.15772249121463</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.6036009800536287</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.324149238746186</v>
+        <v>3.242668874212719</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.254933952413722</v>
+        <v>-4.369604591856575</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.261237682445387</v>
+        <v>1.215369426668245</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6729916395593221</v>
+        <v>0.553503887866188</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.367362671460216</v>
+        <v>3.295670020444335</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539943</v>
+        <v>3.843274527539944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.122066263350444</v>
+        <v>-4.236736902793298</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.330278940872521</v>
+        <v>1.284410685095379</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6729916395593221</v>
+        <v>0.553503887866188</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.383256854262039</v>
+        <v>3.311564203246159</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.001893179985945</v>
+        <v>-4.116563819428799</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.379494018658622</v>
+        <v>1.333625762881481</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.793164722923821</v>
+        <v>0.6736769712306869</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.45650654872104</v>
+        <v>3.38481389770516</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576993</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.866639818655968</v>
+        <v>-3.981310458098822</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.443683465752053</v>
+        <v>1.397815209974911</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.9284180842537981</v>
+        <v>0.808930332560664</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.547746668080467</v>
+        <v>3.476054017064586</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942099</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.92651464601366</v>
+        <v>-4.041185285456514</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.405771026210402</v>
+        <v>1.35990277043326</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.868543256896106</v>
+        <v>0.7490555052029719</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.497859263067277</v>
+        <v>3.426166612051396</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674509</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.806694415102823</v>
+        <v>-3.921365054545677</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.468988287808945</v>
+        <v>1.423120032031804</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.868543256896106</v>
+        <v>0.7490555052029719</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.513148432301485</v>
+        <v>3.441455781285605</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430688</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.809164121564629</v>
+        <v>-3.923834761007483</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.375644604546665</v>
+        <v>1.329776348769523</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8660735504342998</v>
+        <v>0.7465857987411657</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.419310807746843</v>
+        <v>3.347618156730963</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003595</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.877534307888639</v>
+        <v>-3.992204947331492</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.267558391502362</v>
+        <v>1.221690135725221</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8753492494705147</v>
+        <v>0.7558614977773807</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.344138088653874</v>
+        <v>3.272445437637994</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508364</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.891322360735685</v>
+        <v>-4.005993000178539</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.252479878995435</v>
+        <v>1.206611623218293</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8753492494705147</v>
+        <v>0.7558614977773807</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.334574797285765</v>
+        <v>3.262882146269884</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417698</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.946842436628275</v>
+        <v>-4.061513076071129</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.367302685330601</v>
+        <v>1.32143442955346</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8753492494705147</v>
+        <v>0.7558614977773807</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.471605633977967</v>
+        <v>3.399912982962087</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.771368176835806</v>
+        <v>-3.886038816278659</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.442059621239377</v>
+        <v>1.396191365462235</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8753492494705147</v>
+        <v>0.7558614977773807</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.476172865969755</v>
+        <v>3.404480214953875</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225437</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.763443802250892</v>
+        <v>-3.878114441693745</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.420971399834549</v>
+        <v>1.375103144057408</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8753492494705147</v>
+        <v>0.7558614977773807</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.451914894730963</v>
+        <v>3.380222243715082</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.72978025677861</v>
+        <v>-3.844450896221463</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.362975131424912</v>
+        <v>1.31710687564777</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.9090127949427966</v>
+        <v>0.7895250432496626</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.400651335415781</v>
+        <v>3.328958684399901</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.669927637574887</v>
+        <v>-3.78459827701774</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.397088565538533</v>
+        <v>1.351220309761392</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.9090127949427966</v>
+        <v>0.7895250432496626</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.410823721847914</v>
+        <v>3.339131070832033</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.583684174548509</v>
+        <v>-3.698354813991362</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.426532221322945</v>
+        <v>1.380663965545804</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.9090127949427966</v>
+        <v>0.7895250432496626</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.405769992421774</v>
+        <v>3.334077341405894</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.628990993947489</v>
+        <v>-3.743661633390342</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.400185269007879</v>
+        <v>1.354317013230737</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8682026319335658</v>
+        <v>0.7487148802404318</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.373059670060761</v>
+        <v>3.301367019044881</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.65802409864979</v>
+        <v>-3.772694738092644</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.389123900160059</v>
+        <v>1.343255644382918</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8682026319335658</v>
+        <v>0.7487148802404318</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.373611543093863</v>
+        <v>3.301918892077982</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.565213617198931</v>
+        <v>-3.679884256641785</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.355520784631769</v>
+        <v>1.309652528854627</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9610131133844252</v>
+        <v>0.8415253616912911</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.358570523855744</v>
+        <v>3.286877872839864</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.609603086528359</v>
+        <v>-3.724273725971212</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.339638472824599</v>
+        <v>1.293770217047457</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.9166236440549975</v>
+        <v>0.7971358923618634</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.333810318182688</v>
+        <v>3.262117667166808</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.726144691633702</v>
+        <v>-3.840815331076555</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.288097539294184</v>
+        <v>1.242229283517043</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8000820389496548</v>
+        <v>0.6805942872565207</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.258961063631205</v>
+        <v>3.187268412615325</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.766068786216273</v>
+        <v>-3.880739425659127</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.277619197291823</v>
+        <v>1.231750941514682</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8000820389496548</v>
+        <v>0.6805942872565207</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.264452359461873</v>
+        <v>3.192759708445992</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.793849184117626</v>
+        <v>-3.90851982356048</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.278004239899821</v>
+        <v>1.232135984122679</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7723016410483017</v>
+        <v>0.6528138893551676</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.2592813224896</v>
+        <v>3.18758867147372</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.912229856847765</v>
+        <v>-4.026900496290618</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.069007690808419</v>
+        <v>1.023139435031277</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7050837888973255</v>
+        <v>0.5855960372041914</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.057306331199667</v>
+        <v>2.985613680183787</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.020843935291095</v>
+        <v>-4.135514574733949</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.145711720150292</v>
+        <v>1.099843464373151</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7050837888973255</v>
+        <v>0.5855960372041914</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.177455991918873</v>
+        <v>3.105763340902993</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.985434897042953</v>
+        <v>-4.100105536485806</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.174388361551872</v>
+        <v>1.128520105774731</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7050837888973255</v>
+        <v>0.5855960372041914</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.191969018021196</v>
+        <v>3.120276367005316</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.947051234484801</v>
+        <v>-4.061721873927655</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.187161267917501</v>
+        <v>1.14129301214036</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7434674514554767</v>
+        <v>0.6239796997623426</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.212418656898456</v>
+        <v>3.140726005882575</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.769934904449635</v>
+        <v>-3.884605543892489</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.25473682877687</v>
+        <v>1.208868572999728</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7434674514554767</v>
+        <v>0.6239796997623426</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.209147685743758</v>
+        <v>3.137455034727877</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.815027149283181</v>
+        <v>-3.929697788726035</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.237383322605365</v>
+        <v>1.191515066828223</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6815714082860869</v>
+        <v>0.5620836565929528</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.172693451604037</v>
+        <v>3.101000800588156</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.635651728044413</v>
+        <v>-3.750322367487267</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.302920466407286</v>
+        <v>1.257052210630144</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8383481664568055</v>
+        <v>0.7188604147636715</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.260546481812882</v>
+        <v>3.188853830797002</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.68066594156502</v>
+        <v>-3.795336581007873</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.265722236330633</v>
+        <v>1.219853980553492</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8079992711422009</v>
+        <v>0.6885115194490669</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.223144599955709</v>
+        <v>3.151451948939829</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.947670451837455</v>
+        <v>-4.062341091280309</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.164611994560605</v>
+        <v>1.118743738783463</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6136362330992524</v>
+        <v>0.4941484814061183</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.112218339468886</v>
+        <v>3.040525688453005</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.048868233274628</v>
+        <v>-4.163538872717481</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.123336803882237</v>
+        <v>1.077468548105096</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5452274195539333</v>
+        <v>0.4257396678607991</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.070376973238196</v>
+        <v>2.998684322222315</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.042357266660315</v>
+        <v>-4.157027906103169</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.123541152082279</v>
+        <v>1.077672896305137</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5452274195539333</v>
+        <v>0.4257396678607991</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.067976934792513</v>
+        <v>2.996284283776632</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.023319138953018</v>
+        <v>-4.137989778395871</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.127681122373443</v>
+        <v>1.081812866596301</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4870438082227387</v>
+        <v>0.3675560565296046</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.029591487202041</v>
+        <v>2.95789883618616</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.075834941227838</v>
+        <v>-4.190505580670692</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.225969203097705</v>
+        <v>1.180100947320563</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4870438082227387</v>
+        <v>0.3675560565296046</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.148885888836231</v>
+        <v>3.07719323782035</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.089701702561756</v>
+        <v>-4.20437234200461</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.221255827550271</v>
+        <v>1.17538757177313</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4491858914889158</v>
+        <v>0.3296981397957817</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.127004467782071</v>
+        <v>3.05531181676619</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.044897531021826</v>
+        <v>-4.15956817046468</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.245186026563169</v>
+        <v>1.199317770786028</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4491858914889158</v>
+        <v>0.3296981397957817</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.133012998178997</v>
+        <v>3.061320347163116</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.897154560786824</v>
+        <v>-4.011825200229677</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.20223343593437</v>
+        <v>1.156365180157228</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.616993248723799</v>
+        <v>0.4975054970306648</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.131647633797126</v>
+        <v>3.059954982781246</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.980975782061522</v>
+        <v>-4.095646421504376</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.171498568955971</v>
+        <v>1.12563031317883</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.616993248723799</v>
+        <v>0.4975054970306648</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.134441255328607</v>
+        <v>3.062748604312727</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.974823076008738</v>
+        <v>-4.089493715451591</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.174621999768743</v>
+        <v>1.128753743991602</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6231459547765833</v>
+        <v>0.5036582030834491</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.138795227351936</v>
+        <v>3.067102576336056</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.991632374159239</v>
+        <v>-4.106303013602093</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.166978757248653</v>
+        <v>1.121110501471511</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6063366566260817</v>
+        <v>0.4868489049329475</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.127790125201745</v>
+        <v>3.056097474185865</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.929334375383117</v>
+        <v>-4.044005014825971</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.258233510555923</v>
+        <v>1.212365254778781</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6516309209005238</v>
+        <v>0.5321431692073895</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.221302237563231</v>
+        <v>3.149609586547351</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.727544177717959</v>
+        <v>-3.842214817160813</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.141241591336113</v>
+        <v>1.095373335558972</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8496491130696782</v>
+        <v>0.7301613613765439</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.142405154578851</v>
+        <v>3.070712503562971</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.778430890404154</v>
+        <v>-3.893101529847008</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.19117713858381</v>
+        <v>1.145308882806669</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7987624003834837</v>
+        <v>0.6792746486903494</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.182163359289309</v>
+        <v>3.110470708273429</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.691820147754347</v>
+        <v>-3.8064907871972</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.240449171759777</v>
+        <v>1.194580915982635</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8773881315886419</v>
+        <v>0.7579003798955076</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.243966534128448</v>
+        <v>3.172273883112568</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.752029445759631</v>
+        <v>-3.866700085202485</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.214901433382335</v>
+        <v>1.169033177605193</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8171788335833574</v>
+        <v>0.6976910818902231</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.206376936149949</v>
+        <v>3.134684285134069</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.675607399327705</v>
+        <v>-3.790278038770558</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.243961869995034</v>
+        <v>1.198093614217893</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8171788335833574</v>
+        <v>0.6976910818902231</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.204868554189878</v>
+        <v>3.133175903173997</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.631234267689136</v>
+        <v>-3.745904907131989</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.261573990085898</v>
+        <v>1.215705734308756</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.861551965221926</v>
+        <v>0.7420642135287917</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.231355300608455</v>
+        <v>3.159662649592574</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.653714618548021</v>
+        <v>-3.768385257990874</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.246975643880934</v>
+        <v>1.201107388103793</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.861551965221926</v>
+        <v>0.7420642135287917</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.225749094747046</v>
+        <v>3.154056443731165</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.606058887986965</v>
+        <v>-3.720729527429818</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.272419693133161</v>
+        <v>1.22655143735602</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9092076957829817</v>
+        <v>0.7897199440898474</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.260724290111484</v>
+        <v>3.189031639095603</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.50554072948821</v>
+        <v>-3.620211368931064</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.317519329907388</v>
+        <v>1.271651074130246</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.009725854281736</v>
+        <v>0.8902381025886019</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.325927558585462</v>
+        <v>3.254234907569581</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.489635400055858</v>
+        <v>-3.604306039498711</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.310636134156201</v>
+        <v>1.26476787837906</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9306131935724973</v>
+        <v>0.811125441879363</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.26521463463579</v>
+        <v>3.19352198361991</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.44479699844746</v>
+        <v>-3.559467637890313</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.332669197410189</v>
+        <v>1.286800941633047</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9351566265173668</v>
+        <v>0.8156688748242324</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.272038397013341</v>
+        <v>3.20034574599746</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.464295454689468</v>
+        <v>-3.578966094132321</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.329030754544464</v>
+        <v>1.283162498767322</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8870719852374624</v>
+        <v>0.7675842335443281</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.247348551876476</v>
+        <v>3.175655900860595</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.420092617603567</v>
+        <v>-3.534763257046421</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.352591491906661</v>
+        <v>1.30672323612952</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9312748223233629</v>
+        <v>0.8117870706302286</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.279749856655853</v>
+        <v>3.208057205639973</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.427652283440614</v>
+        <v>-3.542322922883468</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.34797762604109</v>
+        <v>1.302109370263948</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9860782263331822</v>
+        <v>0.8665904746400479</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.311041899530992</v>
+        <v>3.239349248515112</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.269360865901342</v>
+        <v>-3.384031505344196</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.462541958239838</v>
+        <v>1.416673702462697</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9860782263331822</v>
+        <v>0.8665904746400479</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.362289664714032</v>
+        <v>3.290597013698151</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.061718862266866</v>
+        <v>-3.176389501709719</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.544039464287882</v>
+        <v>1.498171208510741</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.193720229967658</v>
+        <v>1.074232478274524</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.485315571488971</v>
+        <v>3.41362292047309</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.010686769544338</v>
+        <v>-3.125357408987191</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.559400529615163</v>
+        <v>1.513532273838022</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.244752322690186</v>
+        <v>1.125264570997052</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.510883055360758</v>
+        <v>3.439190404344877</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.945462588417132</v>
+        <v>-3.060133227859986</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.60267760615875</v>
+        <v>1.556809350381609</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.309976503817392</v>
+        <v>1.190488752124258</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.567204968129786</v>
+        <v>3.495512317113906</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.908035568345998</v>
+        <v>-3.022706207788852</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.613609386486484</v>
+        <v>1.567741130709343</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.315228041846574</v>
+        <v>1.195740290153439</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.566316863246575</v>
+        <v>3.494624212230695</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.928147224380707</v>
+        <v>-3.04281786382356</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.606821516403841</v>
+        <v>1.5609532606267</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.326255386843993</v>
+        <v>1.206767635150858</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.574190062576267</v>
+        <v>3.502497411560387</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.874402409953502</v>
+        <v>-2.989073049396355</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.788877213195934</v>
+        <v>1.743008957418793</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.336318696284455</v>
+        <v>1.216830944591321</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.740785819261755</v>
+        <v>3.669093168245874</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.799620148928489</v>
+        <v>-2.914290788371343</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.938903026823756</v>
+        <v>1.893034771046615</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.411100957309467</v>
+        <v>1.291613205616333</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.90576808509458</v>
+        <v>3.8340754340787</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.773536064664681</v>
+        <v>-2.888206704107535</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.941044636543138</v>
+        <v>1.895176380765997</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.411100957309467</v>
+        <v>1.291613205616333</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.897476061108439</v>
+        <v>3.825783410092559</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.685658151555561</v>
+        <v>-2.800328790998414</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.974388997370566</v>
+        <v>1.928520741593425</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.527026599732819</v>
+        <v>1.407538848039684</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.965224642146229</v>
+        <v>3.893531991130349</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.676765690162277</v>
+        <v>-2.791436329605131</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.995500387654671</v>
+        <v>1.94963213187753</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.527026599732819</v>
+        <v>1.407538848039684</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.98277904787302</v>
+        <v>3.91108639685714</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.845241807132155</v>
+        <v>-2.959912446575009</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.919964988271304</v>
+        <v>1.874096732494162</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.499078764016238</v>
+        <v>1.379591012323104</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.957865393847656</v>
+        <v>3.886172742831775</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.398985614502715</v>
+        <v>-2.513656253945569</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.079737162510941</v>
+        <v>2.0338689067338</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.404360094346605</v>
+        <v>1.284872342653471</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.882303889233738</v>
+        <v>3.810611238217858</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.376264510819563</v>
+        <v>-2.490935150262416</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.079489626481107</v>
+        <v>2.033621370703965</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.404360094346605</v>
+        <v>1.284872342653471</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.872967911730643</v>
+        <v>3.801275260714762</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.505466324113605</v>
+        <v>-2.620136963556459</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.186715027014659</v>
+        <v>2.140846771237518</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.275158281052563</v>
+        <v>1.155670529359429</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.954352949605386</v>
+        <v>3.882660298589506</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.660247330891861</v>
+        <v>-2.774917970334714</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.161880446797003</v>
+        <v>2.116012191019862</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.241790606998087</v>
+        <v>1.122302855304953</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.971410167666347</v>
+        <v>3.899717516650467</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.653192640676687</v>
+        <v>-2.767863280119541</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.161377678872618</v>
+        <v>2.115509423095476</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.248845297213261</v>
+        <v>1.129357545520126</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.972318337784997</v>
+        <v>3.900625686769116</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.626241416350199</v>
+        <v>-2.740912055793053</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.182164322247955</v>
+        <v>2.136296066470813</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.26372564324098</v>
+        <v>1.144237891547845</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.991252699046369</v>
+        <v>3.91956004803049</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.762194424406515</v>
+        <v>-2.876865063849369</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.311886251170388</v>
+        <v>2.266017995393247</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.26372564324098</v>
+        <v>1.144237891547845</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.17535583119133</v>
+        <v>4.103663180175449</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.784602542211387</v>
+        <v>-2.899273181654241</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.295039698951432</v>
+        <v>2.249171443174291</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.26372564324098</v>
+        <v>1.144237891547845</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.167472526094323</v>
+        <v>4.095779875078442</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.812826777788988</v>
+        <v>-2.927497417231841</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.285804004270029</v>
+        <v>2.239935748492888</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.281702395692288</v>
+        <v>1.162214643999154</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.180312577114745</v>
+        <v>4.108619926098864</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.822267703677518</v>
+        <v>-2.936938343120371</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.338281351636465</v>
+        <v>2.292413095859323</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.40412951323568</v>
+        <v>1.284641761542546</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.310022565362627</v>
+        <v>4.238329914346747</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.874541311013159</v>
+        <v>-2.989211950456013</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.320263003247509</v>
+        <v>2.274394747470367</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.351855905900039</v>
+        <v>1.232368154206904</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.281549495506543</v>
+        <v>4.209856844490663</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.950871288614065</v>
+        <v>-3.065541928056918</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.287842825100922</v>
+        <v>2.24197456932378</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.351855905900039</v>
+        <v>1.232368154206904</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.279661308400319</v>
+        <v>4.207968657384438</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.153125008938418</v>
+        <v>-3.267795648381272</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.201761566574043</v>
+        <v>2.155893310796901</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.149602185575685</v>
+        <v>1.030114433882551</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.153129305808569</v>
+        <v>4.081436654792688</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.314693434465673</v>
+        <v>-3.429364073908527</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.135568206573293</v>
+        <v>2.089699950796152</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.022819261777806</v>
+        <v>0.9033315100846714</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.075493561739994</v>
+        <v>4.003800910724113</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.446994726563227</v>
+        <v>-3.56166536600608</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.09572109660019</v>
+        <v>2.049852840823049</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.022819261777806</v>
+        <v>0.9033315100846714</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.088566968605912</v>
+        <v>4.016874317590031</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.632863037402457</v>
+        <v>-3.74753367684531</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.013378969047438</v>
+        <v>1.967510713270297</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8642536684578581</v>
+        <v>0.7447659167647237</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.985432809396883</v>
+        <v>3.913740158381003</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.66076382451193</v>
+        <v>-3.775434463954783</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.000742695330652</v>
+        <v>1.95487443955351</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8296567443149233</v>
+        <v>0.7101689926217889</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.963198696038124</v>
+        <v>3.891506045022244</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.783289927214823</v>
+        <v>-3.897960566657677</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.948496698226692</v>
+        <v>1.902628442449551</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7071306416120294</v>
+        <v>0.587642889918895</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.886447478393587</v>
+        <v>3.814754827377707</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.013804423400412</v>
+        <v>-4.128475062843266</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.922996859342961</v>
+        <v>1.877128603565819</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4766161454264407</v>
+        <v>0.3571283937333063</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.814844740272738</v>
+        <v>3.743152089256857</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.270525241395235</v>
+        <v>-4.38519588083809</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.960620251146878</v>
+        <v>1.914751995369737</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3682015712826259</v>
+        <v>0.2487138195894915</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.890107714788296</v>
+        <v>3.818415063772415</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.424511659171376</v>
+        <v>-4.539182298614231</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.968005953182062</v>
+        <v>1.92213769740492</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3682015712826259</v>
+        <v>0.2487138195894915</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.959087983933935</v>
+        <v>3.887395332918055</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.37398975534371</v>
+        <v>-4.488660394786565</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.974265916833249</v>
+        <v>1.928397661056108</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3682015712826259</v>
+        <v>0.2487138195894915</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.945139186054057</v>
+        <v>3.873446535038176</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.626464909351435</v>
+        <v>-4.741135548794289</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.885146344285574</v>
+        <v>1.839278088508432</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3682015712826259</v>
+        <v>0.2487138195894915</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.957009675109471</v>
+        <v>3.88531702409359</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.919360665830847</v>
+        <v>-5.034031305273701</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.769198576212752</v>
+        <v>1.723330320435611</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3682015712826259</v>
+        <v>0.2487138195894915</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.958220209628414</v>
+        <v>3.886527558612534</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.106024793965655</v>
+        <v>-5.220695433408509</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.698654667186151</v>
+        <v>1.652786411409009</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.341462600458066</v>
+        <v>0.2219748487649316</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.946298569361</v>
+        <v>3.874605918345119</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.252045480879617</v>
+        <v>-5.366716120322471</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.635324245156755</v>
+        <v>1.589455989379613</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.332379508664209</v>
+        <v>0.2128917569710746</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.935926567020875</v>
+        <v>3.864233916004994</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.369013173518508</v>
+        <v>-5.483683812961362</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.750741224800243</v>
+        <v>1.704872969023101</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.332379508664209</v>
+        <v>0.2128917569710746</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.098130623719919</v>
+        <v>4.026437972704039</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.453731115739461</v>
+        <v>-5.568401755182316</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.711700685875676</v>
+        <v>1.665832430098534</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2472634797361626</v>
+        <v>0.1277757280430282</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.041907644326905</v>
+        <v>3.970214993311025</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.535665934008344</v>
+        <v>-5.650336573451199</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.689156176136613</v>
+        <v>1.643287920359472</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2373287341490825</v>
+        <v>0.117840982455948</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.046176214543149</v>
+        <v>3.974483563527268</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.637642056256752</v>
+        <v>-5.752312695699606</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.657291365693153</v>
+        <v>1.611423109916011</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1353526119006749</v>
+        <v>0.01586486020754047</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.993916179650006</v>
+        <v>3.922223528634126</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.52763577277953</v>
+        <v>-5.642306412222385</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.693446766328217</v>
+        <v>1.647578510551075</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1585571838179501</v>
+        <v>0.03906943212481567</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.999991810044547</v>
+        <v>3.928299159028666</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.384576197038605</v>
+        <v>-5.49924683648146</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.754920607346561</v>
+        <v>1.70905235156942</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1665706104079294</v>
+        <v>0.04708285871479495</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.009049876720509</v>
+        <v>3.937357225704628</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.083129471566767</v>
+        <v>-5.197800111009622</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.882760180417832</v>
+        <v>1.836891924640691</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4680173358797666</v>
+        <v>0.3485295841866322</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.197178794886147</v>
+        <v>4.125486143870266</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.107719715801951</v>
+        <v>-5.222390355244806</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.873895260476469</v>
+        <v>1.828027004699328</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4680173358797666</v>
+        <v>0.3485295841866322</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.198149972638857</v>
+        <v>4.126457321622977</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.056681339795431</v>
+        <v>-5.171351979238286</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.895153515258833</v>
+        <v>1.849285259481691</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4680173358797666</v>
+        <v>0.3485295841866322</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.198992877018613</v>
+        <v>4.127300226002732</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.0155420449288</v>
+        <v>-5.130212684371655</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.93064733207963</v>
+        <v>1.884779076302489</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5091566307463975</v>
+        <v>0.389668879053263</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.242714552812736</v>
+        <v>4.171021901796856</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.91890713291016</v>
+        <v>-5.033577772353015</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.785485293011021</v>
+        <v>1.739617037233879</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6057915427650374</v>
+        <v>0.486303791071903</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.116879496147855</v>
+        <v>4.045186845131974</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.049487867441003</v>
+        <v>-5.164158506883857</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.736755043272648</v>
+        <v>1.690886787495506</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4752108082341949</v>
+        <v>0.3557230565410605</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.042033099503313</v>
+        <v>3.970340448487432</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.884991533250041</v>
+        <v>-4.999662172692895</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.786980396025115</v>
+        <v>1.741112140247973</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4752108082341949</v>
+        <v>0.3557230565410605</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.026459918579396</v>
+        <v>3.954767267563515</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.912361465934473</v>
+        <v>-5.027032105377327</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.775220133387772</v>
+        <v>1.72935187761063</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4752108082341949</v>
+        <v>0.3557230565410605</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.025647629015825</v>
+        <v>3.953954977999945</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.922746660824362</v>
+        <v>-5.037417300267217</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.780934834556889</v>
+        <v>1.735066578779747</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4648256133443056</v>
+        <v>0.3453378616511711</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.029285291206964</v>
+        <v>3.957592640191084</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.941334819546587</v>
+        <v>-5.056005458989442</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.844336576844424</v>
+        <v>1.798468321067282</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4462374546220803</v>
+        <v>0.3267497029289458</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.088969401750054</v>
+        <v>4.017276750734173</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.941633366242623</v>
+        <v>-5.056304005685478</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.841086168984308</v>
+        <v>1.795217913207166</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4462374546220803</v>
+        <v>0.3267497029289458</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.085838412568353</v>
+        <v>4.014145761552472</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.840810232552196</v>
+        <v>-4.95548087199505</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.88594631739987</v>
+        <v>1.840078061622729</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4587016701064341</v>
+        <v>0.3392139184132996</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.097847836798357</v>
+        <v>4.026155185782476</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.650028871799789</v>
+        <v>-4.764699511242643</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.962388115179377</v>
+        <v>1.916519859402235</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6494830308588415</v>
+        <v>0.529995279165707</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.212445906728345</v>
+        <v>4.140753255712464</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.631512017757968</v>
+        <v>-4.746182657200823</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.949631702533701</v>
+        <v>1.903763446756559</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6624131602840497</v>
+        <v>0.5429254085909152</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.200040830121066</v>
+        <v>4.128348179105185</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.60631883325665</v>
+        <v>-4.720989472699505</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.994675912946287</v>
+        <v>1.948807657169145</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6876063447853681</v>
+        <v>0.5681185930922336</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.250123677433916</v>
+        <v>4.178431026418035</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.594264706343687</v>
+        <v>-4.708935345786542</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.993184131612909</v>
+        <v>1.947315875835768</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6996604716983309</v>
+        <v>0.5801727200051964</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.251042721483131</v>
+        <v>4.17935007046725</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.600887953034046</v>
+        <v>-4.7155585924769</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.992415463120902</v>
+        <v>1.946547207343761</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6930372250079726</v>
+        <v>0.5735494733148381</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.248949403653052</v>
+        <v>4.177256752637171</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.498007363505453</v>
+        <v>-4.612678002948307</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.046418724810222</v>
+        <v>2.00055046903308</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7959178145365655</v>
+        <v>0.676430062843431</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.32352878324809</v>
+        <v>4.251836132232209</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.52144940268554</v>
+        <v>-4.636120042128394</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.057244579311782</v>
+        <v>2.011376323534639</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7959178145365655</v>
+        <v>0.676430062843431</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.343731453421684</v>
+        <v>4.272038802405803</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.539521910977151</v>
+        <v>-4.654192550420006</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.050015575995137</v>
+        <v>2.004147320217995</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7959178145365655</v>
+        <v>0.676430062843431</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.343731453421684</v>
+        <v>4.272038802405803</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.770695704853783</v>
+        <v>-4.885366344296638</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.91779797203795</v>
+        <v>1.871929716260809</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7959178145365655</v>
+        <v>0.676430062843431</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.30398336701515</v>
+        <v>4.23229071599927</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.739409684313328</v>
+        <v>-4.854080323756182</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.937334999251072</v>
+        <v>1.891466743473931</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8272038350770209</v>
+        <v>0.7077160833838864</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.329777598336364</v>
+        <v>4.258084947320483</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.586384292200044</v>
+        <v>-4.701054931642898</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.09771615566929</v>
+        <v>2.051847899892149</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.980229227190305</v>
+        <v>0.8607414754971705</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.520763833177238</v>
+        <v>4.449071182161358</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.614691606073314</v>
+        <v>-4.729362245516168</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.273859455028274</v>
+        <v>2.227991199251133</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.980229227190305</v>
+        <v>0.8607414754971705</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.708230058085531</v>
+        <v>4.63653740706965</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.781284831186836</v>
+        <v>-4.895955470629691</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.176625116336948</v>
+        <v>2.130756860559806</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8136360020767825</v>
+        <v>0.694148250383648</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.5776770743715</v>
+        <v>4.505984423355619</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.608220451804536</v>
+        <v>-4.722891091247391</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.249527270751586</v>
+        <v>2.203659014974444</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8136360020767825</v>
+        <v>0.694148250383648</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.581353477033217</v>
+        <v>4.509660826017337</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.57897447134884</v>
+        <v>-4.693645110791694</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.25884371805736</v>
+        <v>2.212975462280218</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8136360020767825</v>
+        <v>0.694148250383648</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.578971532156713</v>
+        <v>4.507278881140832</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.685900019226691</v>
+        <v>-4.800570658669545</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.213366738063854</v>
+        <v>2.167498482286712</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7067104541989312</v>
+        <v>0.5872227025057967</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.512109442587636</v>
+        <v>4.440416791571757</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.830918577733939</v>
+        <v>-4.945589217176794</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.156788116804189</v>
+        <v>2.110919861027047</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5616918956916827</v>
+        <v>0.4422041439985481</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.426527109626522</v>
+        <v>4.354834458610641</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.552240899647581</v>
+        <v>3.552240899647582</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.314362672757079</v>
+        <v>4.085308205557848</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.723727364555519</v>
+        <v>-4.838122086591127</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.424515302621124</v>
+        <v>2.14970294660765</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5616918956916827</v>
+        <v>0.4422041439985481</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.65137781017209</v>
+        <v>4.350630691956977</v>
       </c>
     </row>
   </sheetData>
